--- a/data/observation_alpha_beta.xlsx
+++ b/data/observation_alpha_beta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phd\php_pulsating_heat_pipe\Krp_Analysis\Advanced_PulseHeatPipe_krp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45EBA0A-05EE-48C5-BEBC-B5B78F87511A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A842D2A2-9F75-462A-AD8E-8620CF1358F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,18 +36,6 @@
   </si>
   <si>
     <t>beta</t>
-  </si>
-  <si>
-    <t>Te1_mean[K]</t>
-  </si>
-  <si>
-    <t>Te2_mean[K]</t>
-  </si>
-  <si>
-    <t>Tc1_mean[K]</t>
-  </si>
-  <si>
-    <t>Tc2_mean[K]</t>
   </si>
   <si>
     <t>P1[bar]</t>
@@ -84,6 +72,18 @@
   </si>
   <si>
     <t>Q[W]</t>
+  </si>
+  <si>
+    <t>Te1[K]</t>
+  </si>
+  <si>
+    <t>Te2[K]</t>
+  </si>
+  <si>
+    <t>Tc1[K]</t>
+  </si>
+  <si>
+    <t>Tc2[K]</t>
   </si>
 </sst>
 </file>
@@ -1674,9 +1674,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="8.54296875" style="3" customWidth="1"/>
-    <col min="4" max="5" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.54296875" style="3" customWidth="1"/>
-    <col min="7" max="8" width="12.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="9.08984375" style="3" customWidth="1"/>
     <col min="9" max="9" width="8.54296875" style="3" customWidth="1"/>
     <col min="10" max="11" width="10.26953125" style="3" customWidth="1"/>
     <col min="12" max="13" width="8.54296875" style="3" customWidth="1"/>
@@ -1688,7 +1686,7 @@
   <sheetData>
     <row r="1" spans="1:17" s="5" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1697,43 +1695,43 @@
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="O1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2168,7 +2166,7 @@
         <v>-140</v>
       </c>
       <c r="Q9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2562,9 +2560,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="8.54296875" style="3" customWidth="1"/>
-    <col min="4" max="5" width="13" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.54296875" style="3" customWidth="1"/>
-    <col min="7" max="8" width="12.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="9" style="3" customWidth="1"/>
     <col min="9" max="9" width="8.54296875" style="3" customWidth="1"/>
     <col min="10" max="11" width="10.26953125" style="3" customWidth="1"/>
     <col min="12" max="13" width="8.54296875" style="3" customWidth="1"/>
@@ -2576,7 +2572,7 @@
   <sheetData>
     <row r="1" spans="1:17" s="5" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -2585,43 +2581,43 @@
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="O1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2864,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3231,7 +3227,7 @@
         <v>-140</v>
       </c>
       <c r="Q13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/data/observation_alpha_beta.xlsx
+++ b/data/observation_alpha_beta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phd\php_pulsating_heat_pipe\Krp_Analysis\Advanced_PulseHeatPipe_krp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33761BF9-FF3E-41C1-8ACC-C75317175B24}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4289ED7D-3208-482C-A879-50DBBA8ED12A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/observation_alpha_beta.xlsx
+++ b/data/observation_alpha_beta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phd\php_pulsating_heat_pipe\Krp_Analysis\Advanced_PulseHeatPipe_krp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4289ED7D-3208-482C-A879-50DBBA8ED12A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E11E356-21C3-40DC-892E-DF5D3A7FF373}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="final" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">demo!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">demo!$A$1:$R$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">final!$A$1:$Q$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
   <si>
     <t>alpha</t>
   </si>
@@ -88,6 +88,12 @@
   <si>
     <t>must repeat</t>
   </si>
+  <si>
+    <t>Change in TR1 [%]</t>
+  </si>
+  <si>
+    <t>Change in TR2 [%]</t>
+  </si>
 </sst>
 </file>
 
@@ -357,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -499,6 +505,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -781,20 +799,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC5BB13-84A6-40A9-B2F0-16EBC4A52D5E}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="8.54296875" style="3" customWidth="1"/>
     <col min="4" max="8" width="9" style="3" customWidth="1"/>
     <col min="9" max="9" width="8.54296875" style="3" customWidth="1"/>
-    <col min="10" max="11" width="10.26953125" style="3" customWidth="1"/>
-    <col min="12" max="13" width="8.54296875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.54296875" style="3" customWidth="1"/>
+    <col min="10" max="13" width="10.26953125" style="3" customWidth="1"/>
+    <col min="14" max="15" width="8.54296875" style="3" customWidth="1"/>
     <col min="16" max="16" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.54296875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" s="5" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>13</v>
       </c>
@@ -826,25 +844,31 @@
         <v>12</v>
       </c>
       <c r="K1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>40</v>
       </c>
@@ -878,27 +902,33 @@
         <f>(D2-G2)/A2</f>
         <v>1.05</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="49">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6">
         <f>(E2-H2)/A2</f>
         <v>0.92500000000000004</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="49">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
         <v>0.62</v>
       </c>
-      <c r="M2" s="1">
+      <c r="O2" s="1">
         <v>0.75</v>
       </c>
-      <c r="N2" s="1">
+      <c r="P2" s="1">
         <v>-155</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>-190</v>
       </c>
-      <c r="P2" s="1">
+      <c r="R2" s="1">
         <v>-100</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>40</v>
       </c>
@@ -933,26 +963,34 @@
         <v>1.125</v>
       </c>
       <c r="K3" s="6">
-        <f t="shared" ref="K3:K17" si="3">(E3-H3)/A3</f>
+        <f>(J2-J3)/J2</f>
+        <v>-7.1428571428571383E-2</v>
+      </c>
+      <c r="L3" s="6">
+        <f>(E3-H3)/A3</f>
         <v>1.3</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="6">
+        <f>(L2-L3)/L2</f>
+        <v>-0.40540540540540537</v>
+      </c>
+      <c r="N3" s="1">
         <v>0.7</v>
       </c>
-      <c r="M3" s="1">
+      <c r="O3" s="1">
         <v>0.8</v>
       </c>
-      <c r="N3" s="1">
+      <c r="P3" s="1">
         <v>-140</v>
       </c>
-      <c r="O3" s="1">
+      <c r="Q3" s="1">
         <v>-160</v>
       </c>
-      <c r="P3" s="1">
+      <c r="R3" s="1">
         <v>-0.85</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>40</v>
       </c>
@@ -987,26 +1025,34 @@
         <v>1.125</v>
       </c>
       <c r="K4" s="6">
-        <f t="shared" si="3"/>
+        <f>(J2-J4)/J2</f>
+        <v>-7.1428571428571383E-2</v>
+      </c>
+      <c r="L4" s="6">
+        <f t="shared" ref="L3:L17" si="3">(E4-H4)/A4</f>
         <v>1.3125</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="6">
+        <f>(L2-L4)/L2</f>
+        <v>-0.41891891891891886</v>
+      </c>
+      <c r="N4" s="1">
         <v>0.7</v>
       </c>
-      <c r="M4" s="1">
+      <c r="O4" s="1">
         <v>0.83</v>
       </c>
-      <c r="N4" s="1">
+      <c r="P4" s="1">
         <v>-130</v>
       </c>
-      <c r="O4" s="1">
+      <c r="Q4" s="1">
         <v>-150</v>
       </c>
-      <c r="P4" s="1">
+      <c r="R4" s="1">
         <v>-90</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>60</v>
       </c>
@@ -1040,27 +1086,29 @@
         <f t="shared" si="2"/>
         <v>0.78333333333333333</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="6"/>
+      <c r="L5" s="6">
         <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="6"/>
+      <c r="N5" s="1">
         <v>0.65</v>
       </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1">
         <v>-160</v>
       </c>
-      <c r="O5" s="1">
+      <c r="Q5" s="1">
         <v>-180</v>
       </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>60</v>
       </c>
@@ -1094,27 +1142,29 @@
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="6"/>
+      <c r="L6" s="6">
         <f t="shared" si="3"/>
         <v>0.6333333333333333</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="6"/>
+      <c r="N6" s="1">
         <v>0.75</v>
       </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1">
         <v>-120</v>
       </c>
-      <c r="O6" s="1">
+      <c r="Q6" s="1">
         <v>-150</v>
       </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>80</v>
       </c>
@@ -1148,27 +1198,33 @@
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="50">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
         <f t="shared" si="3"/>
         <v>0.4375</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="50">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
         <v>0.75</v>
       </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1">
         <v>-125</v>
       </c>
-      <c r="O7" s="1">
+      <c r="Q7" s="1">
         <v>-150</v>
       </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>80</v>
       </c>
@@ -1203,26 +1259,34 @@
         <v>0.625</v>
       </c>
       <c r="K8" s="6">
+        <f>(J7-J8)/J7</f>
+        <v>-4.1666666666666706E-2</v>
+      </c>
+      <c r="L8" s="6">
         <f t="shared" si="3"/>
         <v>0.5625</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="6">
+        <f>(L7-L8)/L7</f>
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="N8" s="1">
         <v>0.8</v>
       </c>
-      <c r="M8" s="1">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1">
         <v>-85</v>
       </c>
-      <c r="O8" s="1">
+      <c r="Q8" s="1">
         <v>-100</v>
       </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>80</v>
       </c>
@@ -1257,26 +1321,34 @@
         <v>0.5625</v>
       </c>
       <c r="K9" s="6">
+        <f>(J7-J9)/J7</f>
+        <v>6.2499999999999965E-2</v>
+      </c>
+      <c r="L9" s="6">
         <f t="shared" si="3"/>
         <v>0.45</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="6">
+        <f>(L7-L9)/L7</f>
+        <v>-2.8571428571428598E-2</v>
+      </c>
+      <c r="N9" s="1">
         <v>0.65</v>
       </c>
-      <c r="M9" s="1">
-        <v>1</v>
-      </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1">
         <v>-160</v>
       </c>
-      <c r="O9" s="1">
+      <c r="Q9" s="1">
         <v>-200</v>
       </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>80</v>
       </c>
@@ -1302,35 +1374,43 @@
       <c r="H10" s="2">
         <v>303.5</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="51">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="52">
         <f t="shared" si="2"/>
         <v>0.71250000000000002</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="52">
+        <f>(J7-J10)/J7</f>
+        <v>-0.18750000000000008</v>
+      </c>
+      <c r="L10" s="52">
         <f t="shared" si="3"/>
         <v>0.75624999999999998</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="52">
+        <f>(L7-L10)/L7</f>
+        <v>-0.72857142857142854</v>
+      </c>
+      <c r="N10" s="2">
         <v>0.7</v>
       </c>
-      <c r="M10" s="2">
+      <c r="O10" s="2">
         <v>0.75</v>
       </c>
-      <c r="N10" s="2">
+      <c r="P10" s="2">
         <v>-150</v>
       </c>
-      <c r="O10" s="2">
+      <c r="Q10" s="2">
         <v>-160</v>
       </c>
-      <c r="P10" s="2">
+      <c r="R10" s="2">
         <v>-140</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -1365,26 +1445,32 @@
         <v>0.47</v>
       </c>
       <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
         <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="6">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
         <v>0.72</v>
       </c>
-      <c r="M11" s="1">
-        <v>1</v>
-      </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1">
         <v>-130</v>
       </c>
-      <c r="O11" s="1">
+      <c r="Q11" s="1">
         <v>-160</v>
       </c>
-      <c r="P11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>100</v>
       </c>
@@ -1419,26 +1505,34 @@
         <v>0.47</v>
       </c>
       <c r="K12" s="6">
+        <f>(J11-J12)/J11</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="6">
         <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="6">
+        <f>(L11-L12)/L11</f>
+        <v>7.5000000000000067E-2</v>
+      </c>
+      <c r="N12" s="1">
         <v>0.75</v>
       </c>
-      <c r="M12" s="1">
-        <v>1</v>
-      </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1">
         <v>-120</v>
       </c>
-      <c r="O12" s="1">
+      <c r="Q12" s="1">
         <v>-130</v>
       </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>100</v>
       </c>
@@ -1473,26 +1567,34 @@
         <v>0.4</v>
       </c>
       <c r="K13" s="6">
+        <f>(J11-J13)/J11</f>
+        <v>0.14893617021276587</v>
+      </c>
+      <c r="L13" s="6">
         <f t="shared" si="3"/>
         <v>0.32</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="6">
+        <f>(L11-L13)/L11</f>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="N13" s="1">
         <v>0.45</v>
       </c>
-      <c r="M13" s="1">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1">
         <v>-250</v>
       </c>
-      <c r="O13" s="1">
+      <c r="Q13" s="1">
         <v>-280</v>
       </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>100</v>
       </c>
@@ -1527,26 +1629,34 @@
         <v>0.48</v>
       </c>
       <c r="K14" s="6">
+        <f>(J11-J14)/J11</f>
+        <v>-2.1276595744680871E-2</v>
+      </c>
+      <c r="L14" s="6">
         <f t="shared" si="3"/>
         <v>0.79</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="6">
+        <f>(L11-L14)/L11</f>
+        <v>-0.97499999999999998</v>
+      </c>
+      <c r="N14" s="1">
         <v>0.67</v>
       </c>
-      <c r="M14" s="1">
+      <c r="O14" s="1">
         <v>0.69</v>
       </c>
-      <c r="N14" s="1">
+      <c r="P14" s="1">
         <v>-270</v>
       </c>
-      <c r="O14" s="1">
+      <c r="Q14" s="1">
         <v>-370</v>
       </c>
-      <c r="P14" s="1">
+      <c r="R14" s="1">
         <v>-240</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>120</v>
       </c>
@@ -1581,26 +1691,32 @@
         <v>0.40833333333333333</v>
       </c>
       <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15" s="6">
         <f t="shared" si="3"/>
         <v>0.34166666666666667</v>
       </c>
-      <c r="L15" s="1">
+      <c r="M15" s="6">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
         <v>0.77</v>
       </c>
-      <c r="M15" s="1">
-        <v>1</v>
-      </c>
-      <c r="N15" s="1">
+      <c r="O15" s="1">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1">
         <v>-100</v>
       </c>
-      <c r="O15" s="1">
+      <c r="Q15" s="1">
         <v>-130</v>
       </c>
-      <c r="P15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>120</v>
       </c>
@@ -1635,26 +1751,34 @@
         <v>0.38333333333333336</v>
       </c>
       <c r="K16" s="6">
+        <f>(J15-J16)/J15</f>
+        <v>6.122448979591829E-2</v>
+      </c>
+      <c r="L16" s="6">
         <f t="shared" si="3"/>
         <v>0.35833333333333334</v>
       </c>
-      <c r="L16" s="1">
+      <c r="M16" s="6">
+        <f>(L15-L16)/L15</f>
+        <v>-4.8780487804878037E-2</v>
+      </c>
+      <c r="N16" s="1">
         <v>0.8</v>
       </c>
-      <c r="M16" s="1">
-        <v>1</v>
-      </c>
-      <c r="N16" s="1">
+      <c r="O16" s="1">
+        <v>1</v>
+      </c>
+      <c r="P16" s="1">
         <v>-75</v>
       </c>
-      <c r="O16" s="1">
+      <c r="Q16" s="1">
         <v>-85</v>
       </c>
-      <c r="P16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>120</v>
       </c>
@@ -1689,26 +1813,34 @@
         <v>0.375</v>
       </c>
       <c r="K17" s="6">
+        <f>(J15-J17)/J15</f>
+        <v>8.1632653061224469E-2</v>
+      </c>
+      <c r="L17" s="6">
         <f t="shared" si="3"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M17" s="6">
+        <f>(L15-L17)/L15</f>
+        <v>0.14634146341463411</v>
+      </c>
+      <c r="N17" s="1">
         <v>0.6</v>
       </c>
-      <c r="M17" s="1">
-        <v>1</v>
-      </c>
-      <c r="N17" s="1">
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
+      <c r="P17" s="1">
         <v>-185</v>
       </c>
-      <c r="O17" s="1">
+      <c r="Q17" s="1">
         <v>-230</v>
       </c>
-      <c r="P17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>40</v>
       </c>
@@ -1743,26 +1875,34 @@
         <v>0.9375</v>
       </c>
       <c r="K18" s="6">
+        <f>(J2-J18)/J2</f>
+        <v>0.10714285714285718</v>
+      </c>
+      <c r="L18" s="6">
         <f>(E18-H18)/A18</f>
         <v>1.2375</v>
       </c>
-      <c r="L18" s="1">
+      <c r="M18" s="6">
+        <f>(L2-L18)/L2</f>
+        <v>-0.33783783783783783</v>
+      </c>
+      <c r="N18" s="1">
         <v>0.5</v>
       </c>
-      <c r="M18" s="1">
+      <c r="O18" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="N18" s="1">
+      <c r="P18" s="1">
         <v>-220</v>
       </c>
-      <c r="O18" s="1">
+      <c r="Q18" s="1">
         <v>-235</v>
       </c>
-      <c r="P18" s="1">
+      <c r="R18" s="1">
         <v>-225</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>40</v>
       </c>
@@ -1797,26 +1937,34 @@
         <v>1.05</v>
       </c>
       <c r="K19" s="6">
+        <f>(J2-J19)/J2</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="6">
         <f>(E19-H19)/A19</f>
         <v>1.125</v>
       </c>
-      <c r="L19" s="9">
+      <c r="M19" s="6">
+        <f>(L2-L19)/L2</f>
+        <v>-0.21621621621621614</v>
+      </c>
+      <c r="N19" s="9">
         <v>0.6</v>
       </c>
-      <c r="M19" s="9">
+      <c r="O19" s="9">
         <v>0.72</v>
       </c>
-      <c r="N19" s="9">
+      <c r="P19" s="9">
         <v>-175</v>
       </c>
-      <c r="O19" s="9">
+      <c r="Q19" s="9">
         <v>-190</v>
       </c>
-      <c r="P19" s="9">
+      <c r="R19" s="9">
         <v>-120</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>40</v>
       </c>
@@ -1851,26 +1999,34 @@
         <v>1.125</v>
       </c>
       <c r="K20" s="6">
+        <f>(J2-J20)/J2</f>
+        <v>-7.1428571428571383E-2</v>
+      </c>
+      <c r="L20" s="6">
         <f>(E20-H20)/A20</f>
         <v>1.2</v>
       </c>
-      <c r="L20" s="9">
+      <c r="M20" s="6">
+        <f>(L2-L20)/L2</f>
+        <v>-0.2972972972972972</v>
+      </c>
+      <c r="N20" s="9">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M20" s="9">
+      <c r="O20" s="9">
         <v>0.6</v>
       </c>
-      <c r="N20" s="9">
+      <c r="P20" s="9">
         <v>-230</v>
       </c>
-      <c r="O20" s="9">
+      <c r="Q20" s="9">
         <v>-240</v>
       </c>
-      <c r="P20" s="9">
+      <c r="R20" s="9">
         <v>-220</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
         <v>60</v>
       </c>
@@ -1904,27 +2060,29 @@
         <f t="shared" ref="J21:J31" si="4">(D21-G21)/A21</f>
         <v>0.67500000000000004</v>
       </c>
-      <c r="K21" s="6">
-        <f t="shared" ref="K21:K31" si="5">(E21-H21)/A21</f>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6">
+        <f t="shared" ref="L21:L31" si="5">(E21-H21)/A21</f>
         <v>1.0083333333333333</v>
       </c>
-      <c r="L21" s="1">
+      <c r="M21" s="6"/>
+      <c r="N21" s="1">
         <v>0.62</v>
       </c>
-      <c r="M21" s="1">
+      <c r="O21" s="1">
         <v>0.8</v>
       </c>
-      <c r="N21" s="1">
+      <c r="P21" s="1">
         <v>-155</v>
       </c>
-      <c r="O21" s="1">
+      <c r="Q21" s="1">
         <v>-175</v>
       </c>
-      <c r="P21" s="1">
+      <c r="R21" s="1">
         <v>-90</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
         <v>60</v>
       </c>
@@ -1958,27 +2116,29 @@
         <f>(D22-G22)/A22</f>
         <v>0.6166666666666667</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="6"/>
+      <c r="L22" s="6">
         <f>(E22-H22)/A22</f>
         <v>0.51666666666666672</v>
       </c>
-      <c r="L22" s="9">
+      <c r="M22" s="6"/>
+      <c r="N22" s="9">
         <v>0.5</v>
       </c>
-      <c r="M22" s="9">
+      <c r="O22" s="9">
         <v>0.74</v>
       </c>
-      <c r="N22" s="9">
+      <c r="P22" s="9">
         <v>-220</v>
       </c>
-      <c r="O22" s="9">
+      <c r="Q22" s="9">
         <v>-225</v>
       </c>
-      <c r="P22" s="9">
+      <c r="R22" s="9">
         <v>-75</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>60</v>
       </c>
@@ -2012,27 +2172,29 @@
         <f>(D23-G23)/A23</f>
         <v>0.73333333333333328</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="6"/>
+      <c r="L23" s="6">
         <f>(E23-H23)/A23</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="L23" s="9">
+      <c r="M23" s="6"/>
+      <c r="N23" s="9">
         <v>0.68</v>
       </c>
-      <c r="M23" s="9">
+      <c r="O23" s="9">
         <v>0.78</v>
       </c>
-      <c r="N23" s="9">
+      <c r="P23" s="9">
         <v>-130</v>
       </c>
-      <c r="O23" s="9">
+      <c r="Q23" s="9">
         <v>-260</v>
       </c>
-      <c r="P23" s="9">
+      <c r="R23" s="9">
         <v>-70</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>80</v>
       </c>
@@ -2067,26 +2229,34 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="K24" s="6">
+        <f>(J7-J24)/J7</f>
+        <v>8.3333333333333232E-2</v>
+      </c>
+      <c r="L24" s="6">
         <f>(E24-H24)/A24</f>
         <v>0.38750000000000001</v>
       </c>
-      <c r="L24" s="9">
+      <c r="M24" s="6">
+        <f>(L7-L24)/L7</f>
+        <v>0.11428571428571425</v>
+      </c>
+      <c r="N24" s="9">
         <v>0.62</v>
       </c>
-      <c r="M24" s="9">
-        <v>1</v>
-      </c>
-      <c r="N24" s="9">
+      <c r="O24" s="9">
+        <v>1</v>
+      </c>
+      <c r="P24" s="9">
         <v>-160</v>
       </c>
-      <c r="O24" s="9">
+      <c r="Q24" s="9">
         <v>-230</v>
       </c>
-      <c r="P24" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>80</v>
       </c>
@@ -2121,26 +2291,34 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="K25" s="6">
+        <f>(J7-J25)/J7</f>
+        <v>0.12499999999999993</v>
+      </c>
+      <c r="L25" s="6">
         <f>(E25-H25)/A25</f>
         <v>0.35</v>
       </c>
-      <c r="L25" s="9">
+      <c r="M25" s="6">
+        <f>(L7-L25)/L7</f>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="N25" s="9">
         <v>0.46</v>
       </c>
-      <c r="M25" s="9">
+      <c r="O25" s="9">
         <v>0.92</v>
       </c>
-      <c r="N25" s="9">
+      <c r="P25" s="9">
         <v>-255</v>
       </c>
-      <c r="O25" s="9">
+      <c r="Q25" s="9">
         <v>-300</v>
       </c>
-      <c r="P25" s="9">
+      <c r="R25" s="9">
         <v>-20</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>100</v>
       </c>
@@ -2175,26 +2353,34 @@
         <v>0.46</v>
       </c>
       <c r="K26" s="6">
+        <f>(J11-J26)/J11</f>
+        <v>2.1276595744680753E-2</v>
+      </c>
+      <c r="L26" s="6">
         <f t="shared" si="5"/>
         <v>0.66</v>
       </c>
-      <c r="L26" s="1">
+      <c r="M26" s="6">
+        <f>(L11-L26)/L11</f>
+        <v>-0.65</v>
+      </c>
+      <c r="N26" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M26" s="1">
-        <v>1</v>
-      </c>
-      <c r="N26" s="1">
+      <c r="O26" s="1">
+        <v>1</v>
+      </c>
+      <c r="P26" s="1">
         <v>-150</v>
       </c>
-      <c r="O26" s="1">
+      <c r="Q26" s="1">
         <v>-170</v>
       </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
         <v>100</v>
       </c>
@@ -2229,26 +2415,34 @@
         <v>0.39</v>
       </c>
       <c r="K27" s="6">
+        <f>(J11-J27)/J11</f>
+        <v>0.17021276595744672</v>
+      </c>
+      <c r="L27" s="6">
         <f>(E27-H27)/A27</f>
         <v>0.27</v>
       </c>
-      <c r="L27" s="9">
+      <c r="M27" s="6">
+        <f>(L11-L27)/L11</f>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="N27" s="9">
         <v>0.48</v>
       </c>
-      <c r="M27" s="9">
-        <v>1</v>
-      </c>
-      <c r="N27" s="9">
+      <c r="O27" s="9">
+        <v>1</v>
+      </c>
+      <c r="P27" s="9">
         <v>-220</v>
       </c>
-      <c r="O27" s="9">
+      <c r="Q27" s="9">
         <v>-250</v>
       </c>
-      <c r="P27" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R27" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9">
         <v>100</v>
       </c>
@@ -2283,26 +2477,34 @@
         <v>0.4</v>
       </c>
       <c r="K28" s="6">
+        <f>(J11-J28)/J11</f>
+        <v>0.14893617021276587</v>
+      </c>
+      <c r="L28" s="6">
         <f>(E28-H28)/A28</f>
         <v>0.26</v>
       </c>
-      <c r="L28" s="9">
+      <c r="M28" s="6">
+        <f>(L11-L28)/L11</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="N28" s="9">
         <v>0.6</v>
       </c>
-      <c r="M28" s="9">
-        <v>1</v>
-      </c>
-      <c r="N28" s="9">
+      <c r="O28" s="9">
+        <v>1</v>
+      </c>
+      <c r="P28" s="9">
         <v>-150</v>
       </c>
-      <c r="O28" s="9">
+      <c r="Q28" s="9">
         <v>-210</v>
       </c>
-      <c r="P28" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>120</v>
       </c>
@@ -2337,26 +2539,34 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="K29" s="6">
+        <f>(J15-J29)/J15</f>
+        <v>-2.0408163265306187E-2</v>
+      </c>
+      <c r="L29" s="6">
         <f t="shared" si="5"/>
         <v>0.46666666666666667</v>
       </c>
-      <c r="L29" s="1">
+      <c r="M29" s="6">
+        <f>(L15-L29)/L15</f>
+        <v>-0.36585365853658536</v>
+      </c>
+      <c r="N29" s="1">
         <v>0.6</v>
       </c>
-      <c r="M29" s="1">
-        <v>1</v>
-      </c>
-      <c r="N29" s="1">
+      <c r="O29" s="1">
+        <v>1</v>
+      </c>
+      <c r="P29" s="1">
         <v>215</v>
       </c>
-      <c r="O29" s="1">
+      <c r="Q29" s="1">
         <v>-230</v>
       </c>
-      <c r="P29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>120</v>
       </c>
@@ -2391,26 +2601,34 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="K30" s="6">
+        <f>(J15-J30)/J15</f>
+        <v>0.18367346938775514</v>
+      </c>
+      <c r="L30" s="6">
         <f t="shared" si="5"/>
         <v>0.20833333333333334</v>
       </c>
-      <c r="L30" s="9">
+      <c r="M30" s="6">
+        <f>(L15-L30)/L15</f>
+        <v>0.3902439024390244</v>
+      </c>
+      <c r="N30" s="9">
         <v>0.54</v>
       </c>
-      <c r="M30" s="9">
-        <v>1</v>
-      </c>
-      <c r="N30" s="9">
+      <c r="O30" s="9">
+        <v>1</v>
+      </c>
+      <c r="P30" s="9">
         <v>-215</v>
       </c>
-      <c r="O30" s="9">
+      <c r="Q30" s="9">
         <v>-230</v>
       </c>
-      <c r="P30" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R30" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>120</v>
       </c>
@@ -2445,22 +2663,30 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="K31" s="6">
+        <f>(J15-J31)/J15</f>
+        <v>0.20408163265306117</v>
+      </c>
+      <c r="L31" s="6">
         <f t="shared" si="5"/>
         <v>0.23333333333333334</v>
       </c>
-      <c r="L31" s="9">
+      <c r="M31" s="6">
+        <f>(L15-L31)/L15</f>
+        <v>0.31707317073170732</v>
+      </c>
+      <c r="N31" s="9">
         <v>0.52</v>
       </c>
-      <c r="M31" s="9">
-        <v>1</v>
-      </c>
-      <c r="N31" s="9">
+      <c r="O31" s="9">
+        <v>1</v>
+      </c>
+      <c r="P31" s="9">
         <v>-200</v>
       </c>
-      <c r="O31" s="9">
+      <c r="Q31" s="9">
         <v>-250</v>
       </c>
-      <c r="P31" s="9">
+      <c r="R31" s="9">
         <v>0</v>
       </c>
     </row>

--- a/data/observation_alpha_beta.xlsx
+++ b/data/observation_alpha_beta.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20416"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phd\php_pulsating_heat_pipe\Krp_Analysis\Advanced_PulseHeatPipe_krp\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3895D7-EEAB-4C6E-B736-5D856B0CDE7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18200" windowHeight="8510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="demo" sheetId="1" r:id="rId1"/>
-    <sheet name="final" sheetId="2" r:id="rId2"/>
+    <sheet r:id="rId1" sheetId="1" name="demo"/>
+    <sheet r:id="rId2" sheetId="2" name="final"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">demo!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">demo!$A$1:$R$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">final!$A$1:$Q$36</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -87,13 +81,13 @@
     <t>Change_in_TR1[%]</t>
   </si>
   <si>
-    <t>Change_in_TR2[%]</t>
+    <t>Change_in_TR2 [%]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
@@ -113,7 +107,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFff0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -127,12 +121,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFffffff"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFff0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -326,7 +320,7 @@
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -370,7 +364,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -389,16 +383,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </left>
       <right style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </right>
       <top style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -414,197 +408,196 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="61">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="11" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="14" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="15" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="16" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="17" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="18" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="19" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -615,10 +608,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -656,71 +649,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -748,7 +741,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -771,11 +764,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -784,13 +777,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -800,7 +793,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -809,7 +802,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -818,7 +811,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -826,10 +819,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -894,28 +887,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="9" style="49" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" style="50" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" style="50" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.54296875" style="51" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="49" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="49" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="49" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="49" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="49" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="50" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="50" width="10.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="50" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="50" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="51" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="49" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="49" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="49" width="11.862142857142858" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="39.5" customFormat="1" s="1">
       <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
@@ -971,7 +970,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A2" s="12">
         <v>40</v>
       </c>
@@ -988,8 +987,7 @@
         <v>352</v>
       </c>
       <c r="F2" s="12">
-        <f t="shared" ref="F2:F31" si="0">(E2-D2)</f>
-        <v>4</v>
+        <f>(E2-D2)</f>
       </c>
       <c r="G2" s="12">
         <v>306</v>
@@ -998,19 +996,16 @@
         <v>315</v>
       </c>
       <c r="I2" s="12">
-        <f t="shared" ref="I2:I31" si="1">(H2-G2)</f>
-        <v>9</v>
+        <f>(H2-G2)</f>
       </c>
       <c r="J2" s="14">
-        <f t="shared" ref="J2:J31" si="2">(D2-G2)/A2</f>
-        <v>1.05</v>
+        <f>(D2-G2)/A2</f>
       </c>
       <c r="K2" s="56">
         <v>0</v>
       </c>
       <c r="L2" s="14">
         <f>(E2-H2)/A2</f>
-        <v>0.92500000000000004</v>
       </c>
       <c r="M2" s="56">
         <v>0</v>
@@ -1031,7 +1026,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A3" s="12">
         <v>40</v>
       </c>
@@ -1048,8 +1043,7 @@
         <v>357</v>
       </c>
       <c r="F3" s="12">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>(E3-D3)</f>
       </c>
       <c r="G3" s="12">
         <v>304</v>
@@ -1058,24 +1052,19 @@
         <v>305</v>
       </c>
       <c r="I3" s="13">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>(H3-G3)</f>
       </c>
       <c r="J3" s="14">
-        <f t="shared" si="2"/>
-        <v>1.125</v>
+        <f>(D3-G3)/A3</f>
       </c>
       <c r="K3" s="14">
         <f>(J2-J3)/J2</f>
-        <v>-7.1428571428571383E-2</v>
       </c>
       <c r="L3" s="14">
         <f>(E3-H3)/A3</f>
-        <v>1.3</v>
       </c>
       <c r="M3" s="14">
         <f>(L2-L3)/L2</f>
-        <v>-0.40540540540540537</v>
       </c>
       <c r="N3" s="15">
         <v>0.7</v>
@@ -1093,7 +1082,7 @@
         <v>-0.85</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A4" s="12">
         <v>40</v>
       </c>
@@ -1110,8 +1099,7 @@
         <v>358.5</v>
       </c>
       <c r="F4" s="15">
-        <f t="shared" si="0"/>
-        <v>9.5</v>
+        <f>(E4-D4)</f>
       </c>
       <c r="G4" s="12">
         <v>304</v>
@@ -1120,24 +1108,19 @@
         <v>306</v>
       </c>
       <c r="I4" s="13">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>(H4-G4)</f>
       </c>
       <c r="J4" s="14">
-        <f t="shared" si="2"/>
-        <v>1.125</v>
+        <f>(D4-G4)/A4</f>
       </c>
       <c r="K4" s="14">
         <f>(J2-J4)/J2</f>
-        <v>-7.1428571428571383E-2</v>
       </c>
       <c r="L4" s="14">
         <f>(E4-H4)/A4</f>
-        <v>1.3125</v>
       </c>
       <c r="M4" s="14">
         <f>(L2-L4)/L2</f>
-        <v>-0.41891891891891886</v>
       </c>
       <c r="N4" s="15">
         <v>0.7</v>
@@ -1155,7 +1138,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A5" s="12">
         <v>60</v>
       </c>
@@ -1172,8 +1155,7 @@
         <v>355</v>
       </c>
       <c r="F5" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>(E5-D5)</f>
       </c>
       <c r="G5" s="12">
         <v>303</v>
@@ -1182,17 +1164,14 @@
         <v>319</v>
       </c>
       <c r="I5" s="13">
-        <f t="shared" si="1"/>
-        <v>16</v>
+        <f>(H5-G5)</f>
       </c>
       <c r="J5" s="14">
-        <f t="shared" si="2"/>
-        <v>0.78333333333333333</v>
+        <f>(D5-G5)/A5</f>
       </c>
       <c r="K5" s="14"/>
       <c r="L5" s="14">
-        <f t="shared" ref="L5:L17" si="3">(E6-H6)/A6</f>
-        <v>0.6333333333333333</v>
+        <f>(E6-H6)/A6</f>
       </c>
       <c r="M5" s="14"/>
       <c r="N5" s="15">
@@ -1211,7 +1190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A6" s="12">
         <v>60</v>
       </c>
@@ -1228,8 +1207,7 @@
         <v>359</v>
       </c>
       <c r="F6" s="12">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>(E6-D6)</f>
       </c>
       <c r="G6" s="12">
         <v>305</v>
@@ -1238,17 +1216,14 @@
         <v>321</v>
       </c>
       <c r="I6" s="13">
-        <f t="shared" si="1"/>
-        <v>16</v>
+        <f>(H6-G6)</f>
       </c>
       <c r="J6" s="14">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
+        <f>(D6-G6)/A6</f>
       </c>
       <c r="K6" s="14"/>
       <c r="L6" s="14">
-        <f t="shared" si="3"/>
-        <v>0.4375</v>
+        <f>(E7-H7)/A7</f>
       </c>
       <c r="M6" s="14"/>
       <c r="N6" s="15">
@@ -1267,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A7" s="12">
         <v>80</v>
       </c>
@@ -1284,8 +1259,7 @@
         <v>355</v>
       </c>
       <c r="F7" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>(E7-D7)</f>
       </c>
       <c r="G7" s="12">
         <v>302</v>
@@ -1294,19 +1268,16 @@
         <v>320</v>
       </c>
       <c r="I7" s="13">
-        <f t="shared" si="1"/>
-        <v>18</v>
+        <f>(H7-G7)</f>
       </c>
       <c r="J7" s="14">
-        <f t="shared" si="2"/>
-        <v>0.6</v>
+        <f>(D7-G7)/A7</f>
       </c>
       <c r="K7" s="15">
         <v>0</v>
       </c>
       <c r="L7" s="14">
-        <f t="shared" si="3"/>
-        <v>0.5625</v>
+        <f>(E8-H8)/A8</f>
       </c>
       <c r="M7" s="15">
         <v>0</v>
@@ -1327,7 +1298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A8" s="12">
         <v>80</v>
       </c>
@@ -1344,8 +1315,7 @@
         <v>358</v>
       </c>
       <c r="F8" s="12">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>(E8-D8)</f>
       </c>
       <c r="G8" s="12">
         <v>305</v>
@@ -1354,24 +1324,19 @@
         <v>313</v>
       </c>
       <c r="I8" s="13">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f>(H8-G8)</f>
       </c>
       <c r="J8" s="14">
-        <f t="shared" si="2"/>
-        <v>0.625</v>
+        <f>(D8-G8)/A8</f>
       </c>
       <c r="K8" s="14">
         <f>(J7-J8)/J7</f>
-        <v>-4.1666666666666706E-2</v>
       </c>
       <c r="L8" s="14">
-        <f t="shared" si="3"/>
-        <v>0.45</v>
+        <f>(E9-H9)/A9</f>
       </c>
       <c r="M8" s="14">
         <f>(L7-L8)/L7</f>
-        <v>0.19999999999999998</v>
       </c>
       <c r="N8" s="15">
         <v>0.8</v>
@@ -1389,7 +1354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A9" s="12">
         <v>80</v>
       </c>
@@ -1406,8 +1371,7 @@
         <v>358</v>
       </c>
       <c r="F9" s="12">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>(E9-D9)</f>
       </c>
       <c r="G9" s="12">
         <v>303</v>
@@ -1416,24 +1380,19 @@
         <v>322</v>
       </c>
       <c r="I9" s="13">
-        <f t="shared" si="1"/>
-        <v>19</v>
+        <f>(H9-G9)</f>
       </c>
       <c r="J9" s="14">
-        <f t="shared" si="2"/>
-        <v>0.5625</v>
+        <f>(D9-G9)/A9</f>
       </c>
       <c r="K9" s="14">
         <f>(J7-J9)/J7</f>
-        <v>6.2499999999999965E-2</v>
       </c>
       <c r="L9" s="14">
-        <f t="shared" si="3"/>
-        <v>0.75624999999999998</v>
+        <f>(E10-H10)/A10</f>
       </c>
       <c r="M9" s="14">
         <f>(L7-L9)/L7</f>
-        <v>-0.34444444444444439</v>
       </c>
       <c r="N9" s="15">
         <v>0.65</v>
@@ -1451,7 +1410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A10" s="57">
         <v>80</v>
       </c>
@@ -1468,8 +1427,7 @@
         <v>364</v>
       </c>
       <c r="F10" s="57">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>(E10-D10)</f>
       </c>
       <c r="G10" s="57">
         <v>303</v>
@@ -1478,24 +1436,19 @@
         <v>303.5</v>
       </c>
       <c r="I10" s="59">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>(H10-G10)</f>
       </c>
       <c r="J10" s="60">
-        <f t="shared" si="2"/>
-        <v>0.71250000000000002</v>
+        <f>(D10-G10)/A10</f>
       </c>
       <c r="K10" s="60">
         <f>(J7-J10)/J7</f>
-        <v>-0.18750000000000008</v>
       </c>
       <c r="L10" s="60">
-        <f t="shared" si="3"/>
-        <v>0.4</v>
+        <f>(E11-H11)/A11</f>
       </c>
       <c r="M10" s="60">
         <f>(L7-L10)/L7</f>
-        <v>0.28888888888888886</v>
       </c>
       <c r="N10" s="58">
         <v>0.7</v>
@@ -1513,7 +1466,7 @@
         <v>-140</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A11" s="12">
         <v>100</v>
       </c>
@@ -1530,8 +1483,7 @@
         <v>355</v>
       </c>
       <c r="F11" s="12">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>(E11-D11)</f>
       </c>
       <c r="G11" s="12">
         <v>305</v>
@@ -1540,19 +1492,16 @@
         <v>315</v>
       </c>
       <c r="I11" s="13">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f>(H11-G11)</f>
       </c>
       <c r="J11" s="14">
-        <f t="shared" si="2"/>
-        <v>0.47</v>
+        <f>(D11-G11)/A11</f>
       </c>
       <c r="K11" s="14">
         <v>0</v>
       </c>
       <c r="L11" s="14">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
+        <f>(E12-H12)/A12</f>
       </c>
       <c r="M11" s="14">
         <v>0</v>
@@ -1573,7 +1522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A12" s="12">
         <v>100</v>
       </c>
@@ -1590,8 +1539,7 @@
         <v>358</v>
       </c>
       <c r="F12" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>(E12-D12)</f>
       </c>
       <c r="G12" s="12">
         <v>306</v>
@@ -1600,24 +1548,19 @@
         <v>321</v>
       </c>
       <c r="I12" s="13">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f>(H12-G12)</f>
       </c>
       <c r="J12" s="14">
-        <f t="shared" si="2"/>
-        <v>0.47</v>
+        <f>(D12-G12)/A12</f>
       </c>
       <c r="K12" s="14">
         <f>(J11-J12)/J11</f>
-        <v>0</v>
       </c>
       <c r="L12" s="14">
-        <f t="shared" si="3"/>
-        <v>0.32</v>
+        <f>(E13-H13)/A13</f>
       </c>
       <c r="M12" s="14">
         <f>(L11-L12)/L11</f>
-        <v>0.13513513513513511</v>
       </c>
       <c r="N12" s="15">
         <v>0.75</v>
@@ -1635,7 +1578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A13" s="12">
         <v>100</v>
       </c>
@@ -1652,8 +1595,7 @@
         <v>357</v>
       </c>
       <c r="F13" s="12">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <f>(E13-D13)</f>
       </c>
       <c r="G13" s="12">
         <v>306</v>
@@ -1662,24 +1604,19 @@
         <v>325</v>
       </c>
       <c r="I13" s="13">
-        <f t="shared" si="1"/>
-        <v>19</v>
+        <f>(H13-G13)</f>
       </c>
       <c r="J13" s="14">
-        <f t="shared" si="2"/>
-        <v>0.4</v>
+        <f>(D13-G13)/A13</f>
       </c>
       <c r="K13" s="14">
         <f>(J11-J13)/J11</f>
-        <v>0.14893617021276587</v>
       </c>
       <c r="L13" s="14">
-        <f t="shared" si="3"/>
-        <v>0.79</v>
+        <f>(E14-H14)/A14</f>
       </c>
       <c r="M13" s="14">
         <f>(L11-L13)/L11</f>
-        <v>-1.1351351351351353</v>
       </c>
       <c r="N13" s="15">
         <v>0.45</v>
@@ -1697,7 +1634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A14" s="12">
         <v>100</v>
       </c>
@@ -1714,8 +1651,7 @@
         <v>385</v>
       </c>
       <c r="F14" s="12">
-        <f t="shared" si="0"/>
-        <v>35</v>
+        <f>(E14-D14)</f>
       </c>
       <c r="G14" s="12">
         <v>302</v>
@@ -1724,24 +1660,19 @@
         <v>306</v>
       </c>
       <c r="I14" s="13">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f>(H14-G14)</f>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="2"/>
-        <v>0.48</v>
+        <f>(D14-G14)/A14</f>
       </c>
       <c r="K14" s="14">
         <f>(J11-J14)/J11</f>
-        <v>-2.1276595744680871E-2</v>
       </c>
       <c r="L14" s="14">
-        <f t="shared" si="3"/>
-        <v>0.34166666666666667</v>
+        <f>(E15-H15)/A15</f>
       </c>
       <c r="M14" s="14">
         <f>(L11-L14)/L11</f>
-        <v>7.6576576576576544E-2</v>
       </c>
       <c r="N14" s="15">
         <v>0.67</v>
@@ -1759,7 +1690,7 @@
         <v>-240</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A15" s="12">
         <v>120</v>
       </c>
@@ -1776,8 +1707,7 @@
         <v>356</v>
       </c>
       <c r="F15" s="12">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>(E15-D15)</f>
       </c>
       <c r="G15" s="12">
         <v>304</v>
@@ -1786,19 +1716,16 @@
         <v>315</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
-        <v>11</v>
+        <f>(H15-G15)</f>
       </c>
       <c r="J15" s="14">
-        <f t="shared" si="2"/>
-        <v>0.40833333333333333</v>
+        <f>(D15-G15)/A15</f>
       </c>
       <c r="K15" s="14">
         <v>0</v>
       </c>
       <c r="L15" s="14">
-        <f t="shared" si="3"/>
-        <v>0.35833333333333334</v>
+        <f>(E16-H16)/A16</f>
       </c>
       <c r="M15" s="14">
         <v>0</v>
@@ -1819,7 +1746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A16" s="12">
         <v>120</v>
       </c>
@@ -1836,8 +1763,7 @@
         <v>356</v>
       </c>
       <c r="F16" s="12">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>(E16-D16)</f>
       </c>
       <c r="G16" s="12">
         <v>307</v>
@@ -1846,24 +1772,19 @@
         <v>313</v>
       </c>
       <c r="I16" s="13">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <f>(H16-G16)</f>
       </c>
       <c r="J16" s="14">
-        <f t="shared" si="2"/>
-        <v>0.38333333333333336</v>
+        <f>(D16-G16)/A16</f>
       </c>
       <c r="K16" s="14">
         <f>(J15-J16)/J15</f>
-        <v>6.122448979591829E-2</v>
       </c>
       <c r="L16" s="14">
-        <f t="shared" si="3"/>
-        <v>0.29166666666666669</v>
+        <f>(E17-H17)/A17</f>
       </c>
       <c r="M16" s="14">
         <f>(L15-L16)/L15</f>
-        <v>0.18604651162790695</v>
       </c>
       <c r="N16" s="15">
         <v>0.8</v>
@@ -1881,7 +1802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A17" s="12">
         <v>120</v>
       </c>
@@ -1898,8 +1819,7 @@
         <v>358</v>
       </c>
       <c r="F17" s="12">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>(E17-D17)</f>
       </c>
       <c r="G17" s="12">
         <v>303</v>
@@ -1908,24 +1828,19 @@
         <v>323</v>
       </c>
       <c r="I17" s="13">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>(H17-G17)</f>
       </c>
       <c r="J17" s="14">
-        <f t="shared" si="2"/>
-        <v>0.375</v>
+        <f>(D17-G17)/A17</f>
       </c>
       <c r="K17" s="14">
         <f>(J15-J17)/J15</f>
-        <v>8.1632653061224469E-2</v>
       </c>
       <c r="L17" s="14">
-        <f t="shared" si="3"/>
-        <v>1.2375</v>
+        <f>(E18-H18)/A18</f>
       </c>
       <c r="M17" s="14">
         <f>(L15-L17)/L15</f>
-        <v>-2.4534883720930232</v>
       </c>
       <c r="N17" s="15">
         <v>0.6</v>
@@ -1943,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A18" s="12">
         <v>40</v>
       </c>
@@ -1960,8 +1875,7 @@
         <v>355</v>
       </c>
       <c r="F18" s="12">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f>(E18-D18)</f>
       </c>
       <c r="G18" s="15">
         <v>304.5</v>
@@ -1970,30 +1884,25 @@
         <v>305.5</v>
       </c>
       <c r="I18" s="13">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>(H18-G18)</f>
       </c>
       <c r="J18" s="14">
-        <f t="shared" si="2"/>
-        <v>0.9375</v>
+        <f>(D18-G18)/A18</f>
       </c>
       <c r="K18" s="14">
         <f>(J2-J18)/J2</f>
-        <v>0.10714285714285718</v>
       </c>
       <c r="L18" s="14">
-        <f t="shared" ref="L18:L31" si="4">(E18-H18)/A18</f>
-        <v>1.2375</v>
+        <f>(E18-H18)/A18</f>
       </c>
       <c r="M18" s="14">
         <f>(L2-L18)/L2</f>
-        <v>-0.33783783783783783</v>
       </c>
       <c r="N18" s="15">
         <v>0.5</v>
       </c>
       <c r="O18" s="15">
-        <v>0.57999999999999996</v>
+        <v>0.58</v>
       </c>
       <c r="P18" s="12">
         <v>-220</v>
@@ -2005,7 +1914,7 @@
         <v>-225</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A19" s="12">
         <v>40</v>
       </c>
@@ -2022,8 +1931,7 @@
         <v>352</v>
       </c>
       <c r="F19" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>(E19-D19)</f>
       </c>
       <c r="G19" s="12">
         <v>305</v>
@@ -2032,24 +1940,19 @@
         <v>307</v>
       </c>
       <c r="I19" s="13">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>(H19-G19)</f>
       </c>
       <c r="J19" s="14">
-        <f t="shared" si="2"/>
-        <v>1.05</v>
+        <f>(D19-G19)/A19</f>
       </c>
       <c r="K19" s="14">
         <f>(J2-J19)/J2</f>
-        <v>0</v>
       </c>
       <c r="L19" s="14">
-        <f t="shared" si="4"/>
-        <v>1.125</v>
+        <f>(E19-H19)/A19</f>
       </c>
       <c r="M19" s="14">
         <f>(L2-L19)/L2</f>
-        <v>-0.21621621621621614</v>
       </c>
       <c r="N19" s="15">
         <v>0.6</v>
@@ -2067,7 +1970,7 @@
         <v>-120</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A20" s="12">
         <v>40</v>
       </c>
@@ -2084,8 +1987,7 @@
         <v>354</v>
       </c>
       <c r="F20" s="12">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>(E20-D20)</f>
       </c>
       <c r="G20" s="12">
         <v>305</v>
@@ -2094,27 +1996,22 @@
         <v>306</v>
       </c>
       <c r="I20" s="13">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>(H20-G20)</f>
       </c>
       <c r="J20" s="14">
-        <f t="shared" si="2"/>
-        <v>1.125</v>
+        <f>(D20-G20)/A20</f>
       </c>
       <c r="K20" s="14">
         <f>(J2-J20)/J2</f>
-        <v>-7.1428571428571383E-2</v>
       </c>
       <c r="L20" s="14">
-        <f t="shared" si="4"/>
-        <v>1.2</v>
+        <f>(E20-H20)/A20</f>
       </c>
       <c r="M20" s="14">
         <f>(L2-L20)/L2</f>
-        <v>-0.2972972972972972</v>
       </c>
       <c r="N20" s="15">
-        <v>0.55000000000000004</v>
+        <v>0.55</v>
       </c>
       <c r="O20" s="15">
         <v>0.6</v>
@@ -2129,7 +2026,7 @@
         <v>-220</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A21" s="12">
         <v>60</v>
       </c>
@@ -2146,8 +2043,7 @@
         <v>368</v>
       </c>
       <c r="F21" s="12">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <f>(E21-D21)</f>
       </c>
       <c r="G21" s="15">
         <v>304.5</v>
@@ -2156,17 +2052,14 @@
         <v>307.5</v>
       </c>
       <c r="I21" s="13">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f>(H21-G21)</f>
       </c>
       <c r="J21" s="14">
-        <f t="shared" si="2"/>
-        <v>0.67500000000000004</v>
+        <f>(D21-G21)/A21</f>
       </c>
       <c r="K21" s="14"/>
       <c r="L21" s="14">
-        <f t="shared" si="4"/>
-        <v>1.0083333333333333</v>
+        <f>(E21-H21)/A21</f>
       </c>
       <c r="M21" s="14"/>
       <c r="N21" s="15">
@@ -2185,7 +2078,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A22" s="12">
         <v>60</v>
       </c>
@@ -2202,8 +2095,7 @@
         <v>351</v>
       </c>
       <c r="F22" s="12">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>(E22-D22)</f>
       </c>
       <c r="G22" s="12">
         <v>305</v>
@@ -2212,17 +2104,14 @@
         <v>320</v>
       </c>
       <c r="I22" s="13">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f>(H22-G22)</f>
       </c>
       <c r="J22" s="14">
-        <f t="shared" si="2"/>
-        <v>0.6166666666666667</v>
+        <f>(D22-G22)/A22</f>
       </c>
       <c r="K22" s="14"/>
       <c r="L22" s="14">
-        <f t="shared" si="4"/>
-        <v>0.51666666666666672</v>
+        <f>(E22-H22)/A22</f>
       </c>
       <c r="M22" s="14"/>
       <c r="N22" s="15">
@@ -2241,7 +2130,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A23" s="12">
         <v>60</v>
       </c>
@@ -2258,8 +2147,7 @@
         <v>354</v>
       </c>
       <c r="F23" s="12">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>(E23-D23)</f>
       </c>
       <c r="G23" s="12">
         <v>307</v>
@@ -2268,17 +2156,14 @@
         <v>319</v>
       </c>
       <c r="I23" s="13">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>(H23-G23)</f>
       </c>
       <c r="J23" s="14">
-        <f t="shared" si="2"/>
-        <v>0.73333333333333328</v>
+        <f>(D23-G23)/A23</f>
       </c>
       <c r="K23" s="14"/>
       <c r="L23" s="14">
-        <f t="shared" si="4"/>
-        <v>0.58333333333333337</v>
+        <f>(E23-H23)/A23</f>
       </c>
       <c r="M23" s="14"/>
       <c r="N23" s="15">
@@ -2297,7 +2182,7 @@
         <v>-70</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A24" s="12">
         <v>80</v>
       </c>
@@ -2314,8 +2199,7 @@
         <v>360</v>
       </c>
       <c r="F24" s="12">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>(E24-D24)</f>
       </c>
       <c r="G24" s="12">
         <v>304</v>
@@ -2324,24 +2208,19 @@
         <v>329</v>
       </c>
       <c r="I24" s="13">
-        <f t="shared" si="1"/>
-        <v>25</v>
+        <f>(H24-G24)</f>
       </c>
       <c r="J24" s="14">
-        <f t="shared" si="2"/>
-        <v>0.55000000000000004</v>
+        <f>(D24-G24)/A24</f>
       </c>
       <c r="K24" s="14">
         <f>(J7-J24)/J7</f>
-        <v>8.3333333333333232E-2</v>
       </c>
       <c r="L24" s="14">
-        <f t="shared" si="4"/>
-        <v>0.38750000000000001</v>
+        <f>(E24-H24)/A24</f>
       </c>
       <c r="M24" s="14">
         <f>(L7-L24)/L7</f>
-        <v>0.31111111111111112</v>
       </c>
       <c r="N24" s="15">
         <v>0.62</v>
@@ -2359,7 +2238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A25" s="12">
         <v>80</v>
       </c>
@@ -2376,8 +2255,7 @@
         <v>354</v>
       </c>
       <c r="F25" s="12">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>(E25-D25)</f>
       </c>
       <c r="G25" s="12">
         <v>304</v>
@@ -2386,24 +2264,19 @@
         <v>326</v>
       </c>
       <c r="I25" s="13">
-        <f t="shared" si="1"/>
-        <v>22</v>
+        <f>(H25-G25)</f>
       </c>
       <c r="J25" s="14">
-        <f t="shared" si="2"/>
-        <v>0.52500000000000002</v>
+        <f>(D25-G25)/A25</f>
       </c>
       <c r="K25" s="14">
         <f>(J7-J25)/J7</f>
-        <v>0.12499999999999993</v>
       </c>
       <c r="L25" s="14">
-        <f t="shared" si="4"/>
-        <v>0.35</v>
+        <f>(E25-H25)/A25</f>
       </c>
       <c r="M25" s="14">
         <f>(L7-L25)/L7</f>
-        <v>0.37777777777777782</v>
       </c>
       <c r="N25" s="15">
         <v>0.46</v>
@@ -2421,7 +2294,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A26" s="12">
         <v>100</v>
       </c>
@@ -2438,8 +2311,7 @@
         <v>374</v>
       </c>
       <c r="F26" s="12">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <f>(E26-D26)</f>
       </c>
       <c r="G26" s="12">
         <v>306</v>
@@ -2448,27 +2320,22 @@
         <v>308</v>
       </c>
       <c r="I26" s="13">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>(H26-G26)</f>
       </c>
       <c r="J26" s="14">
-        <f t="shared" si="2"/>
-        <v>0.46</v>
+        <f>(D26-G26)/A26</f>
       </c>
       <c r="K26" s="14">
         <f>(J11-J26)/J11</f>
-        <v>2.1276595744680753E-2</v>
       </c>
       <c r="L26" s="14">
-        <f t="shared" si="4"/>
-        <v>0.66</v>
+        <f>(E26-H26)/A26</f>
       </c>
       <c r="M26" s="14">
         <f>(L11-L26)/L11</f>
-        <v>-0.78378378378378388</v>
       </c>
       <c r="N26" s="15">
-        <v>0.55000000000000004</v>
+        <v>0.55</v>
       </c>
       <c r="O26" s="12">
         <v>1</v>
@@ -2483,7 +2350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A27" s="12">
         <v>100</v>
       </c>
@@ -2500,8 +2367,7 @@
         <v>357</v>
       </c>
       <c r="F27" s="12">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>(E27-D27)</f>
       </c>
       <c r="G27" s="12">
         <v>302</v>
@@ -2510,24 +2376,19 @@
         <v>330</v>
       </c>
       <c r="I27" s="13">
-        <f t="shared" si="1"/>
-        <v>28</v>
+        <f>(H27-G27)</f>
       </c>
       <c r="J27" s="14">
-        <f t="shared" si="2"/>
-        <v>0.39</v>
+        <f>(D27-G27)/A27</f>
       </c>
       <c r="K27" s="14">
         <f>(J11-J27)/J11</f>
-        <v>0.17021276595744672</v>
       </c>
       <c r="L27" s="14">
-        <f t="shared" si="4"/>
-        <v>0.27</v>
+        <f>(E27-H27)/A27</f>
       </c>
       <c r="M27" s="14">
         <f>(L11-L27)/L11</f>
-        <v>0.27027027027027023</v>
       </c>
       <c r="N27" s="15">
         <v>0.48</v>
@@ -2545,7 +2406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A28" s="12">
         <v>100</v>
       </c>
@@ -2562,8 +2423,7 @@
         <v>355</v>
       </c>
       <c r="F28" s="12">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>(E28-D28)</f>
       </c>
       <c r="G28" s="12">
         <v>306</v>
@@ -2572,24 +2432,19 @@
         <v>329</v>
       </c>
       <c r="I28" s="13">
-        <f t="shared" si="1"/>
-        <v>23</v>
+        <f>(H28-G28)</f>
       </c>
       <c r="J28" s="14">
-        <f t="shared" si="2"/>
-        <v>0.4</v>
+        <f>(D28-G28)/A28</f>
       </c>
       <c r="K28" s="14">
         <f>(J11-J28)/J11</f>
-        <v>0.14893617021276587</v>
       </c>
       <c r="L28" s="14">
-        <f t="shared" si="4"/>
-        <v>0.26</v>
+        <f>(E28-H28)/A28</f>
       </c>
       <c r="M28" s="14">
         <f>(L11-L28)/L11</f>
-        <v>0.29729729729729726</v>
       </c>
       <c r="N28" s="15">
         <v>0.6</v>
@@ -2607,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A29" s="12">
         <v>120</v>
       </c>
@@ -2624,8 +2479,7 @@
         <v>370</v>
       </c>
       <c r="F29" s="12">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>(E29-D29)</f>
       </c>
       <c r="G29" s="12">
         <v>304</v>
@@ -2634,24 +2488,19 @@
         <v>314</v>
       </c>
       <c r="I29" s="13">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f>(H29-G29)</f>
       </c>
       <c r="J29" s="14">
-        <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <f>(D29-G29)/A29</f>
       </c>
       <c r="K29" s="14">
         <f>(J15-J29)/J15</f>
-        <v>-2.0408163265306187E-2</v>
       </c>
       <c r="L29" s="14">
-        <f t="shared" si="4"/>
-        <v>0.46666666666666667</v>
+        <f>(E29-H29)/A29</f>
       </c>
       <c r="M29" s="14">
         <f>(L15-L29)/L15</f>
-        <v>-0.30232558139534882</v>
       </c>
       <c r="N29" s="15">
         <v>0.6</v>
@@ -2669,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A30" s="12">
         <v>120</v>
       </c>
@@ -2686,8 +2535,7 @@
         <v>355</v>
       </c>
       <c r="F30" s="12">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f>(E30-D30)</f>
       </c>
       <c r="G30" s="12">
         <v>302</v>
@@ -2696,24 +2544,19 @@
         <v>330</v>
       </c>
       <c r="I30" s="13">
-        <f t="shared" si="1"/>
-        <v>28</v>
+        <f>(H30-G30)</f>
       </c>
       <c r="J30" s="14">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <f>(D30-G30)/A30</f>
       </c>
       <c r="K30" s="14">
         <f>(J15-J30)/J15</f>
-        <v>0.18367346938775514</v>
       </c>
       <c r="L30" s="14">
-        <f t="shared" si="4"/>
-        <v>0.20833333333333334</v>
+        <f>(E30-H30)/A30</f>
       </c>
       <c r="M30" s="14">
         <f>(L15-L30)/L15</f>
-        <v>0.41860465116279066</v>
       </c>
       <c r="N30" s="15">
         <v>0.54</v>
@@ -2731,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A31" s="12">
         <v>120</v>
       </c>
@@ -2748,8 +2591,7 @@
         <v>355</v>
       </c>
       <c r="F31" s="12">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>(E31-D31)</f>
       </c>
       <c r="G31" s="12">
         <v>304</v>
@@ -2758,24 +2600,19 @@
         <v>327</v>
       </c>
       <c r="I31" s="13">
-        <f t="shared" si="1"/>
-        <v>23</v>
+        <f>(H31-G31)</f>
       </c>
       <c r="J31" s="14">
-        <f t="shared" si="2"/>
-        <v>0.32500000000000001</v>
+        <f>(D31-G31)/A31</f>
       </c>
       <c r="K31" s="14">
         <f>(J15-J31)/J15</f>
-        <v>0.20408163265306117</v>
       </c>
       <c r="L31" s="14">
-        <f t="shared" si="4"/>
-        <v>0.23333333333333334</v>
+        <f>(E31-H31)/A31</f>
       </c>
       <c r="M31" s="14">
         <f>(L15-L31)/L15</f>
-        <v>0.34883720930232559</v>
       </c>
       <c r="N31" s="15">
         <v>0.52</v>
@@ -2794,32 +2631,38 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1" xr:uid="{BC3F519D-1E72-4C40-A9EB-D73907B1CA29}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:Q36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="9" style="49" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.54296875" style="51" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.453125" style="52" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="49" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="49" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="49" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="49" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="49" width="9.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="50" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="50" width="10.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="51" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="49" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="49" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="49" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="52" width="14.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="39.5" customFormat="1" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2870,7 +2713,7 @@
       </c>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A2" s="6">
         <v>40</v>
       </c>
@@ -2887,8 +2730,7 @@
         <v>352</v>
       </c>
       <c r="F2" s="7">
-        <f t="shared" ref="F2:F36" si="0">(E2-D2)</f>
-        <v>4</v>
+        <f>(E2-D2)</f>
       </c>
       <c r="G2" s="7">
         <v>306</v>
@@ -2897,16 +2739,13 @@
         <v>315</v>
       </c>
       <c r="I2" s="7">
-        <f t="shared" ref="I2:I36" si="1">(H2-G2)</f>
-        <v>9</v>
+        <f>(H2-G2)</f>
       </c>
       <c r="J2" s="8">
-        <f t="shared" ref="J2:J36" si="2">(D2-G2)/A2</f>
-        <v>1.05</v>
+        <f>(D2-G2)/A2</f>
       </c>
       <c r="K2" s="8">
-        <f t="shared" ref="K2:K36" si="3">(E2-H2)/A2</f>
-        <v>0.92500000000000004</v>
+        <f>(E2-H2)/A2</f>
       </c>
       <c r="L2" s="9">
         <v>0.62</v>
@@ -2925,7 +2764,7 @@
       </c>
       <c r="Q2" s="5"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A3" s="11">
         <v>40</v>
       </c>
@@ -2942,8 +2781,7 @@
         <v>357</v>
       </c>
       <c r="F3" s="12">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>(E3-D3)</f>
       </c>
       <c r="G3" s="12">
         <v>304</v>
@@ -2952,16 +2790,13 @@
         <v>305</v>
       </c>
       <c r="I3" s="13">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>(H3-G3)</f>
       </c>
       <c r="J3" s="14">
-        <f t="shared" si="2"/>
-        <v>1.125</v>
+        <f>(D3-G3)/A3</f>
       </c>
       <c r="K3" s="14">
-        <f t="shared" si="3"/>
-        <v>1.3</v>
+        <f>(E3-H3)/A3</f>
       </c>
       <c r="L3" s="15">
         <v>0.7</v>
@@ -2980,7 +2815,7 @@
       </c>
       <c r="Q3" s="5"/>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A4" s="11">
         <v>40</v>
       </c>
@@ -2997,8 +2832,7 @@
         <v>358.5</v>
       </c>
       <c r="F4" s="15">
-        <f t="shared" si="0"/>
-        <v>9.5</v>
+        <f>(E4-D4)</f>
       </c>
       <c r="G4" s="12">
         <v>304</v>
@@ -3007,16 +2841,13 @@
         <v>306</v>
       </c>
       <c r="I4" s="13">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>(H4-G4)</f>
       </c>
       <c r="J4" s="14">
-        <f t="shared" si="2"/>
-        <v>1.125</v>
+        <f>(D4-G4)/A4</f>
       </c>
       <c r="K4" s="14">
-        <f t="shared" si="3"/>
-        <v>1.3125</v>
+        <f>(E4-H4)/A4</f>
       </c>
       <c r="L4" s="15">
         <v>0.7</v>
@@ -3035,7 +2866,7 @@
       </c>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A5" s="18">
         <v>40</v>
       </c>
@@ -3048,22 +2879,18 @@
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
       <c r="F5" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(E5-D5)</f>
       </c>
       <c r="G5" s="20"/>
       <c r="H5" s="20"/>
       <c r="I5" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>(H5-G5)</f>
       </c>
       <c r="J5" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>(D5-G5)/A5</f>
       </c>
       <c r="K5" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>(E5-H5)/A5</f>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="19">
@@ -3076,7 +2903,7 @@
       </c>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A6" s="25">
         <v>60</v>
       </c>
@@ -3089,22 +2916,18 @@
       <c r="D6" s="27"/>
       <c r="E6" s="27"/>
       <c r="F6" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(E6-D6)</f>
       </c>
       <c r="G6" s="27"/>
       <c r="H6" s="27"/>
       <c r="I6" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>(H6-G6)</f>
       </c>
       <c r="J6" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>(D6-G6)/A6</f>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>(E6-H6)/A6</f>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="7">
@@ -3119,7 +2942,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A7" s="11">
         <v>60</v>
       </c>
@@ -3136,8 +2959,7 @@
         <v>355</v>
       </c>
       <c r="F7" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>(E7-D7)</f>
       </c>
       <c r="G7" s="12">
         <v>303</v>
@@ -3146,16 +2968,13 @@
         <v>319</v>
       </c>
       <c r="I7" s="13">
-        <f t="shared" si="1"/>
-        <v>16</v>
+        <f>(H7-G7)</f>
       </c>
       <c r="J7" s="14">
-        <f t="shared" si="2"/>
-        <v>0.78333333333333333</v>
+        <f>(D7-G7)/A7</f>
       </c>
       <c r="K7" s="14">
-        <f t="shared" si="3"/>
-        <v>0.6</v>
+        <f>(E7-H7)/A7</f>
       </c>
       <c r="L7" s="15">
         <v>0.65</v>
@@ -3174,7 +2993,7 @@
       </c>
       <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A8" s="11">
         <v>60</v>
       </c>
@@ -3191,8 +3010,7 @@
         <v>359</v>
       </c>
       <c r="F8" s="12">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>(E8-D8)</f>
       </c>
       <c r="G8" s="12">
         <v>305</v>
@@ -3201,16 +3019,13 @@
         <v>321</v>
       </c>
       <c r="I8" s="13">
-        <f t="shared" si="1"/>
-        <v>16</v>
+        <f>(H8-G8)</f>
       </c>
       <c r="J8" s="14">
-        <f t="shared" si="2"/>
-        <v>0.75</v>
+        <f>(D8-G8)/A8</f>
       </c>
       <c r="K8" s="14">
-        <f t="shared" si="3"/>
-        <v>0.6333333333333333</v>
+        <f>(E8-H8)/A8</f>
       </c>
       <c r="L8" s="15">
         <v>0.75</v>
@@ -3229,7 +3044,7 @@
       </c>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A9" s="18">
         <v>60</v>
       </c>
@@ -3242,22 +3057,18 @@
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(E9-D9)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="20"/>
       <c r="I9" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>(H9-G9)</f>
       </c>
       <c r="J9" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>(D9-G9)/A9</f>
       </c>
       <c r="K9" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>(E9-H9)/A9</f>
       </c>
       <c r="L9" s="23"/>
       <c r="M9" s="19">
@@ -3270,7 +3081,7 @@
       </c>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A10" s="6">
         <v>80</v>
       </c>
@@ -3287,8 +3098,7 @@
         <v>355</v>
       </c>
       <c r="F10" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>(E10-D10)</f>
       </c>
       <c r="G10" s="7">
         <v>302</v>
@@ -3297,16 +3107,13 @@
         <v>320</v>
       </c>
       <c r="I10" s="28">
-        <f t="shared" si="1"/>
-        <v>18</v>
+        <f>(H10-G10)</f>
       </c>
       <c r="J10" s="8">
-        <f t="shared" si="2"/>
-        <v>0.6</v>
+        <f>(D10-G10)/A10</f>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="3"/>
-        <v>0.4375</v>
+        <f>(E10-H10)/A10</f>
       </c>
       <c r="L10" s="9">
         <v>0.75</v>
@@ -3325,7 +3132,7 @@
       </c>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A11" s="11">
         <v>80</v>
       </c>
@@ -3342,8 +3149,7 @@
         <v>358</v>
       </c>
       <c r="F11" s="12">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>(E11-D11)</f>
       </c>
       <c r="G11" s="12">
         <v>305</v>
@@ -3352,16 +3158,13 @@
         <v>313</v>
       </c>
       <c r="I11" s="13">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f>(H11-G11)</f>
       </c>
       <c r="J11" s="14">
-        <f t="shared" si="2"/>
-        <v>0.625</v>
+        <f>(D11-G11)/A11</f>
       </c>
       <c r="K11" s="14">
-        <f t="shared" si="3"/>
-        <v>0.5625</v>
+        <f>(E11-H11)/A11</f>
       </c>
       <c r="L11" s="15">
         <v>0.8</v>
@@ -3380,7 +3183,7 @@
       </c>
       <c r="Q11" s="5"/>
     </row>
-    <row r="12" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A12" s="11">
         <v>80</v>
       </c>
@@ -3397,8 +3200,7 @@
         <v>358</v>
       </c>
       <c r="F12" s="12">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>(E12-D12)</f>
       </c>
       <c r="G12" s="12">
         <v>303</v>
@@ -3407,16 +3209,13 @@
         <v>322</v>
       </c>
       <c r="I12" s="13">
-        <f t="shared" si="1"/>
-        <v>19</v>
+        <f>(H12-G12)</f>
       </c>
       <c r="J12" s="14">
-        <f t="shared" si="2"/>
-        <v>0.5625</v>
+        <f>(D12-G12)/A12</f>
       </c>
       <c r="K12" s="14">
-        <f t="shared" si="3"/>
-        <v>0.45</v>
+        <f>(E12-H12)/A12</f>
       </c>
       <c r="L12" s="15">
         <v>0.65</v>
@@ -3435,7 +3234,7 @@
       </c>
       <c r="Q12" s="5"/>
     </row>
-    <row r="13" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A13" s="30">
         <v>80</v>
       </c>
@@ -3452,8 +3251,7 @@
         <v>364</v>
       </c>
       <c r="F13" s="31">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>(E13-D13)</f>
       </c>
       <c r="G13" s="31">
         <v>303</v>
@@ -3462,16 +3260,13 @@
         <v>303.5</v>
       </c>
       <c r="I13" s="33">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
+        <f>(H13-G13)</f>
       </c>
       <c r="J13" s="22">
-        <f t="shared" si="2"/>
-        <v>0.71250000000000002</v>
+        <f>(D13-G13)/A13</f>
       </c>
       <c r="K13" s="22">
-        <f t="shared" si="3"/>
-        <v>0.75624999999999998</v>
+        <f>(E13-H13)/A13</f>
       </c>
       <c r="L13" s="32">
         <v>0.7</v>
@@ -3492,7 +3287,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A14" s="6">
         <v>100</v>
       </c>
@@ -3509,8 +3304,7 @@
         <v>355</v>
       </c>
       <c r="F14" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>(E14-D14)</f>
       </c>
       <c r="G14" s="7">
         <v>305</v>
@@ -3519,16 +3313,13 @@
         <v>315</v>
       </c>
       <c r="I14" s="28">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f>(H14-G14)</f>
       </c>
       <c r="J14" s="8">
-        <f t="shared" si="2"/>
-        <v>0.47</v>
+        <f>(D14-G14)/A14</f>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="3"/>
-        <v>0.4</v>
+        <f>(E14-H14)/A14</f>
       </c>
       <c r="L14" s="9">
         <v>0.72</v>
@@ -3547,7 +3338,7 @@
       </c>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A15" s="11">
         <v>100</v>
       </c>
@@ -3564,8 +3355,7 @@
         <v>358</v>
       </c>
       <c r="F15" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>(E15-D15)</f>
       </c>
       <c r="G15" s="12">
         <v>306</v>
@@ -3574,16 +3364,13 @@
         <v>321</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f>(H15-G15)</f>
       </c>
       <c r="J15" s="14">
-        <f t="shared" si="2"/>
-        <v>0.47</v>
+        <f>(D15-G15)/A15</f>
       </c>
       <c r="K15" s="14">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
+        <f>(E15-H15)/A15</f>
       </c>
       <c r="L15" s="15">
         <v>0.75</v>
@@ -3602,7 +3389,7 @@
       </c>
       <c r="Q15" s="5"/>
     </row>
-    <row r="16" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A16" s="11">
         <v>100</v>
       </c>
@@ -3619,8 +3406,7 @@
         <v>357</v>
       </c>
       <c r="F16" s="12">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <f>(E16-D16)</f>
       </c>
       <c r="G16" s="12">
         <v>306</v>
@@ -3629,16 +3415,13 @@
         <v>325</v>
       </c>
       <c r="I16" s="13">
-        <f t="shared" si="1"/>
-        <v>19</v>
+        <f>(H16-G16)</f>
       </c>
       <c r="J16" s="14">
-        <f t="shared" si="2"/>
-        <v>0.4</v>
+        <f>(D16-G16)/A16</f>
       </c>
       <c r="K16" s="14">
-        <f t="shared" si="3"/>
-        <v>0.32</v>
+        <f>(E16-H16)/A16</f>
       </c>
       <c r="L16" s="15">
         <v>0.45</v>
@@ -3657,7 +3440,7 @@
       </c>
       <c r="Q16" s="5"/>
     </row>
-    <row r="17" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A17" s="18">
         <v>100</v>
       </c>
@@ -3674,8 +3457,7 @@
         <v>385</v>
       </c>
       <c r="F17" s="19">
-        <f t="shared" si="0"/>
-        <v>35</v>
+        <f>(E17-D17)</f>
       </c>
       <c r="G17" s="19">
         <v>302</v>
@@ -3684,16 +3466,13 @@
         <v>306</v>
       </c>
       <c r="I17" s="21">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f>(H17-G17)</f>
       </c>
       <c r="J17" s="22">
-        <f t="shared" si="2"/>
-        <v>0.48</v>
+        <f>(D17-G17)/A17</f>
       </c>
       <c r="K17" s="22">
-        <f t="shared" si="3"/>
-        <v>0.79</v>
+        <f>(E17-H17)/A17</f>
       </c>
       <c r="L17" s="35">
         <v>0.67</v>
@@ -3712,7 +3491,7 @@
       </c>
       <c r="Q17" s="5"/>
     </row>
-    <row r="18" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A18" s="36">
         <v>120</v>
       </c>
@@ -3729,8 +3508,7 @@
         <v>356</v>
       </c>
       <c r="F18" s="37">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>(E18-D18)</f>
       </c>
       <c r="G18" s="37">
         <v>304</v>
@@ -3739,16 +3517,13 @@
         <v>315</v>
       </c>
       <c r="I18" s="38">
-        <f t="shared" si="1"/>
-        <v>11</v>
+        <f>(H18-G18)</f>
       </c>
       <c r="J18" s="39">
-        <f t="shared" si="2"/>
-        <v>0.40833333333333333</v>
+        <f>(D18-G18)/A18</f>
       </c>
       <c r="K18" s="39">
-        <f t="shared" si="3"/>
-        <v>0.34166666666666667</v>
+        <f>(E18-H18)/A18</f>
       </c>
       <c r="L18" s="40">
         <v>0.77</v>
@@ -3767,7 +3542,7 @@
       </c>
       <c r="Q18" s="5"/>
     </row>
-    <row r="19" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20.5" customFormat="1" s="1">
       <c r="A19" s="11">
         <v>120</v>
       </c>
@@ -3784,8 +3559,7 @@
         <v>356</v>
       </c>
       <c r="F19" s="12">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>(E19-D19)</f>
       </c>
       <c r="G19" s="12">
         <v>307</v>
@@ -3794,16 +3568,13 @@
         <v>313</v>
       </c>
       <c r="I19" s="13">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <f>(H19-G19)</f>
       </c>
       <c r="J19" s="14">
-        <f t="shared" si="2"/>
-        <v>0.38333333333333336</v>
+        <f>(D19-G19)/A19</f>
       </c>
       <c r="K19" s="14">
-        <f t="shared" si="3"/>
-        <v>0.35833333333333334</v>
+        <f>(E19-H19)/A19</f>
       </c>
       <c r="L19" s="15">
         <v>0.8</v>
@@ -3822,7 +3593,7 @@
       </c>
       <c r="Q19" s="5"/>
     </row>
-    <row r="20" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A20" s="11">
         <v>120</v>
       </c>
@@ -3839,8 +3610,7 @@
         <v>358</v>
       </c>
       <c r="F20" s="12">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>(E20-D20)</f>
       </c>
       <c r="G20" s="12">
         <v>303</v>
@@ -3849,16 +3619,13 @@
         <v>323</v>
       </c>
       <c r="I20" s="13">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f>(H20-G20)</f>
       </c>
       <c r="J20" s="14">
-        <f t="shared" si="2"/>
-        <v>0.375</v>
+        <f>(D20-G20)/A20</f>
       </c>
       <c r="K20" s="14">
-        <f t="shared" si="3"/>
-        <v>0.29166666666666669</v>
+        <f>(E20-H20)/A20</f>
       </c>
       <c r="L20" s="15">
         <v>0.6</v>
@@ -3877,7 +3644,7 @@
       </c>
       <c r="Q20" s="5"/>
     </row>
-    <row r="21" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A21" s="42">
         <v>120</v>
       </c>
@@ -3890,22 +3657,18 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(E21-D21)</f>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="44">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>(H21-G21)</f>
       </c>
       <c r="J21" s="45">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>(D21-G21)/A21</f>
       </c>
       <c r="K21" s="45">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>(E21-H21)/A21</f>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="43">
@@ -3918,7 +3681,7 @@
       </c>
       <c r="Q21" s="5"/>
     </row>
-    <row r="22" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A22" s="6">
         <v>40</v>
       </c>
@@ -3935,8 +3698,7 @@
         <v>355</v>
       </c>
       <c r="F22" s="7">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f>(E22-D22)</f>
       </c>
       <c r="G22" s="9">
         <v>304.5</v>
@@ -3945,22 +3707,19 @@
         <v>305.5</v>
       </c>
       <c r="I22" s="28">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>(H22-G22)</f>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="2"/>
-        <v>0.9375</v>
+        <f>(D22-G22)/A22</f>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="3"/>
-        <v>1.2375</v>
+        <f>(E22-H22)/A22</f>
       </c>
       <c r="L22" s="9">
         <v>0.5</v>
       </c>
       <c r="M22" s="9">
-        <v>0.57999999999999996</v>
+        <v>0.58</v>
       </c>
       <c r="N22" s="7">
         <v>-220</v>
@@ -3973,7 +3732,7 @@
       </c>
       <c r="Q22" s="5"/>
     </row>
-    <row r="23" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A23" s="11">
         <v>40</v>
       </c>
@@ -3990,8 +3749,7 @@
         <v>352</v>
       </c>
       <c r="F23" s="12">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>(E23-D23)</f>
       </c>
       <c r="G23" s="12">
         <v>305</v>
@@ -4000,16 +3758,13 @@
         <v>307</v>
       </c>
       <c r="I23" s="13">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>(H23-G23)</f>
       </c>
       <c r="J23" s="14">
-        <f t="shared" si="2"/>
-        <v>1.05</v>
+        <f>(D23-G23)/A23</f>
       </c>
       <c r="K23" s="14">
-        <f t="shared" si="3"/>
-        <v>1.125</v>
+        <f>(E23-H23)/A23</f>
       </c>
       <c r="L23" s="15">
         <v>0.6</v>
@@ -4028,7 +3783,7 @@
       </c>
       <c r="Q23" s="5"/>
     </row>
-    <row r="24" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A24" s="18">
         <v>40</v>
       </c>
@@ -4045,8 +3800,7 @@
         <v>354</v>
       </c>
       <c r="F24" s="19">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>(E24-D24)</f>
       </c>
       <c r="G24" s="19">
         <v>305</v>
@@ -4055,19 +3809,16 @@
         <v>306</v>
       </c>
       <c r="I24" s="21">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>(H24-G24)</f>
       </c>
       <c r="J24" s="22">
-        <f t="shared" si="2"/>
-        <v>1.125</v>
+        <f>(D24-G24)/A24</f>
       </c>
       <c r="K24" s="22">
-        <f t="shared" si="3"/>
-        <v>1.2</v>
+        <f>(E24-H24)/A24</f>
       </c>
       <c r="L24" s="35">
-        <v>0.55000000000000004</v>
+        <v>0.55</v>
       </c>
       <c r="M24" s="35">
         <v>0.6</v>
@@ -4083,7 +3834,7 @@
       </c>
       <c r="Q24" s="5"/>
     </row>
-    <row r="25" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A25" s="6">
         <v>60</v>
       </c>
@@ -4100,8 +3851,7 @@
         <v>368</v>
       </c>
       <c r="F25" s="7">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <f>(E25-D25)</f>
       </c>
       <c r="G25" s="9">
         <v>304.5</v>
@@ -4110,16 +3860,13 @@
         <v>307.5</v>
       </c>
       <c r="I25" s="28">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f>(H25-G25)</f>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="2"/>
-        <v>0.67500000000000004</v>
+        <f>(D25-G25)/A25</f>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="3"/>
-        <v>1.0083333333333333</v>
+        <f>(E25-H25)/A25</f>
       </c>
       <c r="L25" s="9">
         <v>0.62</v>
@@ -4138,7 +3885,7 @@
       </c>
       <c r="Q25" s="5"/>
     </row>
-    <row r="26" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A26" s="11">
         <v>60</v>
       </c>
@@ -4155,8 +3902,7 @@
         <v>351</v>
       </c>
       <c r="F26" s="12">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>(E26-D26)</f>
       </c>
       <c r="G26" s="12">
         <v>305</v>
@@ -4165,16 +3911,13 @@
         <v>320</v>
       </c>
       <c r="I26" s="13">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f>(H26-G26)</f>
       </c>
       <c r="J26" s="14">
-        <f t="shared" si="2"/>
-        <v>0.6166666666666667</v>
+        <f>(D26-G26)/A26</f>
       </c>
       <c r="K26" s="14">
-        <f t="shared" si="3"/>
-        <v>0.51666666666666672</v>
+        <f>(E26-H26)/A26</f>
       </c>
       <c r="L26" s="15">
         <v>0.5</v>
@@ -4193,7 +3936,7 @@
       </c>
       <c r="Q26" s="5"/>
     </row>
-    <row r="27" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A27" s="18">
         <v>60</v>
       </c>
@@ -4210,8 +3953,7 @@
         <v>354</v>
       </c>
       <c r="F27" s="19">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>(E27-D27)</f>
       </c>
       <c r="G27" s="19">
         <v>307</v>
@@ -4220,16 +3962,13 @@
         <v>319</v>
       </c>
       <c r="I27" s="21">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>(H27-G27)</f>
       </c>
       <c r="J27" s="22">
-        <f t="shared" si="2"/>
-        <v>0.73333333333333328</v>
+        <f>(D27-G27)/A27</f>
       </c>
       <c r="K27" s="22">
-        <f t="shared" si="3"/>
-        <v>0.58333333333333337</v>
+        <f>(E27-H27)/A27</f>
       </c>
       <c r="L27" s="35">
         <v>0.68</v>
@@ -4248,7 +3987,7 @@
       </c>
       <c r="Q27" s="5"/>
     </row>
-    <row r="28" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20">
       <c r="A28" s="6">
         <v>80</v>
       </c>
@@ -4261,22 +4000,18 @@
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
       <c r="F28" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>(E28-D28)</f>
       </c>
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>
       <c r="I28" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>(H28-G28)</f>
       </c>
       <c r="J28" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>(D28-G28)/A28</f>
       </c>
       <c r="K28" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>(E28-H28)/A28</f>
       </c>
       <c r="L28" s="29"/>
       <c r="M28" s="7">
@@ -4291,7 +4026,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A29" s="11">
         <v>80</v>
       </c>
@@ -4308,8 +4043,7 @@
         <v>360</v>
       </c>
       <c r="F29" s="12">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>(E29-D29)</f>
       </c>
       <c r="G29" s="12">
         <v>304</v>
@@ -4318,16 +4052,13 @@
         <v>329</v>
       </c>
       <c r="I29" s="13">
-        <f t="shared" si="1"/>
-        <v>25</v>
+        <f>(H29-G29)</f>
       </c>
       <c r="J29" s="14">
-        <f t="shared" si="2"/>
-        <v>0.55000000000000004</v>
+        <f>(D29-G29)/A29</f>
       </c>
       <c r="K29" s="14">
-        <f t="shared" si="3"/>
-        <v>0.38750000000000001</v>
+        <f>(E29-H29)/A29</f>
       </c>
       <c r="L29" s="15">
         <v>0.62</v>
@@ -4346,7 +4077,7 @@
       </c>
       <c r="Q29" s="5"/>
     </row>
-    <row r="30" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A30" s="18">
         <v>80</v>
       </c>
@@ -4363,8 +4094,7 @@
         <v>354</v>
       </c>
       <c r="F30" s="19">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>(E30-D30)</f>
       </c>
       <c r="G30" s="19">
         <v>304</v>
@@ -4373,16 +4103,13 @@
         <v>326</v>
       </c>
       <c r="I30" s="21">
-        <f t="shared" si="1"/>
-        <v>22</v>
+        <f>(H30-G30)</f>
       </c>
       <c r="J30" s="22">
-        <f t="shared" si="2"/>
-        <v>0.52500000000000002</v>
+        <f>(D30-G30)/A30</f>
       </c>
       <c r="K30" s="22">
-        <f t="shared" si="3"/>
-        <v>0.35</v>
+        <f>(E30-H30)/A30</f>
       </c>
       <c r="L30" s="35">
         <v>0.46</v>
@@ -4401,7 +4128,7 @@
       </c>
       <c r="Q30" s="5"/>
     </row>
-    <row r="31" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A31" s="37">
         <v>100</v>
       </c>
@@ -4418,8 +4145,7 @@
         <v>374</v>
       </c>
       <c r="F31" s="37">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <f>(E31-D31)</f>
       </c>
       <c r="G31" s="37">
         <v>306</v>
@@ -4428,19 +4154,16 @@
         <v>308</v>
       </c>
       <c r="I31" s="38">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>(H31-G31)</f>
       </c>
       <c r="J31" s="39">
-        <f t="shared" si="2"/>
-        <v>0.46</v>
+        <f>(D31-G31)/A31</f>
       </c>
       <c r="K31" s="39">
-        <f t="shared" si="3"/>
-        <v>0.66</v>
+        <f>(E31-H31)/A31</f>
       </c>
       <c r="L31" s="40">
-        <v>0.55000000000000004</v>
+        <v>0.55</v>
       </c>
       <c r="M31" s="37">
         <v>1</v>
@@ -4456,7 +4179,7 @@
       </c>
       <c r="Q31" s="5"/>
     </row>
-    <row r="32" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A32" s="12">
         <v>100</v>
       </c>
@@ -4473,8 +4196,7 @@
         <v>357</v>
       </c>
       <c r="F32" s="12">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>(E32-D32)</f>
       </c>
       <c r="G32" s="12">
         <v>302</v>
@@ -4483,16 +4205,13 @@
         <v>330</v>
       </c>
       <c r="I32" s="13">
-        <f t="shared" si="1"/>
-        <v>28</v>
+        <f>(H32-G32)</f>
       </c>
       <c r="J32" s="14">
-        <f t="shared" si="2"/>
-        <v>0.39</v>
+        <f>(D32-G32)/A32</f>
       </c>
       <c r="K32" s="14">
-        <f t="shared" si="3"/>
-        <v>0.27</v>
+        <f>(E32-H32)/A32</f>
       </c>
       <c r="L32" s="15">
         <v>0.48</v>
@@ -4511,7 +4230,7 @@
       </c>
       <c r="Q32" s="5"/>
     </row>
-    <row r="33" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A33" s="43">
         <v>100</v>
       </c>
@@ -4528,8 +4247,7 @@
         <v>355</v>
       </c>
       <c r="F33" s="43">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>(E33-D33)</f>
       </c>
       <c r="G33" s="43">
         <v>306</v>
@@ -4538,16 +4256,13 @@
         <v>329</v>
       </c>
       <c r="I33" s="44">
-        <f t="shared" si="1"/>
-        <v>23</v>
+        <f>(H33-G33)</f>
       </c>
       <c r="J33" s="45">
-        <f t="shared" si="2"/>
-        <v>0.4</v>
+        <f>(D33-G33)/A33</f>
       </c>
       <c r="K33" s="45">
-        <f t="shared" si="3"/>
-        <v>0.26</v>
+        <f>(E33-H33)/A33</f>
       </c>
       <c r="L33" s="48">
         <v>0.6</v>
@@ -4566,7 +4281,7 @@
       </c>
       <c r="Q33" s="5"/>
     </row>
-    <row r="34" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A34" s="6">
         <v>120</v>
       </c>
@@ -4583,8 +4298,7 @@
         <v>370</v>
       </c>
       <c r="F34" s="7">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>(E34-D34)</f>
       </c>
       <c r="G34" s="7">
         <v>304</v>
@@ -4593,16 +4307,13 @@
         <v>314</v>
       </c>
       <c r="I34" s="28">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f>(H34-G34)</f>
       </c>
       <c r="J34" s="8">
-        <f t="shared" si="2"/>
-        <v>0.41666666666666669</v>
+        <f>(D34-G34)/A34</f>
       </c>
       <c r="K34" s="8">
-        <f t="shared" si="3"/>
-        <v>0.46666666666666667</v>
+        <f>(E34-H34)/A34</f>
       </c>
       <c r="L34" s="9">
         <v>0.6</v>
@@ -4621,7 +4332,7 @@
       </c>
       <c r="Q34" s="5"/>
     </row>
-    <row r="35" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A35" s="11">
         <v>120</v>
       </c>
@@ -4638,8 +4349,7 @@
         <v>355</v>
       </c>
       <c r="F35" s="12">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f>(E35-D35)</f>
       </c>
       <c r="G35" s="12">
         <v>302</v>
@@ -4648,16 +4358,13 @@
         <v>330</v>
       </c>
       <c r="I35" s="13">
-        <f t="shared" si="1"/>
-        <v>28</v>
+        <f>(H35-G35)</f>
       </c>
       <c r="J35" s="14">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <f>(D35-G35)/A35</f>
       </c>
       <c r="K35" s="14">
-        <f t="shared" si="3"/>
-        <v>0.20833333333333334</v>
+        <f>(E35-H35)/A35</f>
       </c>
       <c r="L35" s="15">
         <v>0.54</v>
@@ -4676,7 +4383,7 @@
       </c>
       <c r="Q35" s="5"/>
     </row>
-    <row r="36" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20" customFormat="1" s="1">
       <c r="A36" s="18">
         <v>120</v>
       </c>
@@ -4693,8 +4400,7 @@
         <v>355</v>
       </c>
       <c r="F36" s="19">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <f>(E36-D36)</f>
       </c>
       <c r="G36" s="19">
         <v>304</v>
@@ -4703,16 +4409,13 @@
         <v>327</v>
       </c>
       <c r="I36" s="21">
-        <f t="shared" si="1"/>
-        <v>23</v>
+        <f>(H36-G36)</f>
       </c>
       <c r="J36" s="22">
-        <f t="shared" si="2"/>
-        <v>0.32500000000000001</v>
+        <f>(D36-G36)/A36</f>
       </c>
       <c r="K36" s="22">
-        <f t="shared" si="3"/>
-        <v>0.23333333333333334</v>
+        <f>(E36-H36)/A36</f>
       </c>
       <c r="L36" s="35">
         <v>0.52</v>

--- a/data/observation_alpha_beta.xlsx
+++ b/data/observation_alpha_beta.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20416"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phd\php_pulsating_heat_pipe\Krp_Analysis\Advanced_PulseHeatPipe_krp\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5297DFEA-0699-47E9-B65C-FBF99C881A99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18200" windowHeight="8510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="demo"/>
-    <sheet r:id="rId2" sheetId="2" name="final"/>
+    <sheet name="demo" sheetId="1" r:id="rId1"/>
+    <sheet name="final" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">demo!$A$1:$R$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">demo!$A$1:$R$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">final!$A$1:$Q$36</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -81,13 +87,13 @@
     <t>Change_in_TR1[%]</t>
   </si>
   <si>
-    <t>Change_in_TR2 [%]</t>
+    <t>Change_in_TR2[%]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
@@ -107,7 +113,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFff0000"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -121,12 +127,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffffff"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFff0000"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -320,7 +326,7 @@
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -364,7 +370,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -383,16 +389,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -408,196 +414,197 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="61">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="9" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="11" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="14" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="15" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="16" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="17" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="18" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="19" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -608,10 +615,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -649,71 +656,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -741,7 +748,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -764,11 +771,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -777,13 +784,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -793,7 +800,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -802,7 +809,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -811,7 +818,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -819,10 +826,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -887,34 +894,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="49" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="49" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="49" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="49" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="49" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="50" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="50" width="10.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="50" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="50" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="51" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="49" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="49" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="49" width="11.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="1" max="3" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="9" style="49" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" style="50" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.26953125" style="50" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.54296875" style="51" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.54296875" style="49" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="39.5" customFormat="1" s="1">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
@@ -970,7 +971,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="2" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
         <v>40</v>
       </c>
@@ -987,7 +988,8 @@
         <v>352</v>
       </c>
       <c r="F2" s="12">
-        <f>(E2-D2)</f>
+        <f t="shared" ref="F2:F31" si="0">(E2-D2)</f>
+        <v>4</v>
       </c>
       <c r="G2" s="12">
         <v>306</v>
@@ -996,16 +998,19 @@
         <v>315</v>
       </c>
       <c r="I2" s="12">
-        <f>(H2-G2)</f>
+        <f t="shared" ref="I2:I31" si="1">(H2-G2)</f>
+        <v>9</v>
       </c>
       <c r="J2" s="14">
-        <f>(D2-G2)/A2</f>
+        <f t="shared" ref="J2:J31" si="2">(D2-G2)/A2</f>
+        <v>1.05</v>
       </c>
       <c r="K2" s="56">
         <v>0</v>
       </c>
       <c r="L2" s="14">
         <f>(E2-H2)/A2</f>
+        <v>0.92500000000000004</v>
       </c>
       <c r="M2" s="56">
         <v>0</v>
@@ -1026,7 +1031,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="3" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12">
         <v>40</v>
       </c>
@@ -1043,7 +1048,8 @@
         <v>357</v>
       </c>
       <c r="F3" s="12">
-        <f>(E3-D3)</f>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="G3" s="12">
         <v>304</v>
@@ -1052,19 +1058,24 @@
         <v>305</v>
       </c>
       <c r="I3" s="13">
-        <f>(H3-G3)</f>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J3" s="14">
-        <f>(D3-G3)/A3</f>
+        <f t="shared" si="2"/>
+        <v>1.125</v>
       </c>
       <c r="K3" s="14">
         <f>(J2-J3)/J2</f>
+        <v>-7.1428571428571383E-2</v>
       </c>
       <c r="L3" s="14">
         <f>(E3-H3)/A3</f>
+        <v>1.3</v>
       </c>
       <c r="M3" s="14">
         <f>(L2-L3)/L2</f>
+        <v>-0.40540540540540537</v>
       </c>
       <c r="N3" s="15">
         <v>0.7</v>
@@ -1082,7 +1093,7 @@
         <v>-0.85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="4" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <v>40</v>
       </c>
@@ -1099,7 +1110,8 @@
         <v>358.5</v>
       </c>
       <c r="F4" s="15">
-        <f>(E4-D4)</f>
+        <f t="shared" si="0"/>
+        <v>9.5</v>
       </c>
       <c r="G4" s="12">
         <v>304</v>
@@ -1108,19 +1120,24 @@
         <v>306</v>
       </c>
       <c r="I4" s="13">
-        <f>(H4-G4)</f>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J4" s="14">
-        <f>(D4-G4)/A4</f>
+        <f t="shared" si="2"/>
+        <v>1.125</v>
       </c>
       <c r="K4" s="14">
         <f>(J2-J4)/J2</f>
+        <v>-7.1428571428571383E-2</v>
       </c>
       <c r="L4" s="14">
         <f>(E4-H4)/A4</f>
+        <v>1.3125</v>
       </c>
       <c r="M4" s="14">
         <f>(L2-L4)/L2</f>
+        <v>-0.41891891891891886</v>
       </c>
       <c r="N4" s="15">
         <v>0.7</v>
@@ -1138,7 +1155,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="5" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <v>60</v>
       </c>
@@ -1155,7 +1172,8 @@
         <v>355</v>
       </c>
       <c r="F5" s="12">
-        <f>(E5-D5)</f>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G5" s="12">
         <v>303</v>
@@ -1164,14 +1182,17 @@
         <v>319</v>
       </c>
       <c r="I5" s="13">
-        <f>(H5-G5)</f>
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
       <c r="J5" s="14">
-        <f>(D5-G5)/A5</f>
+        <f t="shared" si="2"/>
+        <v>0.78333333333333333</v>
       </c>
       <c r="K5" s="14"/>
       <c r="L5" s="14">
-        <f>(E6-H6)/A6</f>
+        <f t="shared" ref="L5:L17" si="3">(E6-H6)/A6</f>
+        <v>0.6333333333333333</v>
       </c>
       <c r="M5" s="14"/>
       <c r="N5" s="15">
@@ -1190,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="6" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <v>60</v>
       </c>
@@ -1207,7 +1228,8 @@
         <v>359</v>
       </c>
       <c r="F6" s="12">
-        <f>(E6-D6)</f>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="G6" s="12">
         <v>305</v>
@@ -1216,14 +1238,17 @@
         <v>321</v>
       </c>
       <c r="I6" s="13">
-        <f>(H6-G6)</f>
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
       <c r="J6" s="14">
-        <f>(D6-G6)/A6</f>
+        <f t="shared" si="2"/>
+        <v>0.75</v>
       </c>
       <c r="K6" s="14"/>
       <c r="L6" s="14">
-        <f>(E7-H7)/A7</f>
+        <f t="shared" si="3"/>
+        <v>0.4375</v>
       </c>
       <c r="M6" s="14"/>
       <c r="N6" s="15">
@@ -1242,7 +1267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="7" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <v>80</v>
       </c>
@@ -1259,7 +1284,8 @@
         <v>355</v>
       </c>
       <c r="F7" s="12">
-        <f>(E7-D7)</f>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G7" s="12">
         <v>302</v>
@@ -1268,16 +1294,19 @@
         <v>320</v>
       </c>
       <c r="I7" s="13">
-        <f>(H7-G7)</f>
+        <f t="shared" si="1"/>
+        <v>18</v>
       </c>
       <c r="J7" s="14">
-        <f>(D7-G7)/A7</f>
+        <f t="shared" si="2"/>
+        <v>0.6</v>
       </c>
       <c r="K7" s="15">
         <v>0</v>
       </c>
       <c r="L7" s="14">
-        <f>(E8-H8)/A8</f>
+        <f t="shared" si="3"/>
+        <v>0.5625</v>
       </c>
       <c r="M7" s="15">
         <v>0</v>
@@ -1298,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="8" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <v>80</v>
       </c>
@@ -1315,7 +1344,8 @@
         <v>358</v>
       </c>
       <c r="F8" s="12">
-        <f>(E8-D8)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G8" s="12">
         <v>305</v>
@@ -1324,19 +1354,24 @@
         <v>313</v>
       </c>
       <c r="I8" s="13">
-        <f>(H8-G8)</f>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="J8" s="14">
-        <f>(D8-G8)/A8</f>
+        <f t="shared" si="2"/>
+        <v>0.625</v>
       </c>
       <c r="K8" s="14">
         <f>(J7-J8)/J7</f>
+        <v>-4.1666666666666706E-2</v>
       </c>
       <c r="L8" s="14">
-        <f>(E9-H9)/A9</f>
+        <f t="shared" si="3"/>
+        <v>0.45</v>
       </c>
       <c r="M8" s="14">
         <f>(L7-L8)/L7</f>
+        <v>0.19999999999999998</v>
       </c>
       <c r="N8" s="15">
         <v>0.8</v>
@@ -1354,7 +1389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="9" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
         <v>80</v>
       </c>
@@ -1371,7 +1406,8 @@
         <v>358</v>
       </c>
       <c r="F9" s="12">
-        <f>(E9-D9)</f>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="G9" s="12">
         <v>303</v>
@@ -1380,19 +1416,24 @@
         <v>322</v>
       </c>
       <c r="I9" s="13">
-        <f>(H9-G9)</f>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="J9" s="14">
-        <f>(D9-G9)/A9</f>
+        <f t="shared" si="2"/>
+        <v>0.5625</v>
       </c>
       <c r="K9" s="14">
         <f>(J7-J9)/J7</f>
+        <v>6.2499999999999965E-2</v>
       </c>
       <c r="L9" s="14">
-        <f>(E10-H10)/A10</f>
+        <f t="shared" si="3"/>
+        <v>0.75624999999999998</v>
       </c>
       <c r="M9" s="14">
         <f>(L7-L9)/L7</f>
+        <v>-0.34444444444444439</v>
       </c>
       <c r="N9" s="15">
         <v>0.65</v>
@@ -1410,7 +1451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5" customFormat="1" s="1">
+    <row r="10" spans="1:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="57">
         <v>80</v>
       </c>
@@ -1427,7 +1468,8 @@
         <v>364</v>
       </c>
       <c r="F10" s="57">
-        <f>(E10-D10)</f>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="G10" s="57">
         <v>303</v>
@@ -1436,19 +1478,24 @@
         <v>303.5</v>
       </c>
       <c r="I10" s="59">
-        <f>(H10-G10)</f>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="J10" s="60">
-        <f>(D10-G10)/A10</f>
+        <f t="shared" si="2"/>
+        <v>0.71250000000000002</v>
       </c>
       <c r="K10" s="60">
         <f>(J7-J10)/J7</f>
+        <v>-0.18750000000000008</v>
       </c>
       <c r="L10" s="60">
-        <f>(E11-H11)/A11</f>
+        <f t="shared" si="3"/>
+        <v>0.4</v>
       </c>
       <c r="M10" s="60">
         <f>(L7-L10)/L7</f>
+        <v>0.28888888888888886</v>
       </c>
       <c r="N10" s="58">
         <v>0.7</v>
@@ -1466,7 +1513,7 @@
         <v>-140</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="11" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12">
         <v>100</v>
       </c>
@@ -1483,7 +1530,8 @@
         <v>355</v>
       </c>
       <c r="F11" s="12">
-        <f>(E11-D11)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G11" s="12">
         <v>305</v>
@@ -1492,16 +1540,19 @@
         <v>315</v>
       </c>
       <c r="I11" s="13">
-        <f>(H11-G11)</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J11" s="14">
-        <f>(D11-G11)/A11</f>
+        <f t="shared" si="2"/>
+        <v>0.47</v>
       </c>
       <c r="K11" s="14">
         <v>0</v>
       </c>
       <c r="L11" s="14">
-        <f>(E12-H12)/A12</f>
+        <f t="shared" si="3"/>
+        <v>0.37</v>
       </c>
       <c r="M11" s="14">
         <v>0</v>
@@ -1522,7 +1573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="12" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
         <v>100</v>
       </c>
@@ -1539,7 +1590,8 @@
         <v>358</v>
       </c>
       <c r="F12" s="12">
-        <f>(E12-D12)</f>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G12" s="12">
         <v>306</v>
@@ -1548,19 +1600,24 @@
         <v>321</v>
       </c>
       <c r="I12" s="13">
-        <f>(H12-G12)</f>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J12" s="14">
-        <f>(D12-G12)/A12</f>
+        <f t="shared" si="2"/>
+        <v>0.47</v>
       </c>
       <c r="K12" s="14">
         <f>(J11-J12)/J11</f>
+        <v>0</v>
       </c>
       <c r="L12" s="14">
-        <f>(E13-H13)/A13</f>
+        <f t="shared" si="3"/>
+        <v>0.32</v>
       </c>
       <c r="M12" s="14">
         <f>(L11-L12)/L11</f>
+        <v>0.13513513513513511</v>
       </c>
       <c r="N12" s="15">
         <v>0.75</v>
@@ -1578,7 +1635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="13" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
         <v>100</v>
       </c>
@@ -1595,7 +1652,8 @@
         <v>357</v>
       </c>
       <c r="F13" s="12">
-        <f>(E13-D13)</f>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="G13" s="12">
         <v>306</v>
@@ -1604,19 +1662,24 @@
         <v>325</v>
       </c>
       <c r="I13" s="13">
-        <f>(H13-G13)</f>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="J13" s="14">
-        <f>(D13-G13)/A13</f>
+        <f t="shared" si="2"/>
+        <v>0.4</v>
       </c>
       <c r="K13" s="14">
         <f>(J11-J13)/J11</f>
+        <v>0.14893617021276587</v>
       </c>
       <c r="L13" s="14">
-        <f>(E14-H14)/A14</f>
+        <f t="shared" si="3"/>
+        <v>0.79</v>
       </c>
       <c r="M13" s="14">
         <f>(L11-L13)/L11</f>
+        <v>-1.1351351351351353</v>
       </c>
       <c r="N13" s="15">
         <v>0.45</v>
@@ -1634,7 +1697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="14" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <v>100</v>
       </c>
@@ -1651,7 +1714,8 @@
         <v>385</v>
       </c>
       <c r="F14" s="12">
-        <f>(E14-D14)</f>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
       <c r="G14" s="12">
         <v>302</v>
@@ -1660,19 +1724,24 @@
         <v>306</v>
       </c>
       <c r="I14" s="13">
-        <f>(H14-G14)</f>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="J14" s="14">
-        <f>(D14-G14)/A14</f>
+        <f t="shared" si="2"/>
+        <v>0.48</v>
       </c>
       <c r="K14" s="14">
         <f>(J11-J14)/J11</f>
+        <v>-2.1276595744680871E-2</v>
       </c>
       <c r="L14" s="14">
-        <f>(E15-H15)/A15</f>
+        <f t="shared" si="3"/>
+        <v>0.34166666666666667</v>
       </c>
       <c r="M14" s="14">
         <f>(L11-L14)/L11</f>
+        <v>7.6576576576576544E-2</v>
       </c>
       <c r="N14" s="15">
         <v>0.67</v>
@@ -1690,7 +1759,7 @@
         <v>-240</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="15" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
         <v>120</v>
       </c>
@@ -1707,7 +1776,8 @@
         <v>356</v>
       </c>
       <c r="F15" s="12">
-        <f>(E15-D15)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G15" s="12">
         <v>304</v>
@@ -1716,16 +1786,19 @@
         <v>315</v>
       </c>
       <c r="I15" s="13">
-        <f>(H15-G15)</f>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
-        <f>(D15-G15)/A15</f>
+        <f t="shared" si="2"/>
+        <v>0.40833333333333333</v>
       </c>
       <c r="K15" s="14">
         <v>0</v>
       </c>
       <c r="L15" s="14">
-        <f>(E16-H16)/A16</f>
+        <f t="shared" si="3"/>
+        <v>0.35833333333333334</v>
       </c>
       <c r="M15" s="14">
         <v>0</v>
@@ -1746,7 +1819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="16" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
         <v>120</v>
       </c>
@@ -1763,7 +1836,8 @@
         <v>356</v>
       </c>
       <c r="F16" s="12">
-        <f>(E16-D16)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G16" s="12">
         <v>307</v>
@@ -1772,19 +1846,24 @@
         <v>313</v>
       </c>
       <c r="I16" s="13">
-        <f>(H16-G16)</f>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="J16" s="14">
-        <f>(D16-G16)/A16</f>
+        <f t="shared" si="2"/>
+        <v>0.38333333333333336</v>
       </c>
       <c r="K16" s="14">
         <f>(J15-J16)/J15</f>
+        <v>6.122448979591829E-2</v>
       </c>
       <c r="L16" s="14">
-        <f>(E17-H17)/A17</f>
+        <f t="shared" si="3"/>
+        <v>0.29166666666666669</v>
       </c>
       <c r="M16" s="14">
         <f>(L15-L16)/L15</f>
+        <v>0.18604651162790695</v>
       </c>
       <c r="N16" s="15">
         <v>0.8</v>
@@ -1802,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="17" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12">
         <v>120</v>
       </c>
@@ -1819,7 +1898,8 @@
         <v>358</v>
       </c>
       <c r="F17" s="12">
-        <f>(E17-D17)</f>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="G17" s="12">
         <v>303</v>
@@ -1828,19 +1908,24 @@
         <v>323</v>
       </c>
       <c r="I17" s="13">
-        <f>(H17-G17)</f>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J17" s="14">
-        <f>(D17-G17)/A17</f>
+        <f t="shared" si="2"/>
+        <v>0.375</v>
       </c>
       <c r="K17" s="14">
         <f>(J15-J17)/J15</f>
+        <v>8.1632653061224469E-2</v>
       </c>
       <c r="L17" s="14">
-        <f>(E18-H18)/A18</f>
+        <f t="shared" si="3"/>
+        <v>1.2375</v>
       </c>
       <c r="M17" s="14">
         <f>(L15-L17)/L15</f>
+        <v>-2.4534883720930232</v>
       </c>
       <c r="N17" s="15">
         <v>0.6</v>
@@ -1858,7 +1943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="18" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
         <v>40</v>
       </c>
@@ -1875,7 +1960,8 @@
         <v>355</v>
       </c>
       <c r="F18" s="12">
-        <f>(E18-D18)</f>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
         <v>304.5</v>
@@ -1884,25 +1970,30 @@
         <v>305.5</v>
       </c>
       <c r="I18" s="13">
-        <f>(H18-G18)</f>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J18" s="14">
-        <f>(D18-G18)/A18</f>
+        <f t="shared" si="2"/>
+        <v>0.9375</v>
       </c>
       <c r="K18" s="14">
         <f>(J2-J18)/J2</f>
+        <v>0.10714285714285718</v>
       </c>
       <c r="L18" s="14">
-        <f>(E18-H18)/A18</f>
+        <f t="shared" ref="L18:L31" si="4">(E18-H18)/A18</f>
+        <v>1.2375</v>
       </c>
       <c r="M18" s="14">
         <f>(L2-L18)/L2</f>
+        <v>-0.33783783783783783</v>
       </c>
       <c r="N18" s="15">
         <v>0.5</v>
       </c>
       <c r="O18" s="15">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P18" s="12">
         <v>-220</v>
@@ -1914,7 +2005,7 @@
         <v>-225</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="19" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12">
         <v>40</v>
       </c>
@@ -1931,7 +2022,8 @@
         <v>352</v>
       </c>
       <c r="F19" s="12">
-        <f>(E19-D19)</f>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G19" s="12">
         <v>305</v>
@@ -1940,19 +2032,24 @@
         <v>307</v>
       </c>
       <c r="I19" s="13">
-        <f>(H19-G19)</f>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J19" s="14">
-        <f>(D19-G19)/A19</f>
+        <f t="shared" si="2"/>
+        <v>1.05</v>
       </c>
       <c r="K19" s="14">
         <f>(J2-J19)/J2</f>
+        <v>0</v>
       </c>
       <c r="L19" s="14">
-        <f>(E19-H19)/A19</f>
+        <f t="shared" si="4"/>
+        <v>1.125</v>
       </c>
       <c r="M19" s="14">
         <f>(L2-L19)/L2</f>
+        <v>-0.21621621621621614</v>
       </c>
       <c r="N19" s="15">
         <v>0.6</v>
@@ -1970,7 +2067,7 @@
         <v>-120</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="20" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12">
         <v>40</v>
       </c>
@@ -1987,7 +2084,8 @@
         <v>354</v>
       </c>
       <c r="F20" s="12">
-        <f>(E20-D20)</f>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="G20" s="12">
         <v>305</v>
@@ -1996,22 +2094,27 @@
         <v>306</v>
       </c>
       <c r="I20" s="13">
-        <f>(H20-G20)</f>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J20" s="14">
-        <f>(D20-G20)/A20</f>
+        <f t="shared" si="2"/>
+        <v>1.125</v>
       </c>
       <c r="K20" s="14">
         <f>(J2-J20)/J2</f>
+        <v>-7.1428571428571383E-2</v>
       </c>
       <c r="L20" s="14">
-        <f>(E20-H20)/A20</f>
+        <f t="shared" si="4"/>
+        <v>1.2</v>
       </c>
       <c r="M20" s="14">
         <f>(L2-L20)/L2</f>
+        <v>-0.2972972972972972</v>
       </c>
       <c r="N20" s="15">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O20" s="15">
         <v>0.6</v>
@@ -2026,7 +2129,7 @@
         <v>-220</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="21" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12">
         <v>60</v>
       </c>
@@ -2043,7 +2146,8 @@
         <v>368</v>
       </c>
       <c r="F21" s="12">
-        <f>(E21-D21)</f>
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="G21" s="15">
         <v>304.5</v>
@@ -2052,14 +2156,17 @@
         <v>307.5</v>
       </c>
       <c r="I21" s="13">
-        <f>(H21-G21)</f>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J21" s="14">
-        <f>(D21-G21)/A21</f>
+        <f t="shared" si="2"/>
+        <v>0.67500000000000004</v>
       </c>
       <c r="K21" s="14"/>
       <c r="L21" s="14">
-        <f>(E21-H21)/A21</f>
+        <f t="shared" si="4"/>
+        <v>1.0083333333333333</v>
       </c>
       <c r="M21" s="14"/>
       <c r="N21" s="15">
@@ -2078,7 +2185,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="22" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12">
         <v>60</v>
       </c>
@@ -2095,7 +2202,8 @@
         <v>351</v>
       </c>
       <c r="F22" s="12">
-        <f>(E22-D22)</f>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="G22" s="12">
         <v>305</v>
@@ -2104,14 +2212,17 @@
         <v>320</v>
       </c>
       <c r="I22" s="13">
-        <f>(H22-G22)</f>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J22" s="14">
-        <f>(D22-G22)/A22</f>
+        <f t="shared" si="2"/>
+        <v>0.6166666666666667</v>
       </c>
       <c r="K22" s="14"/>
       <c r="L22" s="14">
-        <f>(E22-H22)/A22</f>
+        <f t="shared" si="4"/>
+        <v>0.51666666666666672</v>
       </c>
       <c r="M22" s="14"/>
       <c r="N22" s="15">
@@ -2130,7 +2241,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row r="23" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12">
         <v>60</v>
       </c>
@@ -2147,7 +2258,8 @@
         <v>354</v>
       </c>
       <c r="F23" s="12">
-        <f>(E23-D23)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G23" s="12">
         <v>307</v>
@@ -2156,14 +2268,17 @@
         <v>319</v>
       </c>
       <c r="I23" s="13">
-        <f>(H23-G23)</f>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="J23" s="14">
-        <f>(D23-G23)/A23</f>
+        <f t="shared" si="2"/>
+        <v>0.73333333333333328</v>
       </c>
       <c r="K23" s="14"/>
       <c r="L23" s="14">
-        <f>(E23-H23)/A23</f>
+        <f t="shared" si="4"/>
+        <v>0.58333333333333337</v>
       </c>
       <c r="M23" s="14"/>
       <c r="N23" s="15">
@@ -2182,7 +2297,7 @@
         <v>-70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="24" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12">
         <v>80</v>
       </c>
@@ -2199,7 +2314,8 @@
         <v>360</v>
       </c>
       <c r="F24" s="12">
-        <f>(E24-D24)</f>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="G24" s="12">
         <v>304</v>
@@ -2208,19 +2324,24 @@
         <v>329</v>
       </c>
       <c r="I24" s="13">
-        <f>(H24-G24)</f>
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J24" s="14">
-        <f>(D24-G24)/A24</f>
+        <f t="shared" si="2"/>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K24" s="14">
         <f>(J7-J24)/J7</f>
+        <v>8.3333333333333232E-2</v>
       </c>
       <c r="L24" s="14">
-        <f>(E24-H24)/A24</f>
+        <f t="shared" si="4"/>
+        <v>0.38750000000000001</v>
       </c>
       <c r="M24" s="14">
         <f>(L7-L24)/L7</f>
+        <v>0.31111111111111112</v>
       </c>
       <c r="N24" s="15">
         <v>0.62</v>
@@ -2238,7 +2359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="25" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12">
         <v>80</v>
       </c>
@@ -2255,7 +2376,8 @@
         <v>354</v>
       </c>
       <c r="F25" s="12">
-        <f>(E25-D25)</f>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="G25" s="12">
         <v>304</v>
@@ -2264,19 +2386,24 @@
         <v>326</v>
       </c>
       <c r="I25" s="13">
-        <f>(H25-G25)</f>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="J25" s="14">
-        <f>(D25-G25)/A25</f>
+        <f t="shared" si="2"/>
+        <v>0.52500000000000002</v>
       </c>
       <c r="K25" s="14">
         <f>(J7-J25)/J7</f>
+        <v>0.12499999999999993</v>
       </c>
       <c r="L25" s="14">
-        <f>(E25-H25)/A25</f>
+        <f t="shared" si="4"/>
+        <v>0.35</v>
       </c>
       <c r="M25" s="14">
         <f>(L7-L25)/L7</f>
+        <v>0.37777777777777782</v>
       </c>
       <c r="N25" s="15">
         <v>0.46</v>
@@ -2294,7 +2421,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="26" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="12">
         <v>100</v>
       </c>
@@ -2311,7 +2438,8 @@
         <v>374</v>
       </c>
       <c r="F26" s="12">
-        <f>(E26-D26)</f>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="G26" s="12">
         <v>306</v>
@@ -2320,22 +2448,27 @@
         <v>308</v>
       </c>
       <c r="I26" s="13">
-        <f>(H26-G26)</f>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J26" s="14">
-        <f>(D26-G26)/A26</f>
+        <f t="shared" si="2"/>
+        <v>0.46</v>
       </c>
       <c r="K26" s="14">
         <f>(J11-J26)/J11</f>
+        <v>2.1276595744680753E-2</v>
       </c>
       <c r="L26" s="14">
-        <f>(E26-H26)/A26</f>
+        <f t="shared" si="4"/>
+        <v>0.66</v>
       </c>
       <c r="M26" s="14">
         <f>(L11-L26)/L11</f>
+        <v>-0.78378378378378388</v>
       </c>
       <c r="N26" s="15">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O26" s="12">
         <v>1</v>
@@ -2350,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="27" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12">
         <v>100</v>
       </c>
@@ -2367,7 +2500,8 @@
         <v>357</v>
       </c>
       <c r="F27" s="12">
-        <f>(E27-D27)</f>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="G27" s="12">
         <v>302</v>
@@ -2376,19 +2510,24 @@
         <v>330</v>
       </c>
       <c r="I27" s="13">
-        <f>(H27-G27)</f>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="J27" s="14">
-        <f>(D27-G27)/A27</f>
+        <f t="shared" si="2"/>
+        <v>0.39</v>
       </c>
       <c r="K27" s="14">
         <f>(J11-J27)/J11</f>
+        <v>0.17021276595744672</v>
       </c>
       <c r="L27" s="14">
-        <f>(E27-H27)/A27</f>
+        <f t="shared" si="4"/>
+        <v>0.27</v>
       </c>
       <c r="M27" s="14">
         <f>(L11-L27)/L11</f>
+        <v>0.27027027027027023</v>
       </c>
       <c r="N27" s="15">
         <v>0.48</v>
@@ -2406,7 +2545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="28" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12">
         <v>100</v>
       </c>
@@ -2423,7 +2562,8 @@
         <v>355</v>
       </c>
       <c r="F28" s="12">
-        <f>(E28-D28)</f>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="G28" s="12">
         <v>306</v>
@@ -2432,19 +2572,24 @@
         <v>329</v>
       </c>
       <c r="I28" s="13">
-        <f>(H28-G28)</f>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <f>(D28-G28)/A28</f>
+        <f t="shared" si="2"/>
+        <v>0.4</v>
       </c>
       <c r="K28" s="14">
         <f>(J11-J28)/J11</f>
+        <v>0.14893617021276587</v>
       </c>
       <c r="L28" s="14">
-        <f>(E28-H28)/A28</f>
+        <f t="shared" si="4"/>
+        <v>0.26</v>
       </c>
       <c r="M28" s="14">
         <f>(L11-L28)/L11</f>
+        <v>0.29729729729729726</v>
       </c>
       <c r="N28" s="15">
         <v>0.6</v>
@@ -2462,7 +2607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="29" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12">
         <v>120</v>
       </c>
@@ -2479,7 +2624,8 @@
         <v>370</v>
       </c>
       <c r="F29" s="12">
-        <f>(E29-D29)</f>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="G29" s="12">
         <v>304</v>
@@ -2488,19 +2634,24 @@
         <v>314</v>
       </c>
       <c r="I29" s="13">
-        <f>(H29-G29)</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J29" s="14">
-        <f>(D29-G29)/A29</f>
+        <f t="shared" si="2"/>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K29" s="14">
         <f>(J15-J29)/J15</f>
+        <v>-2.0408163265306187E-2</v>
       </c>
       <c r="L29" s="14">
-        <f>(E29-H29)/A29</f>
+        <f t="shared" si="4"/>
+        <v>0.46666666666666667</v>
       </c>
       <c r="M29" s="14">
         <f>(L15-L29)/L15</f>
+        <v>-0.30232558139534882</v>
       </c>
       <c r="N29" s="15">
         <v>0.6</v>
@@ -2518,7 +2669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="30" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12">
         <v>120</v>
       </c>
@@ -2535,7 +2686,8 @@
         <v>355</v>
       </c>
       <c r="F30" s="12">
-        <f>(E30-D30)</f>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="G30" s="12">
         <v>302</v>
@@ -2544,19 +2696,24 @@
         <v>330</v>
       </c>
       <c r="I30" s="13">
-        <f>(H30-G30)</f>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="J30" s="14">
-        <f>(D30-G30)/A30</f>
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K30" s="14">
         <f>(J15-J30)/J15</f>
+        <v>0.18367346938775514</v>
       </c>
       <c r="L30" s="14">
-        <f>(E30-H30)/A30</f>
+        <f t="shared" si="4"/>
+        <v>0.20833333333333334</v>
       </c>
       <c r="M30" s="14">
         <f>(L15-L30)/L15</f>
+        <v>0.41860465116279066</v>
       </c>
       <c r="N30" s="15">
         <v>0.54</v>
@@ -2574,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="31" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12">
         <v>120</v>
       </c>
@@ -2591,7 +2748,8 @@
         <v>355</v>
       </c>
       <c r="F31" s="12">
-        <f>(E31-D31)</f>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="G31" s="12">
         <v>304</v>
@@ -2600,19 +2758,24 @@
         <v>327</v>
       </c>
       <c r="I31" s="13">
-        <f>(H31-G31)</f>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="J31" s="14">
-        <f>(D31-G31)/A31</f>
+        <f t="shared" si="2"/>
+        <v>0.32500000000000001</v>
       </c>
       <c r="K31" s="14">
         <f>(J15-J31)/J15</f>
+        <v>0.20408163265306117</v>
       </c>
       <c r="L31" s="14">
-        <f>(E31-H31)/A31</f>
+        <f t="shared" si="4"/>
+        <v>0.23333333333333334</v>
       </c>
       <c r="M31" s="14">
         <f>(L15-L31)/L15</f>
+        <v>0.34883720930232559</v>
       </c>
       <c r="N31" s="15">
         <v>0.52</v>
@@ -2631,38 +2794,32 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R1" xr:uid="{BC3F519D-1E72-4C40-A9EB-D73907B1CA29}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:Q36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="49" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="49" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="49" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="49" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="49" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="50" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="50" width="10.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="51" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="49" width="8.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="49" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="49" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="49" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="52" width="14.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="3" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="9" style="49" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.54296875" style="51" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.54296875" style="49" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.453125" style="52" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="39.5" customFormat="1" s="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2713,7 +2870,7 @@
       </c>
       <c r="Q1" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>40</v>
       </c>
@@ -2730,7 +2887,8 @@
         <v>352</v>
       </c>
       <c r="F2" s="7">
-        <f>(E2-D2)</f>
+        <f t="shared" ref="F2:F36" si="0">(E2-D2)</f>
+        <v>4</v>
       </c>
       <c r="G2" s="7">
         <v>306</v>
@@ -2739,13 +2897,16 @@
         <v>315</v>
       </c>
       <c r="I2" s="7">
-        <f>(H2-G2)</f>
+        <f t="shared" ref="I2:I36" si="1">(H2-G2)</f>
+        <v>9</v>
       </c>
       <c r="J2" s="8">
-        <f>(D2-G2)/A2</f>
+        <f t="shared" ref="J2:J36" si="2">(D2-G2)/A2</f>
+        <v>1.05</v>
       </c>
       <c r="K2" s="8">
-        <f>(E2-H2)/A2</f>
+        <f t="shared" ref="K2:K36" si="3">(E2-H2)/A2</f>
+        <v>0.92500000000000004</v>
       </c>
       <c r="L2" s="9">
         <v>0.62</v>
@@ -2764,7 +2925,7 @@
       </c>
       <c r="Q2" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>40</v>
       </c>
@@ -2781,7 +2942,8 @@
         <v>357</v>
       </c>
       <c r="F3" s="12">
-        <f>(E3-D3)</f>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="G3" s="12">
         <v>304</v>
@@ -2790,13 +2952,16 @@
         <v>305</v>
       </c>
       <c r="I3" s="13">
-        <f>(H3-G3)</f>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J3" s="14">
-        <f>(D3-G3)/A3</f>
+        <f t="shared" si="2"/>
+        <v>1.125</v>
       </c>
       <c r="K3" s="14">
-        <f>(E3-H3)/A3</f>
+        <f t="shared" si="3"/>
+        <v>1.3</v>
       </c>
       <c r="L3" s="15">
         <v>0.7</v>
@@ -2815,7 +2980,7 @@
       </c>
       <c r="Q3" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>40</v>
       </c>
@@ -2832,7 +2997,8 @@
         <v>358.5</v>
       </c>
       <c r="F4" s="15">
-        <f>(E4-D4)</f>
+        <f t="shared" si="0"/>
+        <v>9.5</v>
       </c>
       <c r="G4" s="12">
         <v>304</v>
@@ -2841,13 +3007,16 @@
         <v>306</v>
       </c>
       <c r="I4" s="13">
-        <f>(H4-G4)</f>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J4" s="14">
-        <f>(D4-G4)/A4</f>
+        <f t="shared" si="2"/>
+        <v>1.125</v>
       </c>
       <c r="K4" s="14">
-        <f>(E4-H4)/A4</f>
+        <f t="shared" si="3"/>
+        <v>1.3125</v>
       </c>
       <c r="L4" s="15">
         <v>0.7</v>
@@ -2866,7 +3035,7 @@
       </c>
       <c r="Q4" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="5" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18">
         <v>40</v>
       </c>
@@ -2879,18 +3048,22 @@
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
       <c r="F5" s="19">
-        <f>(E5-D5)</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G5" s="20"/>
       <c r="H5" s="20"/>
       <c r="I5" s="21">
-        <f>(H5-G5)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="J5" s="22">
-        <f>(D5-G5)/A5</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K5" s="22">
-        <f>(E5-H5)/A5</f>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L5" s="23"/>
       <c r="M5" s="19">
@@ -2903,7 +3076,7 @@
       </c>
       <c r="Q5" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="6" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="25">
         <v>60</v>
       </c>
@@ -2916,18 +3089,22 @@
       <c r="D6" s="27"/>
       <c r="E6" s="27"/>
       <c r="F6" s="7">
-        <f>(E6-D6)</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G6" s="27"/>
       <c r="H6" s="27"/>
       <c r="I6" s="28">
-        <f>(H6-G6)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="J6" s="8">
-        <f>(D6-G6)/A6</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f>(E6-H6)/A6</f>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="7">
@@ -2942,7 +3119,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="7" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>60</v>
       </c>
@@ -2959,7 +3136,8 @@
         <v>355</v>
       </c>
       <c r="F7" s="12">
-        <f>(E7-D7)</f>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G7" s="12">
         <v>303</v>
@@ -2968,13 +3146,16 @@
         <v>319</v>
       </c>
       <c r="I7" s="13">
-        <f>(H7-G7)</f>
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
       <c r="J7" s="14">
-        <f>(D7-G7)/A7</f>
+        <f t="shared" si="2"/>
+        <v>0.78333333333333333</v>
       </c>
       <c r="K7" s="14">
-        <f>(E7-H7)/A7</f>
+        <f t="shared" si="3"/>
+        <v>0.6</v>
       </c>
       <c r="L7" s="15">
         <v>0.65</v>
@@ -2993,7 +3174,7 @@
       </c>
       <c r="Q7" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="8" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>60</v>
       </c>
@@ -3010,7 +3191,8 @@
         <v>359</v>
       </c>
       <c r="F8" s="12">
-        <f>(E8-D8)</f>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="G8" s="12">
         <v>305</v>
@@ -3019,13 +3201,16 @@
         <v>321</v>
       </c>
       <c r="I8" s="13">
-        <f>(H8-G8)</f>
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
       <c r="J8" s="14">
-        <f>(D8-G8)/A8</f>
+        <f t="shared" si="2"/>
+        <v>0.75</v>
       </c>
       <c r="K8" s="14">
-        <f>(E8-H8)/A8</f>
+        <f t="shared" si="3"/>
+        <v>0.6333333333333333</v>
       </c>
       <c r="L8" s="15">
         <v>0.75</v>
@@ -3044,7 +3229,7 @@
       </c>
       <c r="Q8" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="9" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="18">
         <v>60</v>
       </c>
@@ -3057,18 +3242,22 @@
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="19">
-        <f>(E9-D9)</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="20"/>
       <c r="I9" s="21">
-        <f>(H9-G9)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="J9" s="22">
-        <f>(D9-G9)/A9</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K9" s="22">
-        <f>(E9-H9)/A9</f>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L9" s="23"/>
       <c r="M9" s="19">
@@ -3081,7 +3270,7 @@
       </c>
       <c r="Q9" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="10" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>80</v>
       </c>
@@ -3098,7 +3287,8 @@
         <v>355</v>
       </c>
       <c r="F10" s="7">
-        <f>(E10-D10)</f>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G10" s="7">
         <v>302</v>
@@ -3107,13 +3297,16 @@
         <v>320</v>
       </c>
       <c r="I10" s="28">
-        <f>(H10-G10)</f>
+        <f t="shared" si="1"/>
+        <v>18</v>
       </c>
       <c r="J10" s="8">
-        <f>(D10-G10)/A10</f>
+        <f t="shared" si="2"/>
+        <v>0.6</v>
       </c>
       <c r="K10" s="8">
-        <f>(E10-H10)/A10</f>
+        <f t="shared" si="3"/>
+        <v>0.4375</v>
       </c>
       <c r="L10" s="9">
         <v>0.75</v>
@@ -3132,7 +3325,7 @@
       </c>
       <c r="Q10" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="11" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>80</v>
       </c>
@@ -3149,7 +3342,8 @@
         <v>358</v>
       </c>
       <c r="F11" s="12">
-        <f>(E11-D11)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G11" s="12">
         <v>305</v>
@@ -3158,13 +3352,16 @@
         <v>313</v>
       </c>
       <c r="I11" s="13">
-        <f>(H11-G11)</f>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="J11" s="14">
-        <f>(D11-G11)/A11</f>
+        <f t="shared" si="2"/>
+        <v>0.625</v>
       </c>
       <c r="K11" s="14">
-        <f>(E11-H11)/A11</f>
+        <f t="shared" si="3"/>
+        <v>0.5625</v>
       </c>
       <c r="L11" s="15">
         <v>0.8</v>
@@ -3183,7 +3380,7 @@
       </c>
       <c r="Q11" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="12" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>80</v>
       </c>
@@ -3200,7 +3397,8 @@
         <v>358</v>
       </c>
       <c r="F12" s="12">
-        <f>(E12-D12)</f>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="G12" s="12">
         <v>303</v>
@@ -3209,13 +3407,16 @@
         <v>322</v>
       </c>
       <c r="I12" s="13">
-        <f>(H12-G12)</f>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="J12" s="14">
-        <f>(D12-G12)/A12</f>
+        <f t="shared" si="2"/>
+        <v>0.5625</v>
       </c>
       <c r="K12" s="14">
-        <f>(E12-H12)/A12</f>
+        <f t="shared" si="3"/>
+        <v>0.45</v>
       </c>
       <c r="L12" s="15">
         <v>0.65</v>
@@ -3234,7 +3435,7 @@
       </c>
       <c r="Q12" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="13" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="30">
         <v>80</v>
       </c>
@@ -3251,7 +3452,8 @@
         <v>364</v>
       </c>
       <c r="F13" s="31">
-        <f>(E13-D13)</f>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="G13" s="31">
         <v>303</v>
@@ -3260,13 +3462,16 @@
         <v>303.5</v>
       </c>
       <c r="I13" s="33">
-        <f>(H13-G13)</f>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="J13" s="22">
-        <f>(D13-G13)/A13</f>
+        <f t="shared" si="2"/>
+        <v>0.71250000000000002</v>
       </c>
       <c r="K13" s="22">
-        <f>(E13-H13)/A13</f>
+        <f t="shared" si="3"/>
+        <v>0.75624999999999998</v>
       </c>
       <c r="L13" s="32">
         <v>0.7</v>
@@ -3287,7 +3492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="14" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>100</v>
       </c>
@@ -3304,7 +3509,8 @@
         <v>355</v>
       </c>
       <c r="F14" s="7">
-        <f>(E14-D14)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G14" s="7">
         <v>305</v>
@@ -3313,13 +3519,16 @@
         <v>315</v>
       </c>
       <c r="I14" s="28">
-        <f>(H14-G14)</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J14" s="8">
-        <f>(D14-G14)/A14</f>
+        <f t="shared" si="2"/>
+        <v>0.47</v>
       </c>
       <c r="K14" s="8">
-        <f>(E14-H14)/A14</f>
+        <f t="shared" si="3"/>
+        <v>0.4</v>
       </c>
       <c r="L14" s="9">
         <v>0.72</v>
@@ -3338,7 +3547,7 @@
       </c>
       <c r="Q14" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="15" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <v>100</v>
       </c>
@@ -3355,7 +3564,8 @@
         <v>358</v>
       </c>
       <c r="F15" s="12">
-        <f>(E15-D15)</f>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G15" s="12">
         <v>306</v>
@@ -3364,13 +3574,16 @@
         <v>321</v>
       </c>
       <c r="I15" s="13">
-        <f>(H15-G15)</f>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
-        <f>(D15-G15)/A15</f>
+        <f t="shared" si="2"/>
+        <v>0.47</v>
       </c>
       <c r="K15" s="14">
-        <f>(E15-H15)/A15</f>
+        <f t="shared" si="3"/>
+        <v>0.37</v>
       </c>
       <c r="L15" s="15">
         <v>0.75</v>
@@ -3389,7 +3602,7 @@
       </c>
       <c r="Q15" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="16" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <v>100</v>
       </c>
@@ -3406,7 +3619,8 @@
         <v>357</v>
       </c>
       <c r="F16" s="12">
-        <f>(E16-D16)</f>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="G16" s="12">
         <v>306</v>
@@ -3415,13 +3629,16 @@
         <v>325</v>
       </c>
       <c r="I16" s="13">
-        <f>(H16-G16)</f>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <f>(D16-G16)/A16</f>
+        <f t="shared" si="2"/>
+        <v>0.4</v>
       </c>
       <c r="K16" s="14">
-        <f>(E16-H16)/A16</f>
+        <f t="shared" si="3"/>
+        <v>0.32</v>
       </c>
       <c r="L16" s="15">
         <v>0.45</v>
@@ -3440,7 +3657,7 @@
       </c>
       <c r="Q16" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="17" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="18">
         <v>100</v>
       </c>
@@ -3457,7 +3674,8 @@
         <v>385</v>
       </c>
       <c r="F17" s="19">
-        <f>(E17-D17)</f>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
       <c r="G17" s="19">
         <v>302</v>
@@ -3466,13 +3684,16 @@
         <v>306</v>
       </c>
       <c r="I17" s="21">
-        <f>(H17-G17)</f>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="J17" s="22">
-        <f>(D17-G17)/A17</f>
+        <f t="shared" si="2"/>
+        <v>0.48</v>
       </c>
       <c r="K17" s="22">
-        <f>(E17-H17)/A17</f>
+        <f t="shared" si="3"/>
+        <v>0.79</v>
       </c>
       <c r="L17" s="35">
         <v>0.67</v>
@@ -3491,7 +3712,7 @@
       </c>
       <c r="Q17" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="18" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="36">
         <v>120</v>
       </c>
@@ -3508,7 +3729,8 @@
         <v>356</v>
       </c>
       <c r="F18" s="37">
-        <f>(E18-D18)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G18" s="37">
         <v>304</v>
@@ -3517,13 +3739,16 @@
         <v>315</v>
       </c>
       <c r="I18" s="38">
-        <f>(H18-G18)</f>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="J18" s="39">
-        <f>(D18-G18)/A18</f>
+        <f t="shared" si="2"/>
+        <v>0.40833333333333333</v>
       </c>
       <c r="K18" s="39">
-        <f>(E18-H18)/A18</f>
+        <f t="shared" si="3"/>
+        <v>0.34166666666666667</v>
       </c>
       <c r="L18" s="40">
         <v>0.77</v>
@@ -3542,7 +3767,7 @@
       </c>
       <c r="Q18" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="20.5" customFormat="1" s="1">
+    <row r="19" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11">
         <v>120</v>
       </c>
@@ -3559,7 +3784,8 @@
         <v>356</v>
       </c>
       <c r="F19" s="12">
-        <f>(E19-D19)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G19" s="12">
         <v>307</v>
@@ -3568,13 +3794,16 @@
         <v>313</v>
       </c>
       <c r="I19" s="13">
-        <f>(H19-G19)</f>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="J19" s="14">
-        <f>(D19-G19)/A19</f>
+        <f t="shared" si="2"/>
+        <v>0.38333333333333336</v>
       </c>
       <c r="K19" s="14">
-        <f>(E19-H19)/A19</f>
+        <f t="shared" si="3"/>
+        <v>0.35833333333333334</v>
       </c>
       <c r="L19" s="15">
         <v>0.8</v>
@@ -3593,7 +3822,7 @@
       </c>
       <c r="Q19" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="20" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
         <v>120</v>
       </c>
@@ -3610,7 +3839,8 @@
         <v>358</v>
       </c>
       <c r="F20" s="12">
-        <f>(E20-D20)</f>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="G20" s="12">
         <v>303</v>
@@ -3619,13 +3849,16 @@
         <v>323</v>
       </c>
       <c r="I20" s="13">
-        <f>(H20-G20)</f>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <f>(D20-G20)/A20</f>
+        <f t="shared" si="2"/>
+        <v>0.375</v>
       </c>
       <c r="K20" s="14">
-        <f>(E20-H20)/A20</f>
+        <f t="shared" si="3"/>
+        <v>0.29166666666666669</v>
       </c>
       <c r="L20" s="15">
         <v>0.6</v>
@@ -3644,7 +3877,7 @@
       </c>
       <c r="Q20" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="21" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="42">
         <v>120</v>
       </c>
@@ -3657,18 +3890,22 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="43">
-        <f>(E21-D21)</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="44">
-        <f>(H21-G21)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="J21" s="45">
-        <f>(D21-G21)/A21</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K21" s="45">
-        <f>(E21-H21)/A21</f>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="43">
@@ -3681,7 +3918,7 @@
       </c>
       <c r="Q21" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="22" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>40</v>
       </c>
@@ -3698,7 +3935,8 @@
         <v>355</v>
       </c>
       <c r="F22" s="7">
-        <f>(E22-D22)</f>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="G22" s="9">
         <v>304.5</v>
@@ -3707,19 +3945,22 @@
         <v>305.5</v>
       </c>
       <c r="I22" s="28">
-        <f>(H22-G22)</f>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J22" s="8">
-        <f>(D22-G22)/A22</f>
+        <f t="shared" si="2"/>
+        <v>0.9375</v>
       </c>
       <c r="K22" s="8">
-        <f>(E22-H22)/A22</f>
+        <f t="shared" si="3"/>
+        <v>1.2375</v>
       </c>
       <c r="L22" s="9">
         <v>0.5</v>
       </c>
       <c r="M22" s="9">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="N22" s="7">
         <v>-220</v>
@@ -3732,7 +3973,7 @@
       </c>
       <c r="Q22" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="23" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
         <v>40</v>
       </c>
@@ -3749,7 +3990,8 @@
         <v>352</v>
       </c>
       <c r="F23" s="12">
-        <f>(E23-D23)</f>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G23" s="12">
         <v>305</v>
@@ -3758,13 +4000,16 @@
         <v>307</v>
       </c>
       <c r="I23" s="13">
-        <f>(H23-G23)</f>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J23" s="14">
-        <f>(D23-G23)/A23</f>
+        <f t="shared" si="2"/>
+        <v>1.05</v>
       </c>
       <c r="K23" s="14">
-        <f>(E23-H23)/A23</f>
+        <f t="shared" si="3"/>
+        <v>1.125</v>
       </c>
       <c r="L23" s="15">
         <v>0.6</v>
@@ -3783,7 +4028,7 @@
       </c>
       <c r="Q23" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="24" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="18">
         <v>40</v>
       </c>
@@ -3800,7 +4045,8 @@
         <v>354</v>
       </c>
       <c r="F24" s="19">
-        <f>(E24-D24)</f>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="G24" s="19">
         <v>305</v>
@@ -3809,16 +4055,19 @@
         <v>306</v>
       </c>
       <c r="I24" s="21">
-        <f>(H24-G24)</f>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J24" s="22">
-        <f>(D24-G24)/A24</f>
+        <f t="shared" si="2"/>
+        <v>1.125</v>
       </c>
       <c r="K24" s="22">
-        <f>(E24-H24)/A24</f>
+        <f t="shared" si="3"/>
+        <v>1.2</v>
       </c>
       <c r="L24" s="35">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M24" s="35">
         <v>0.6</v>
@@ -3834,7 +4083,7 @@
       </c>
       <c r="Q24" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="25" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>60</v>
       </c>
@@ -3851,7 +4100,8 @@
         <v>368</v>
       </c>
       <c r="F25" s="7">
-        <f>(E25-D25)</f>
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="G25" s="9">
         <v>304.5</v>
@@ -3860,13 +4110,16 @@
         <v>307.5</v>
       </c>
       <c r="I25" s="28">
-        <f>(H25-G25)</f>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="J25" s="8">
-        <f>(D25-G25)/A25</f>
+        <f t="shared" si="2"/>
+        <v>0.67500000000000004</v>
       </c>
       <c r="K25" s="8">
-        <f>(E25-H25)/A25</f>
+        <f t="shared" si="3"/>
+        <v>1.0083333333333333</v>
       </c>
       <c r="L25" s="9">
         <v>0.62</v>
@@ -3885,7 +4138,7 @@
       </c>
       <c r="Q25" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="26" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11">
         <v>60</v>
       </c>
@@ -3902,7 +4155,8 @@
         <v>351</v>
       </c>
       <c r="F26" s="12">
-        <f>(E26-D26)</f>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="G26" s="12">
         <v>305</v>
@@ -3911,13 +4165,16 @@
         <v>320</v>
       </c>
       <c r="I26" s="13">
-        <f>(H26-G26)</f>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="J26" s="14">
-        <f>(D26-G26)/A26</f>
+        <f t="shared" si="2"/>
+        <v>0.6166666666666667</v>
       </c>
       <c r="K26" s="14">
-        <f>(E26-H26)/A26</f>
+        <f t="shared" si="3"/>
+        <v>0.51666666666666672</v>
       </c>
       <c r="L26" s="15">
         <v>0.5</v>
@@ -3936,7 +4193,7 @@
       </c>
       <c r="Q26" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="27" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="18">
         <v>60</v>
       </c>
@@ -3953,7 +4210,8 @@
         <v>354</v>
       </c>
       <c r="F27" s="19">
-        <f>(E27-D27)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G27" s="19">
         <v>307</v>
@@ -3962,13 +4220,16 @@
         <v>319</v>
       </c>
       <c r="I27" s="21">
-        <f>(H27-G27)</f>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="J27" s="22">
-        <f>(D27-G27)/A27</f>
+        <f t="shared" si="2"/>
+        <v>0.73333333333333328</v>
       </c>
       <c r="K27" s="22">
-        <f>(E27-H27)/A27</f>
+        <f t="shared" si="3"/>
+        <v>0.58333333333333337</v>
       </c>
       <c r="L27" s="35">
         <v>0.68</v>
@@ -3987,7 +4248,7 @@
       </c>
       <c r="Q27" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20">
+    <row r="28" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>80</v>
       </c>
@@ -4000,18 +4261,22 @@
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
       <c r="F28" s="7">
-        <f>(E28-D28)</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>
       <c r="I28" s="28">
-        <f>(H28-G28)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="J28" s="8">
-        <f>(D28-G28)/A28</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K28" s="8">
-        <f>(E28-H28)/A28</f>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="L28" s="29"/>
       <c r="M28" s="7">
@@ -4026,7 +4291,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="29" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11">
         <v>80</v>
       </c>
@@ -4043,7 +4308,8 @@
         <v>360</v>
       </c>
       <c r="F29" s="12">
-        <f>(E29-D29)</f>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="G29" s="12">
         <v>304</v>
@@ -4052,13 +4318,16 @@
         <v>329</v>
       </c>
       <c r="I29" s="13">
-        <f>(H29-G29)</f>
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="J29" s="14">
-        <f>(D29-G29)/A29</f>
+        <f t="shared" si="2"/>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K29" s="14">
-        <f>(E29-H29)/A29</f>
+        <f t="shared" si="3"/>
+        <v>0.38750000000000001</v>
       </c>
       <c r="L29" s="15">
         <v>0.62</v>
@@ -4077,7 +4346,7 @@
       </c>
       <c r="Q29" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="30" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="18">
         <v>80</v>
       </c>
@@ -4094,7 +4363,8 @@
         <v>354</v>
       </c>
       <c r="F30" s="19">
-        <f>(E30-D30)</f>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="G30" s="19">
         <v>304</v>
@@ -4103,13 +4373,16 @@
         <v>326</v>
       </c>
       <c r="I30" s="21">
-        <f>(H30-G30)</f>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="J30" s="22">
-        <f>(D30-G30)/A30</f>
+        <f t="shared" si="2"/>
+        <v>0.52500000000000002</v>
       </c>
       <c r="K30" s="22">
-        <f>(E30-H30)/A30</f>
+        <f t="shared" si="3"/>
+        <v>0.35</v>
       </c>
       <c r="L30" s="35">
         <v>0.46</v>
@@ -4128,7 +4401,7 @@
       </c>
       <c r="Q30" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="31" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="37">
         <v>100</v>
       </c>
@@ -4145,7 +4418,8 @@
         <v>374</v>
       </c>
       <c r="F31" s="37">
-        <f>(E31-D31)</f>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="G31" s="37">
         <v>306</v>
@@ -4154,16 +4428,19 @@
         <v>308</v>
       </c>
       <c r="I31" s="38">
-        <f>(H31-G31)</f>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J31" s="39">
-        <f>(D31-G31)/A31</f>
+        <f t="shared" si="2"/>
+        <v>0.46</v>
       </c>
       <c r="K31" s="39">
-        <f>(E31-H31)/A31</f>
+        <f t="shared" si="3"/>
+        <v>0.66</v>
       </c>
       <c r="L31" s="40">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M31" s="37">
         <v>1</v>
@@ -4179,7 +4456,7 @@
       </c>
       <c r="Q31" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="32" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12">
         <v>100</v>
       </c>
@@ -4196,7 +4473,8 @@
         <v>357</v>
       </c>
       <c r="F32" s="12">
-        <f>(E32-D32)</f>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="G32" s="12">
         <v>302</v>
@@ -4205,13 +4483,16 @@
         <v>330</v>
       </c>
       <c r="I32" s="13">
-        <f>(H32-G32)</f>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="J32" s="14">
-        <f>(D32-G32)/A32</f>
+        <f t="shared" si="2"/>
+        <v>0.39</v>
       </c>
       <c r="K32" s="14">
-        <f>(E32-H32)/A32</f>
+        <f t="shared" si="3"/>
+        <v>0.27</v>
       </c>
       <c r="L32" s="15">
         <v>0.48</v>
@@ -4230,7 +4511,7 @@
       </c>
       <c r="Q32" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="33" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="43">
         <v>100</v>
       </c>
@@ -4247,7 +4528,8 @@
         <v>355</v>
       </c>
       <c r="F33" s="43">
-        <f>(E33-D33)</f>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="G33" s="43">
         <v>306</v>
@@ -4256,13 +4538,16 @@
         <v>329</v>
       </c>
       <c r="I33" s="44">
-        <f>(H33-G33)</f>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="J33" s="45">
-        <f>(D33-G33)/A33</f>
+        <f t="shared" si="2"/>
+        <v>0.4</v>
       </c>
       <c r="K33" s="45">
-        <f>(E33-H33)/A33</f>
+        <f t="shared" si="3"/>
+        <v>0.26</v>
       </c>
       <c r="L33" s="48">
         <v>0.6</v>
@@ -4281,7 +4566,7 @@
       </c>
       <c r="Q33" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="34" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>120</v>
       </c>
@@ -4298,7 +4583,8 @@
         <v>370</v>
       </c>
       <c r="F34" s="7">
-        <f>(E34-D34)</f>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="G34" s="7">
         <v>304</v>
@@ -4307,13 +4593,16 @@
         <v>314</v>
       </c>
       <c r="I34" s="28">
-        <f>(H34-G34)</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="J34" s="8">
-        <f>(D34-G34)/A34</f>
+        <f t="shared" si="2"/>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K34" s="8">
-        <f>(E34-H34)/A34</f>
+        <f t="shared" si="3"/>
+        <v>0.46666666666666667</v>
       </c>
       <c r="L34" s="9">
         <v>0.6</v>
@@ -4332,7 +4621,7 @@
       </c>
       <c r="Q34" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="35" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11">
         <v>120</v>
       </c>
@@ -4349,7 +4638,8 @@
         <v>355</v>
       </c>
       <c r="F35" s="12">
-        <f>(E35-D35)</f>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="G35" s="12">
         <v>302</v>
@@ -4358,13 +4648,16 @@
         <v>330</v>
       </c>
       <c r="I35" s="13">
-        <f>(H35-G35)</f>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="J35" s="14">
-        <f>(D35-G35)/A35</f>
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K35" s="14">
-        <f>(E35-H35)/A35</f>
+        <f t="shared" si="3"/>
+        <v>0.20833333333333334</v>
       </c>
       <c r="L35" s="15">
         <v>0.54</v>
@@ -4383,7 +4676,7 @@
       </c>
       <c r="Q35" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20" customFormat="1" s="1">
+    <row r="36" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="18">
         <v>120</v>
       </c>
@@ -4400,7 +4693,8 @@
         <v>355</v>
       </c>
       <c r="F36" s="19">
-        <f>(E36-D36)</f>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="G36" s="19">
         <v>304</v>
@@ -4409,13 +4703,16 @@
         <v>327</v>
       </c>
       <c r="I36" s="21">
-        <f>(H36-G36)</f>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="J36" s="22">
-        <f>(D36-G36)/A36</f>
+        <f t="shared" si="2"/>
+        <v>0.32500000000000001</v>
       </c>
       <c r="K36" s="22">
-        <f>(E36-H36)/A36</f>
+        <f t="shared" si="3"/>
+        <v>0.23333333333333334</v>
       </c>
       <c r="L36" s="35">
         <v>0.52</v>

--- a/data/observation_alpha_beta.xlsx
+++ b/data/observation_alpha_beta.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phd\php_pulsating_heat_pipe\Krp_Analysis\Advanced_PulseHeatPipe_krp\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/58033850cf77e637/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5297DFEA-0699-47E9-B65C-FBF99C881A99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEEFA822-9600-45A4-8730-889827C4070E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18200" windowHeight="8510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="final" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">demo!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">demo!$A$1:$T$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">final!$A$1:$Q$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>Q[W]</t>
   </si>
@@ -89,6 +89,12 @@
   <si>
     <t>Change_in_TR2[%]</t>
   </si>
+  <si>
+    <t>Change_in_TR1</t>
+  </si>
+  <si>
+    <t>Change_in_TR2</t>
+  </si>
 </sst>
 </file>
 
@@ -403,10 +409,18 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -569,28 +583,28 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -898,7 +912,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
@@ -906,552 +920,620 @@
     <col min="9" max="9" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.453125" style="50" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" style="50" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.54296875" style="51" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.54296875" style="49" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.453125" style="50" customWidth="1"/>
+    <col min="13" max="13" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.26953125" style="50" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.26953125" style="50" customWidth="1"/>
+    <col min="16" max="16" width="8.54296875" style="51" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.54296875" style="49" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="53" t="s">
+    <row r="1" spans="1:20" s="1" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="53" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="54" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="54" t="s">
+      <c r="K1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="54" t="s">
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="54" t="s">
+      <c r="N1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="55" t="s">
+      <c r="P1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="53" t="s">
+      <c r="Q1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="53" t="s">
+      <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="53" t="s">
+      <c r="S1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="53" t="s">
+      <c r="T1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="12">
+    <row r="2" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="53">
         <v>40</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="53">
         <v>90</v>
       </c>
-      <c r="C2" s="12">
-        <v>0</v>
-      </c>
-      <c r="D2" s="12">
+      <c r="C2" s="53">
+        <v>0</v>
+      </c>
+      <c r="D2" s="53">
         <v>348</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="53">
         <v>352</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="53">
         <f t="shared" ref="F2:F31" si="0">(E2-D2)</f>
         <v>4</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="53">
         <v>306</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="53">
         <v>315</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="53">
         <f t="shared" ref="I2:I31" si="1">(H2-G2)</f>
         <v>9</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="54">
         <f t="shared" ref="J2:J31" si="2">(D2-G2)/A2</f>
         <v>1.05</v>
       </c>
-      <c r="K2" s="56">
-        <v>0</v>
-      </c>
-      <c r="L2" s="14">
+      <c r="K2" s="55">
+        <v>0</v>
+      </c>
+      <c r="L2" s="55">
+        <v>0</v>
+      </c>
+      <c r="M2" s="54">
         <f>(E2-H2)/A2</f>
         <v>0.92500000000000004</v>
       </c>
-      <c r="M2" s="56">
-        <v>0</v>
-      </c>
-      <c r="N2" s="15">
+      <c r="N2" s="55">
+        <v>0</v>
+      </c>
+      <c r="O2" s="55">
+        <v>0</v>
+      </c>
+      <c r="P2" s="55">
         <v>0.62</v>
       </c>
-      <c r="O2" s="15">
+      <c r="Q2" s="55">
         <v>0.75</v>
       </c>
-      <c r="P2" s="12">
+      <c r="R2" s="53">
         <v>-155</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="S2" s="53">
         <v>-190</v>
       </c>
-      <c r="R2" s="12">
+      <c r="T2" s="53">
         <v>-100</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12">
+    <row r="3" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="53">
         <v>40</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="53">
         <v>60</v>
       </c>
-      <c r="C3" s="12">
-        <v>0</v>
-      </c>
-      <c r="D3" s="12">
+      <c r="C3" s="53">
+        <v>0</v>
+      </c>
+      <c r="D3" s="53">
         <v>349</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="53">
         <v>357</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="53">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="53">
         <v>304</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="53">
         <v>305</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="56">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="54">
         <f t="shared" si="2"/>
         <v>1.125</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="54">
         <f>(J2-J3)/J2</f>
         <v>-7.1428571428571383E-2</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="55">
+        <f t="shared" ref="L3:L31" si="3">K3*100</f>
+        <v>-7.1428571428571379</v>
+      </c>
+      <c r="M3" s="54">
         <f>(E3-H3)/A3</f>
         <v>1.3</v>
       </c>
-      <c r="M3" s="14">
-        <f>(L2-L3)/L2</f>
+      <c r="N3" s="54">
+        <f>(M2-M3)/M2</f>
         <v>-0.40540540540540537</v>
       </c>
-      <c r="N3" s="15">
+      <c r="O3" s="55">
+        <f t="shared" ref="O3:O31" si="4">N3*100</f>
+        <v>-40.54054054054054</v>
+      </c>
+      <c r="P3" s="55">
         <v>0.7</v>
       </c>
-      <c r="O3" s="15">
+      <c r="Q3" s="55">
         <v>0.8</v>
       </c>
-      <c r="P3" s="12">
+      <c r="R3" s="53">
         <v>-140</v>
       </c>
-      <c r="Q3" s="12">
+      <c r="S3" s="53">
         <v>-160</v>
       </c>
-      <c r="R3" s="15">
+      <c r="T3" s="55">
         <v>-0.85</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="12">
+    <row r="4" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="53">
         <v>40</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="53">
         <v>30</v>
       </c>
-      <c r="C4" s="12">
-        <v>0</v>
-      </c>
-      <c r="D4" s="12">
+      <c r="C4" s="53">
+        <v>0</v>
+      </c>
+      <c r="D4" s="53">
         <v>349</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="55">
         <v>358.5</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="55">
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="53">
         <v>304</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="53">
         <v>306</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="56">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="54">
         <f t="shared" si="2"/>
         <v>1.125</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="54">
         <f>(J2-J4)/J2</f>
         <v>-7.1428571428571383E-2</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="55">
+        <f t="shared" si="3"/>
+        <v>-7.1428571428571379</v>
+      </c>
+      <c r="M4" s="54">
         <f>(E4-H4)/A4</f>
         <v>1.3125</v>
       </c>
-      <c r="M4" s="14">
-        <f>(L2-L4)/L2</f>
+      <c r="N4" s="54">
+        <f>(M2-M4)/M2</f>
         <v>-0.41891891891891886</v>
       </c>
-      <c r="N4" s="15">
+      <c r="O4" s="55">
+        <f t="shared" si="4"/>
+        <v>-41.891891891891888</v>
+      </c>
+      <c r="P4" s="55">
         <v>0.7</v>
       </c>
-      <c r="O4" s="15">
+      <c r="Q4" s="55">
         <v>0.83</v>
       </c>
-      <c r="P4" s="12">
+      <c r="R4" s="53">
         <v>-130</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="S4" s="53">
         <v>-150</v>
       </c>
-      <c r="R4" s="12">
+      <c r="T4" s="53">
         <v>-90</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="12">
+    <row r="5" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="53">
         <v>60</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="53">
         <v>60</v>
       </c>
-      <c r="C5" s="12">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12">
+      <c r="C5" s="53">
+        <v>0</v>
+      </c>
+      <c r="D5" s="53">
         <v>350</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="53">
         <v>355</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="53">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="53">
         <v>303</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="53">
         <v>319</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="56">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="54">
         <f t="shared" si="2"/>
         <v>0.78333333333333333</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14">
-        <f t="shared" ref="L5:L17" si="3">(E6-H6)/A6</f>
+      <c r="K5" s="54"/>
+      <c r="L5" s="55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="54">
+        <f t="shared" ref="M5:M17" si="5">(E6-H6)/A6</f>
         <v>0.6333333333333333</v>
       </c>
-      <c r="M5" s="14"/>
-      <c r="N5" s="15">
+      <c r="N5" s="54"/>
+      <c r="O5" s="55">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="55">
         <v>0.65</v>
       </c>
-      <c r="O5" s="12">
+      <c r="Q5" s="53">
         <v>1</v>
       </c>
-      <c r="P5" s="12">
+      <c r="R5" s="53">
         <v>-160</v>
       </c>
-      <c r="Q5" s="12">
+      <c r="S5" s="53">
         <v>-180</v>
       </c>
-      <c r="R5" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="12">
+      <c r="T5" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="53">
         <v>60</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="53">
         <v>30</v>
       </c>
-      <c r="C6" s="12">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C6" s="53">
+        <v>0</v>
+      </c>
+      <c r="D6" s="53">
         <v>350</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="53">
         <v>359</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="53">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="53">
         <v>305</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="53">
         <v>321</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="56">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="54">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14">
-        <f t="shared" si="3"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="54">
+        <f t="shared" si="5"/>
         <v>0.4375</v>
       </c>
-      <c r="M6" s="14"/>
-      <c r="N6" s="15">
+      <c r="N6" s="54"/>
+      <c r="O6" s="55">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="55">
         <v>0.75</v>
       </c>
-      <c r="O6" s="12">
+      <c r="Q6" s="53">
         <v>1</v>
       </c>
-      <c r="P6" s="12">
+      <c r="R6" s="53">
         <v>-120</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="S6" s="53">
         <v>-150</v>
       </c>
-      <c r="R6" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="12">
+      <c r="T6" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="53">
         <v>80</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="53">
         <v>90</v>
       </c>
-      <c r="C7" s="12">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="C7" s="53">
+        <v>0</v>
+      </c>
+      <c r="D7" s="53">
         <v>350</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="53">
         <v>355</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="53">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="53">
         <v>302</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="53">
         <v>320</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="56">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="54">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="K7" s="15">
-        <v>0</v>
-      </c>
-      <c r="L7" s="14">
-        <f t="shared" si="3"/>
+      <c r="K7" s="55">
+        <v>0</v>
+      </c>
+      <c r="L7" s="55">
+        <v>0</v>
+      </c>
+      <c r="M7" s="54">
+        <f t="shared" si="5"/>
         <v>0.5625</v>
       </c>
-      <c r="M7" s="15">
-        <v>0</v>
-      </c>
-      <c r="N7" s="15">
+      <c r="N7" s="55">
+        <v>0</v>
+      </c>
+      <c r="O7" s="55">
+        <v>0</v>
+      </c>
+      <c r="P7" s="55">
         <v>0.75</v>
       </c>
-      <c r="O7" s="12">
+      <c r="Q7" s="53">
         <v>1</v>
       </c>
-      <c r="P7" s="12">
+      <c r="R7" s="53">
         <v>-125</v>
       </c>
-      <c r="Q7" s="12">
+      <c r="S7" s="53">
         <v>-150</v>
       </c>
-      <c r="R7" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
+      <c r="T7" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="53">
         <v>80</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="53">
         <v>60</v>
       </c>
-      <c r="C8" s="12">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="C8" s="53">
+        <v>0</v>
+      </c>
+      <c r="D8" s="53">
         <v>355</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="53">
         <v>358</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="53">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="53">
         <v>305</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="53">
         <v>313</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="56">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="54">
         <f t="shared" si="2"/>
         <v>0.625</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="54">
         <f>(J7-J8)/J7</f>
         <v>-4.1666666666666706E-2</v>
       </c>
-      <c r="L8" s="14">
-        <f t="shared" si="3"/>
+      <c r="L8" s="55">
+        <f t="shared" si="3"/>
+        <v>-4.1666666666666705</v>
+      </c>
+      <c r="M8" s="54">
+        <f t="shared" si="5"/>
         <v>0.45</v>
       </c>
-      <c r="M8" s="14">
-        <f>(L7-L8)/L7</f>
+      <c r="N8" s="54">
+        <f>(M7-M8)/M7</f>
         <v>0.19999999999999998</v>
       </c>
-      <c r="N8" s="15">
+      <c r="O8" s="55">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="P8" s="55">
         <v>0.8</v>
       </c>
-      <c r="O8" s="12">
+      <c r="Q8" s="53">
         <v>1</v>
       </c>
-      <c r="P8" s="12">
+      <c r="R8" s="53">
         <v>-85</v>
       </c>
-      <c r="Q8" s="12">
+      <c r="S8" s="53">
         <v>-100</v>
       </c>
-      <c r="R8" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="12">
+      <c r="T8" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="53">
         <v>80</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="53">
         <v>30</v>
       </c>
-      <c r="C9" s="12">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12">
+      <c r="C9" s="53">
+        <v>0</v>
+      </c>
+      <c r="D9" s="53">
         <v>348</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="53">
         <v>358</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="53">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="53">
         <v>303</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="53">
         <v>322</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="56">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="54">
         <f t="shared" si="2"/>
         <v>0.5625</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="54">
         <f>(J7-J9)/J7</f>
         <v>6.2499999999999965E-2</v>
       </c>
-      <c r="L9" s="14">
-        <f t="shared" si="3"/>
+      <c r="L9" s="55">
+        <f t="shared" si="3"/>
+        <v>6.2499999999999964</v>
+      </c>
+      <c r="M9" s="54">
+        <f t="shared" si="5"/>
         <v>0.75624999999999998</v>
       </c>
-      <c r="M9" s="14">
-        <f>(L7-L9)/L7</f>
+      <c r="N9" s="54">
+        <f>(M7-M9)/M7</f>
         <v>-0.34444444444444439</v>
       </c>
-      <c r="N9" s="15">
+      <c r="O9" s="55">
+        <f t="shared" si="4"/>
+        <v>-34.444444444444436</v>
+      </c>
+      <c r="P9" s="55">
         <v>0.65</v>
       </c>
-      <c r="O9" s="12">
+      <c r="Q9" s="53">
         <v>1</v>
       </c>
-      <c r="P9" s="12">
+      <c r="R9" s="53">
         <v>-160</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="S9" s="53">
         <v>-200</v>
       </c>
-      <c r="R9" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T9" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="57">
         <v>80</v>
       </c>
@@ -1489,1312 +1571,1483 @@
         <f>(J7-J10)/J7</f>
         <v>-0.18750000000000008</v>
       </c>
-      <c r="L10" s="60">
-        <f t="shared" si="3"/>
+      <c r="L10" s="55">
+        <f t="shared" si="3"/>
+        <v>-18.750000000000007</v>
+      </c>
+      <c r="M10" s="60">
+        <f t="shared" si="5"/>
         <v>0.4</v>
       </c>
-      <c r="M10" s="60">
-        <f>(L7-L10)/L7</f>
+      <c r="N10" s="60">
+        <f>(M7-M10)/M7</f>
         <v>0.28888888888888886</v>
       </c>
-      <c r="N10" s="58">
+      <c r="O10" s="55">
+        <f t="shared" si="4"/>
+        <v>28.888888888888886</v>
+      </c>
+      <c r="P10" s="58">
         <v>0.7</v>
       </c>
-      <c r="O10" s="58">
+      <c r="Q10" s="58">
         <v>0.75</v>
       </c>
-      <c r="P10" s="57">
+      <c r="R10" s="57">
         <v>-150</v>
       </c>
-      <c r="Q10" s="57">
+      <c r="S10" s="57">
         <v>-160</v>
       </c>
-      <c r="R10" s="57">
+      <c r="T10" s="57">
         <v>-140</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="12">
+    <row r="11" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="53">
         <v>100</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="53">
         <v>90</v>
       </c>
-      <c r="C11" s="12">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12">
+      <c r="C11" s="53">
+        <v>0</v>
+      </c>
+      <c r="D11" s="53">
         <v>352</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="53">
         <v>355</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="53">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="53">
         <v>305</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="53">
         <v>315</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="56">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="54">
         <f t="shared" si="2"/>
         <v>0.47</v>
       </c>
-      <c r="K11" s="14">
-        <v>0</v>
-      </c>
-      <c r="L11" s="14">
-        <f t="shared" si="3"/>
+      <c r="K11" s="54">
+        <v>0</v>
+      </c>
+      <c r="L11" s="55">
+        <v>0</v>
+      </c>
+      <c r="M11" s="54">
+        <f t="shared" si="5"/>
         <v>0.37</v>
       </c>
-      <c r="M11" s="14">
-        <v>0</v>
-      </c>
-      <c r="N11" s="15">
+      <c r="N11" s="54">
+        <v>0</v>
+      </c>
+      <c r="O11" s="55">
+        <v>0</v>
+      </c>
+      <c r="P11" s="55">
         <v>0.72</v>
       </c>
-      <c r="O11" s="12">
+      <c r="Q11" s="53">
         <v>1</v>
       </c>
-      <c r="P11" s="12">
+      <c r="R11" s="53">
         <v>-130</v>
       </c>
-      <c r="Q11" s="12">
+      <c r="S11" s="53">
         <v>-160</v>
       </c>
-      <c r="R11" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="12">
+      <c r="T11" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="53">
         <v>100</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="53">
         <v>60</v>
       </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
+      <c r="C12" s="53">
+        <v>0</v>
+      </c>
+      <c r="D12" s="53">
         <v>353</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="53">
         <v>358</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="53">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="53">
         <v>306</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="53">
         <v>321</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="56">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="54">
         <f t="shared" si="2"/>
         <v>0.47</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="54">
         <f>(J11-J12)/J11</f>
         <v>0</v>
       </c>
-      <c r="L12" s="14">
-        <f t="shared" si="3"/>
+      <c r="L12" s="55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="54">
+        <f t="shared" si="5"/>
         <v>0.32</v>
       </c>
-      <c r="M12" s="14">
-        <f>(L11-L12)/L11</f>
+      <c r="N12" s="54">
+        <f>(M11-M12)/M11</f>
         <v>0.13513513513513511</v>
       </c>
-      <c r="N12" s="15">
+      <c r="O12" s="55">
+        <f t="shared" si="4"/>
+        <v>13.513513513513512</v>
+      </c>
+      <c r="P12" s="55">
         <v>0.75</v>
       </c>
-      <c r="O12" s="12">
+      <c r="Q12" s="53">
         <v>1</v>
       </c>
-      <c r="P12" s="12">
+      <c r="R12" s="53">
         <v>-120</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="S12" s="53">
         <v>-130</v>
       </c>
-      <c r="R12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
+      <c r="T12" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="53">
         <v>100</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="53">
         <v>30</v>
       </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
+      <c r="C13" s="53">
+        <v>0</v>
+      </c>
+      <c r="D13" s="53">
         <v>346</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="53">
         <v>357</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="53">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="53">
         <v>306</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="53">
         <v>325</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="56">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="54">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="54">
         <f>(J11-J13)/J11</f>
         <v>0.14893617021276587</v>
       </c>
-      <c r="L13" s="14">
-        <f t="shared" si="3"/>
+      <c r="L13" s="55">
+        <f t="shared" si="3"/>
+        <v>14.893617021276587</v>
+      </c>
+      <c r="M13" s="54">
+        <f t="shared" si="5"/>
         <v>0.79</v>
       </c>
-      <c r="M13" s="14">
-        <f>(L11-L13)/L11</f>
+      <c r="N13" s="54">
+        <f>(M11-M13)/M11</f>
         <v>-1.1351351351351353</v>
       </c>
-      <c r="N13" s="15">
+      <c r="O13" s="55">
+        <f t="shared" si="4"/>
+        <v>-113.51351351351353</v>
+      </c>
+      <c r="P13" s="55">
         <v>0.45</v>
       </c>
-      <c r="O13" s="12">
+      <c r="Q13" s="53">
         <v>1</v>
       </c>
-      <c r="P13" s="12">
+      <c r="R13" s="53">
         <v>-250</v>
       </c>
-      <c r="Q13" s="12">
+      <c r="S13" s="53">
         <v>-280</v>
       </c>
-      <c r="R13" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="12">
+      <c r="T13" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="53">
         <v>100</v>
       </c>
-      <c r="B14" s="12">
-        <v>0</v>
-      </c>
-      <c r="C14" s="12">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12">
+      <c r="B14" s="53">
+        <v>0</v>
+      </c>
+      <c r="C14" s="53">
+        <v>0</v>
+      </c>
+      <c r="D14" s="53">
         <v>350</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="53">
         <v>385</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="53">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="53">
         <v>302</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="53">
         <v>306</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="56">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="54">
         <f t="shared" si="2"/>
         <v>0.48</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="54">
         <f>(J11-J14)/J11</f>
         <v>-2.1276595744680871E-2</v>
       </c>
-      <c r="L14" s="14">
-        <f t="shared" si="3"/>
+      <c r="L14" s="55">
+        <f t="shared" si="3"/>
+        <v>-2.1276595744680873</v>
+      </c>
+      <c r="M14" s="54">
+        <f t="shared" si="5"/>
         <v>0.34166666666666667</v>
       </c>
-      <c r="M14" s="14">
-        <f>(L11-L14)/L11</f>
+      <c r="N14" s="54">
+        <f>(M11-M14)/M11</f>
         <v>7.6576576576576544E-2</v>
       </c>
-      <c r="N14" s="15">
+      <c r="O14" s="55">
+        <f t="shared" si="4"/>
+        <v>7.657657657657654</v>
+      </c>
+      <c r="P14" s="55">
         <v>0.67</v>
       </c>
-      <c r="O14" s="15">
+      <c r="Q14" s="55">
         <v>0.69</v>
       </c>
-      <c r="P14" s="12">
+      <c r="R14" s="53">
         <v>-270</v>
       </c>
-      <c r="Q14" s="12">
+      <c r="S14" s="53">
         <v>-370</v>
       </c>
-      <c r="R14" s="12">
+      <c r="T14" s="53">
         <v>-240</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="12">
+    <row r="15" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="53">
         <v>120</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="53">
         <v>90</v>
       </c>
-      <c r="C15" s="12">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12">
+      <c r="C15" s="53">
+        <v>0</v>
+      </c>
+      <c r="D15" s="53">
         <v>353</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="53">
         <v>356</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="53">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="53">
         <v>304</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="53">
         <v>315</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="56">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="54">
         <f t="shared" si="2"/>
         <v>0.40833333333333333</v>
       </c>
-      <c r="K15" s="14">
-        <v>0</v>
-      </c>
-      <c r="L15" s="14">
-        <f t="shared" si="3"/>
+      <c r="K15" s="54">
+        <v>0</v>
+      </c>
+      <c r="L15" s="55">
+        <v>0</v>
+      </c>
+      <c r="M15" s="54">
+        <f t="shared" si="5"/>
         <v>0.35833333333333334</v>
       </c>
-      <c r="M15" s="14">
-        <v>0</v>
-      </c>
-      <c r="N15" s="15">
+      <c r="N15" s="54">
+        <v>0</v>
+      </c>
+      <c r="O15" s="55">
+        <v>0</v>
+      </c>
+      <c r="P15" s="55">
         <v>0.77</v>
       </c>
-      <c r="O15" s="12">
+      <c r="Q15" s="53">
         <v>1</v>
       </c>
-      <c r="P15" s="12">
+      <c r="R15" s="53">
         <v>-100</v>
       </c>
-      <c r="Q15" s="12">
+      <c r="S15" s="53">
         <v>-130</v>
       </c>
-      <c r="R15" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="12">
+      <c r="T15" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="53">
         <v>120</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="53">
         <v>60</v>
       </c>
-      <c r="C16" s="12">
-        <v>0</v>
-      </c>
-      <c r="D16" s="12">
+      <c r="C16" s="53">
+        <v>0</v>
+      </c>
+      <c r="D16" s="53">
         <v>353</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="53">
         <v>356</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="53">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="53">
         <v>307</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="53">
         <v>313</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="56">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="54">
         <f t="shared" si="2"/>
         <v>0.38333333333333336</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="54">
         <f>(J15-J16)/J15</f>
         <v>6.122448979591829E-2</v>
       </c>
-      <c r="L16" s="14">
-        <f t="shared" si="3"/>
+      <c r="L16" s="55">
+        <f t="shared" si="3"/>
+        <v>6.1224489795918293</v>
+      </c>
+      <c r="M16" s="54">
+        <f t="shared" si="5"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="M16" s="14">
-        <f>(L15-L16)/L15</f>
+      <c r="N16" s="54">
+        <f>(M15-M16)/M15</f>
         <v>0.18604651162790695</v>
       </c>
-      <c r="N16" s="15">
+      <c r="O16" s="55">
+        <f t="shared" si="4"/>
+        <v>18.604651162790695</v>
+      </c>
+      <c r="P16" s="55">
         <v>0.8</v>
       </c>
-      <c r="O16" s="12">
+      <c r="Q16" s="53">
         <v>1</v>
       </c>
-      <c r="P16" s="12">
+      <c r="R16" s="53">
         <v>-75</v>
       </c>
-      <c r="Q16" s="12">
+      <c r="S16" s="53">
         <v>-85</v>
       </c>
-      <c r="R16" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="12">
+      <c r="T16" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="53">
         <v>120</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="53">
         <v>30</v>
       </c>
-      <c r="C17" s="12">
-        <v>0</v>
-      </c>
-      <c r="D17" s="12">
+      <c r="C17" s="53">
+        <v>0</v>
+      </c>
+      <c r="D17" s="53">
         <v>348</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="53">
         <v>358</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="53">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="53">
         <v>303</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="53">
         <v>323</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="56">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="54">
         <f t="shared" si="2"/>
         <v>0.375</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="54">
         <f>(J15-J17)/J15</f>
         <v>8.1632653061224469E-2</v>
       </c>
-      <c r="L17" s="14">
-        <f t="shared" si="3"/>
+      <c r="L17" s="55">
+        <f t="shared" si="3"/>
+        <v>8.1632653061224474</v>
+      </c>
+      <c r="M17" s="54">
+        <f t="shared" si="5"/>
         <v>1.2375</v>
       </c>
-      <c r="M17" s="14">
-        <f>(L15-L17)/L15</f>
+      <c r="N17" s="54">
+        <f>(M15-M17)/M15</f>
         <v>-2.4534883720930232</v>
       </c>
-      <c r="N17" s="15">
+      <c r="O17" s="55">
+        <f t="shared" si="4"/>
+        <v>-245.3488372093023</v>
+      </c>
+      <c r="P17" s="55">
         <v>0.6</v>
       </c>
-      <c r="O17" s="12">
+      <c r="Q17" s="53">
         <v>1</v>
       </c>
-      <c r="P17" s="12">
+      <c r="R17" s="53">
         <v>-185</v>
       </c>
-      <c r="Q17" s="12">
+      <c r="S17" s="53">
         <v>-230</v>
       </c>
-      <c r="R17" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="12">
+      <c r="T17" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="53">
         <v>40</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="53">
         <v>90</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="53">
         <v>90</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="53">
         <v>342</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="53">
         <v>355</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="53">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="55">
         <v>304.5</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="55">
         <v>305.5</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="56">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="54">
         <f t="shared" si="2"/>
         <v>0.9375</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="54">
         <f>(J2-J18)/J2</f>
         <v>0.10714285714285718</v>
       </c>
-      <c r="L18" s="14">
-        <f t="shared" ref="L18:L31" si="4">(E18-H18)/A18</f>
+      <c r="L18" s="55">
+        <f t="shared" si="3"/>
+        <v>10.714285714285717</v>
+      </c>
+      <c r="M18" s="54">
+        <f t="shared" ref="M18:M31" si="6">(E18-H18)/A18</f>
         <v>1.2375</v>
       </c>
-      <c r="M18" s="14">
-        <f>(L2-L18)/L2</f>
+      <c r="N18" s="54">
+        <f>(M2-M18)/M2</f>
         <v>-0.33783783783783783</v>
       </c>
-      <c r="N18" s="15">
+      <c r="O18" s="55">
+        <f t="shared" si="4"/>
+        <v>-33.783783783783782</v>
+      </c>
+      <c r="P18" s="55">
         <v>0.5</v>
       </c>
-      <c r="O18" s="15">
+      <c r="Q18" s="55">
         <v>0.57999999999999996</v>
       </c>
-      <c r="P18" s="12">
+      <c r="R18" s="53">
         <v>-220</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="S18" s="53">
         <v>-235</v>
       </c>
-      <c r="R18" s="12">
+      <c r="T18" s="53">
         <v>-225</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="12">
+    <row r="19" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="53">
         <v>40</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="53">
         <v>90</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="53">
         <v>60</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="53">
         <v>347</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="53">
         <v>352</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="53">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="53">
         <v>305</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="53">
         <v>307</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="56">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="54">
         <f t="shared" si="2"/>
         <v>1.05</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="54">
         <f>(J2-J19)/J2</f>
         <v>0</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="54">
+        <f t="shared" si="6"/>
+        <v>1.125</v>
+      </c>
+      <c r="N19" s="54">
+        <f>(M2-M19)/M2</f>
+        <v>-0.21621621621621614</v>
+      </c>
+      <c r="O19" s="55">
         <f t="shared" si="4"/>
+        <v>-21.621621621621614</v>
+      </c>
+      <c r="P19" s="55">
+        <v>0.6</v>
+      </c>
+      <c r="Q19" s="55">
+        <v>0.72</v>
+      </c>
+      <c r="R19" s="53">
+        <v>-175</v>
+      </c>
+      <c r="S19" s="53">
+        <v>-190</v>
+      </c>
+      <c r="T19" s="53">
+        <v>-120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="53">
+        <v>40</v>
+      </c>
+      <c r="B20" s="53">
+        <v>90</v>
+      </c>
+      <c r="C20" s="53">
+        <v>30</v>
+      </c>
+      <c r="D20" s="53">
+        <v>350</v>
+      </c>
+      <c r="E20" s="53">
+        <v>354</v>
+      </c>
+      <c r="F20" s="53">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G20" s="53">
+        <v>305</v>
+      </c>
+      <c r="H20" s="53">
+        <v>306</v>
+      </c>
+      <c r="I20" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J20" s="54">
+        <f t="shared" si="2"/>
         <v>1.125</v>
       </c>
-      <c r="M19" s="14">
-        <f>(L2-L19)/L2</f>
-        <v>-0.21621621621621614</v>
-      </c>
-      <c r="N19" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="O19" s="15">
-        <v>0.72</v>
-      </c>
-      <c r="P19" s="12">
-        <v>-175</v>
-      </c>
-      <c r="Q19" s="12">
-        <v>-190</v>
-      </c>
-      <c r="R19" s="12">
-        <v>-120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="12">
-        <v>40</v>
-      </c>
-      <c r="B20" s="12">
-        <v>90</v>
-      </c>
-      <c r="C20" s="12">
-        <v>30</v>
-      </c>
-      <c r="D20" s="12">
-        <v>350</v>
-      </c>
-      <c r="E20" s="12">
-        <v>354</v>
-      </c>
-      <c r="F20" s="12">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G20" s="12">
-        <v>305</v>
-      </c>
-      <c r="H20" s="12">
-        <v>306</v>
-      </c>
-      <c r="I20" s="13">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J20" s="14">
-        <f t="shared" si="2"/>
-        <v>1.125</v>
-      </c>
-      <c r="K20" s="14">
+      <c r="K20" s="54">
         <f>(J2-J20)/J2</f>
         <v>-7.1428571428571383E-2</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="55">
+        <f t="shared" si="3"/>
+        <v>-7.1428571428571379</v>
+      </c>
+      <c r="M20" s="54">
+        <f t="shared" si="6"/>
+        <v>1.2</v>
+      </c>
+      <c r="N20" s="54">
+        <f>(M2-M20)/M2</f>
+        <v>-0.2972972972972972</v>
+      </c>
+      <c r="O20" s="55">
         <f t="shared" si="4"/>
-        <v>1.2</v>
-      </c>
-      <c r="M20" s="14">
-        <f>(L2-L20)/L2</f>
-        <v>-0.2972972972972972</v>
-      </c>
-      <c r="N20" s="15">
+        <v>-29.729729729729719</v>
+      </c>
+      <c r="P20" s="55">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O20" s="15">
+      <c r="Q20" s="55">
         <v>0.6</v>
       </c>
-      <c r="P20" s="12">
+      <c r="R20" s="53">
         <v>-230</v>
       </c>
-      <c r="Q20" s="12">
+      <c r="S20" s="53">
         <v>-240</v>
       </c>
-      <c r="R20" s="12">
+      <c r="T20" s="53">
         <v>-220</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="12">
+    <row r="21" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="53">
         <v>60</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="53">
         <v>90</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="53">
         <v>90</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="53">
         <v>345</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="53">
         <v>368</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="53">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="55">
         <v>304.5</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="55">
         <v>307.5</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="56">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="54">
         <f t="shared" si="2"/>
         <v>0.67500000000000004</v>
       </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14">
+      <c r="K21" s="54"/>
+      <c r="L21" s="55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="54">
+        <f t="shared" si="6"/>
+        <v>1.0083333333333333</v>
+      </c>
+      <c r="N21" s="54"/>
+      <c r="O21" s="55">
         <f t="shared" si="4"/>
-        <v>1.0083333333333333</v>
-      </c>
-      <c r="M21" s="14"/>
-      <c r="N21" s="15">
+        <v>0</v>
+      </c>
+      <c r="P21" s="55">
         <v>0.62</v>
       </c>
-      <c r="O21" s="15">
+      <c r="Q21" s="55">
         <v>0.8</v>
       </c>
-      <c r="P21" s="12">
+      <c r="R21" s="53">
         <v>-155</v>
       </c>
-      <c r="Q21" s="12">
+      <c r="S21" s="53">
         <v>-175</v>
       </c>
-      <c r="R21" s="12">
+      <c r="T21" s="53">
         <v>-90</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="12">
+    <row r="22" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="53">
         <v>60</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="53">
         <v>90</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="53">
         <v>60</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="53">
         <v>342</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="53">
         <v>351</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="53">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="53">
         <v>305</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="53">
         <v>320</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="56">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="54">
         <f t="shared" si="2"/>
         <v>0.6166666666666667</v>
       </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14">
+      <c r="K22" s="54"/>
+      <c r="L22" s="55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="54">
+        <f t="shared" si="6"/>
+        <v>0.51666666666666672</v>
+      </c>
+      <c r="N22" s="54"/>
+      <c r="O22" s="55">
         <f t="shared" si="4"/>
-        <v>0.51666666666666672</v>
-      </c>
-      <c r="M22" s="14"/>
-      <c r="N22" s="15">
+        <v>0</v>
+      </c>
+      <c r="P22" s="55">
         <v>0.5</v>
       </c>
-      <c r="O22" s="15">
+      <c r="Q22" s="55">
         <v>0.74</v>
       </c>
-      <c r="P22" s="12">
+      <c r="R22" s="53">
         <v>-220</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="S22" s="53">
         <v>-225</v>
       </c>
-      <c r="R22" s="12">
+      <c r="T22" s="53">
         <v>-75</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="12">
+    <row r="23" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="53">
         <v>60</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="53">
         <v>90</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="53">
         <v>30</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="53">
         <v>351</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="53">
         <v>354</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="53">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="53">
         <v>307</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="53">
         <v>319</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="56">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="54">
         <f t="shared" si="2"/>
         <v>0.73333333333333328</v>
       </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14">
+      <c r="K23" s="54"/>
+      <c r="L23" s="55">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="54">
+        <f t="shared" si="6"/>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="N23" s="54"/>
+      <c r="O23" s="55">
         <f t="shared" si="4"/>
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="M23" s="14"/>
-      <c r="N23" s="15">
+        <v>0</v>
+      </c>
+      <c r="P23" s="55">
         <v>0.68</v>
       </c>
-      <c r="O23" s="15">
+      <c r="Q23" s="55">
         <v>0.78</v>
       </c>
-      <c r="P23" s="12">
+      <c r="R23" s="53">
         <v>-130</v>
       </c>
-      <c r="Q23" s="12">
+      <c r="S23" s="53">
         <v>-260</v>
       </c>
-      <c r="R23" s="12">
+      <c r="T23" s="53">
         <v>-70</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="12">
+    <row r="24" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="53">
         <v>80</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="53">
         <v>90</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="53">
         <v>60</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="53">
         <v>348</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="53">
         <v>360</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="53">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="53">
         <v>304</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="53">
         <v>329</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="56">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="54">
         <f t="shared" si="2"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="54">
         <f>(J7-J24)/J7</f>
         <v>8.3333333333333232E-2</v>
       </c>
-      <c r="L24" s="14">
+      <c r="L24" s="55">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333233</v>
+      </c>
+      <c r="M24" s="54">
+        <f t="shared" si="6"/>
+        <v>0.38750000000000001</v>
+      </c>
+      <c r="N24" s="54">
+        <f>(M7-M24)/M7</f>
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="O24" s="55">
         <f t="shared" si="4"/>
-        <v>0.38750000000000001</v>
-      </c>
-      <c r="M24" s="14">
-        <f>(L7-L24)/L7</f>
-        <v>0.31111111111111112</v>
-      </c>
-      <c r="N24" s="15">
+        <v>31.111111111111111</v>
+      </c>
+      <c r="P24" s="55">
         <v>0.62</v>
       </c>
-      <c r="O24" s="12">
+      <c r="Q24" s="53">
         <v>1</v>
       </c>
-      <c r="P24" s="12">
+      <c r="R24" s="53">
         <v>-160</v>
       </c>
-      <c r="Q24" s="12">
+      <c r="S24" s="53">
         <v>-230</v>
       </c>
-      <c r="R24" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="12">
+      <c r="T24" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="53">
         <v>80</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="53">
         <v>90</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="53">
         <v>30</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="53">
         <v>346</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="53">
         <v>354</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="53">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="53">
         <v>304</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="53">
         <v>326</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="56">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="54">
         <f t="shared" si="2"/>
         <v>0.52500000000000002</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="54">
         <f>(J7-J25)/J7</f>
         <v>0.12499999999999993</v>
       </c>
-      <c r="L25" s="14">
+      <c r="L25" s="55">
+        <f t="shared" si="3"/>
+        <v>12.499999999999993</v>
+      </c>
+      <c r="M25" s="54">
+        <f t="shared" si="6"/>
+        <v>0.35</v>
+      </c>
+      <c r="N25" s="54">
+        <f>(M7-M25)/M7</f>
+        <v>0.37777777777777782</v>
+      </c>
+      <c r="O25" s="55">
         <f t="shared" si="4"/>
-        <v>0.35</v>
-      </c>
-      <c r="M25" s="14">
-        <f>(L7-L25)/L7</f>
-        <v>0.37777777777777782</v>
-      </c>
-      <c r="N25" s="15">
+        <v>37.777777777777786</v>
+      </c>
+      <c r="P25" s="55">
         <v>0.46</v>
       </c>
-      <c r="O25" s="15">
+      <c r="Q25" s="55">
         <v>0.92</v>
       </c>
-      <c r="P25" s="12">
+      <c r="R25" s="53">
         <v>-255</v>
       </c>
-      <c r="Q25" s="12">
+      <c r="S25" s="53">
         <v>-300</v>
       </c>
-      <c r="R25" s="12">
+      <c r="T25" s="53">
         <v>-20</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="12">
+    <row r="26" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="53">
         <v>100</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="53">
         <v>90</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="53">
         <v>90</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="53">
         <v>352</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="53">
         <v>374</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="53">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="53">
         <v>306</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="53">
         <v>308</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="56">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="54">
         <f t="shared" si="2"/>
         <v>0.46</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="54">
         <f>(J11-J26)/J11</f>
         <v>2.1276595744680753E-2</v>
       </c>
-      <c r="L26" s="14">
+      <c r="L26" s="55">
+        <f t="shared" si="3"/>
+        <v>2.1276595744680753</v>
+      </c>
+      <c r="M26" s="54">
+        <f t="shared" si="6"/>
+        <v>0.66</v>
+      </c>
+      <c r="N26" s="54">
+        <f>(M11-M26)/M11</f>
+        <v>-0.78378378378378388</v>
+      </c>
+      <c r="O26" s="55">
         <f t="shared" si="4"/>
-        <v>0.66</v>
-      </c>
-      <c r="M26" s="14">
-        <f>(L11-L26)/L11</f>
-        <v>-0.78378378378378388</v>
-      </c>
-      <c r="N26" s="15">
+        <v>-78.378378378378386</v>
+      </c>
+      <c r="P26" s="55">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O26" s="12">
+      <c r="Q26" s="53">
         <v>1</v>
       </c>
-      <c r="P26" s="12">
+      <c r="R26" s="53">
         <v>-150</v>
       </c>
-      <c r="Q26" s="12">
+      <c r="S26" s="53">
         <v>-170</v>
       </c>
-      <c r="R26" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="12">
+      <c r="T26" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="53">
         <v>100</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="53">
         <v>90</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="53">
         <v>60</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="53">
         <v>341</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="53">
         <v>357</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="53">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="53">
         <v>302</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="53">
         <v>330</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="56">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="54">
         <f t="shared" si="2"/>
         <v>0.39</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="54">
         <f>(J11-J27)/J11</f>
         <v>0.17021276595744672</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="55">
+        <f t="shared" si="3"/>
+        <v>17.021276595744673</v>
+      </c>
+      <c r="M27" s="54">
+        <f t="shared" si="6"/>
+        <v>0.27</v>
+      </c>
+      <c r="N27" s="54">
+        <f>(M11-M27)/M11</f>
+        <v>0.27027027027027023</v>
+      </c>
+      <c r="O27" s="55">
         <f t="shared" si="4"/>
-        <v>0.27</v>
-      </c>
-      <c r="M27" s="14">
-        <f>(L11-L27)/L11</f>
-        <v>0.27027027027027023</v>
-      </c>
-      <c r="N27" s="15">
+        <v>27.027027027027025</v>
+      </c>
+      <c r="P27" s="55">
         <v>0.48</v>
       </c>
-      <c r="O27" s="12">
+      <c r="Q27" s="53">
         <v>1</v>
       </c>
-      <c r="P27" s="12">
+      <c r="R27" s="53">
         <v>-220</v>
       </c>
-      <c r="Q27" s="12">
+      <c r="S27" s="53">
         <v>-250</v>
       </c>
-      <c r="R27" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="12">
+      <c r="T27" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="53">
         <v>100</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="53">
         <v>90</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="53">
         <v>30</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="53">
         <v>346</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="53">
         <v>355</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="53">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="53">
         <v>306</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="53">
         <v>329</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="56">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="54">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="54">
         <f>(J11-J28)/J11</f>
         <v>0.14893617021276587</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="55">
+        <f t="shared" si="3"/>
+        <v>14.893617021276587</v>
+      </c>
+      <c r="M28" s="54">
+        <f t="shared" si="6"/>
+        <v>0.26</v>
+      </c>
+      <c r="N28" s="54">
+        <f>(M11-M28)/M11</f>
+        <v>0.29729729729729726</v>
+      </c>
+      <c r="O28" s="55">
         <f t="shared" si="4"/>
-        <v>0.26</v>
-      </c>
-      <c r="M28" s="14">
-        <f>(L11-L28)/L11</f>
-        <v>0.29729729729729726</v>
-      </c>
-      <c r="N28" s="15">
+        <v>29.729729729729726</v>
+      </c>
+      <c r="P28" s="55">
         <v>0.6</v>
       </c>
-      <c r="O28" s="12">
+      <c r="Q28" s="53">
         <v>1</v>
       </c>
-      <c r="P28" s="12">
+      <c r="R28" s="53">
         <v>-150</v>
       </c>
-      <c r="Q28" s="12">
+      <c r="S28" s="53">
         <v>-210</v>
       </c>
-      <c r="R28" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="12">
+      <c r="T28" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="53">
         <v>120</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="53">
         <v>90</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="53">
         <v>90</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="53">
         <v>354</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="53">
         <v>370</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="53">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="53">
         <v>304</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="53">
         <v>314</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="56">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="54">
         <f t="shared" si="2"/>
         <v>0.41666666666666669</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="54">
         <f>(J15-J29)/J15</f>
         <v>-2.0408163265306187E-2</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="55">
+        <f t="shared" si="3"/>
+        <v>-2.0408163265306185</v>
+      </c>
+      <c r="M29" s="54">
+        <f t="shared" si="6"/>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="N29" s="54">
+        <f>(M15-M29)/M15</f>
+        <v>-0.30232558139534882</v>
+      </c>
+      <c r="O29" s="55">
         <f t="shared" si="4"/>
-        <v>0.46666666666666667</v>
-      </c>
-      <c r="M29" s="14">
-        <f>(L15-L29)/L15</f>
-        <v>-0.30232558139534882</v>
-      </c>
-      <c r="N29" s="15">
+        <v>-30.232558139534881</v>
+      </c>
+      <c r="P29" s="55">
         <v>0.6</v>
       </c>
-      <c r="O29" s="12">
+      <c r="Q29" s="53">
         <v>1</v>
       </c>
-      <c r="P29" s="12">
+      <c r="R29" s="53">
         <v>215</v>
       </c>
-      <c r="Q29" s="12">
+      <c r="S29" s="53">
         <v>-230</v>
       </c>
-      <c r="R29" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="12">
+      <c r="T29" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="53">
         <v>120</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="53">
         <v>90</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="53">
         <v>60</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="53">
         <v>342</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="53">
         <v>355</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="53">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="53">
         <v>302</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="53">
         <v>330</v>
       </c>
-      <c r="I30" s="13">
+      <c r="I30" s="56">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="54">
         <f t="shared" si="2"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="54">
         <f>(J15-J30)/J15</f>
         <v>0.18367346938775514</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="55">
+        <f t="shared" si="3"/>
+        <v>18.367346938775515</v>
+      </c>
+      <c r="M30" s="54">
+        <f t="shared" si="6"/>
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="N30" s="54">
+        <f>(M15-M30)/M15</f>
+        <v>0.41860465116279066</v>
+      </c>
+      <c r="O30" s="55">
         <f t="shared" si="4"/>
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="M30" s="14">
-        <f>(L15-L30)/L15</f>
-        <v>0.41860465116279066</v>
-      </c>
-      <c r="N30" s="15">
+        <v>41.860465116279066</v>
+      </c>
+      <c r="P30" s="55">
         <v>0.54</v>
       </c>
-      <c r="O30" s="12">
+      <c r="Q30" s="53">
         <v>1</v>
       </c>
-      <c r="P30" s="12">
+      <c r="R30" s="53">
         <v>-215</v>
       </c>
-      <c r="Q30" s="12">
+      <c r="S30" s="53">
         <v>-230</v>
       </c>
-      <c r="R30" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="12">
+      <c r="T30" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="53">
         <v>120</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="53">
         <v>90</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="53">
         <v>30</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="53">
         <v>343</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="53">
         <v>355</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="53">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="53">
         <v>304</v>
       </c>
-      <c r="H31" s="12">
+      <c r="H31" s="53">
         <v>327</v>
       </c>
-      <c r="I31" s="13">
+      <c r="I31" s="56">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="54">
         <f t="shared" si="2"/>
         <v>0.32500000000000001</v>
       </c>
-      <c r="K31" s="14">
+      <c r="K31" s="54">
         <f>(J15-J31)/J15</f>
         <v>0.20408163265306117</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="55">
+        <f t="shared" si="3"/>
+        <v>20.408163265306118</v>
+      </c>
+      <c r="M31" s="54">
+        <f t="shared" si="6"/>
+        <v>0.23333333333333334</v>
+      </c>
+      <c r="N31" s="54">
+        <f>(M15-M31)/M15</f>
+        <v>0.34883720930232559</v>
+      </c>
+      <c r="O31" s="55">
         <f t="shared" si="4"/>
-        <v>0.23333333333333334</v>
-      </c>
-      <c r="M31" s="14">
-        <f>(L15-L31)/L15</f>
-        <v>0.34883720930232559</v>
-      </c>
-      <c r="N31" s="15">
+        <v>34.883720930232556</v>
+      </c>
+      <c r="P31" s="55">
         <v>0.52</v>
       </c>
-      <c r="O31" s="12">
+      <c r="Q31" s="53">
         <v>1</v>
       </c>
-      <c r="P31" s="12">
+      <c r="R31" s="53">
         <v>-200</v>
       </c>
-      <c r="Q31" s="12">
+      <c r="S31" s="53">
         <v>-250</v>
       </c>
-      <c r="R31" s="12">
+      <c r="T31" s="53">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1" xr:uid="{BC3F519D-1E72-4C40-A9EB-D73907B1CA29}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/observation_alpha_beta.xlsx
+++ b/data/observation_alpha_beta.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/58033850cf77e637/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phd\php_pulsating_heat_pipe\Krp_Analysis\Advanced_PulseHeatPipe_krp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEEFA822-9600-45A4-8730-889827C4070E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE050A59-0AA2-43C9-9235-D380B1992CA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18200" windowHeight="8510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/observation_alpha_beta.xlsx
+++ b/data/observation_alpha_beta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phd\php_pulsating_heat_pipe\Krp_Analysis\Advanced_PulseHeatPipe_krp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE050A59-0AA2-43C9-9235-D380B1992CA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC9E0F1-BBD3-4453-A86D-081082238606}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18200" windowHeight="8510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1234,19 +1234,13 @@
         <v>0.78333333333333333</v>
       </c>
       <c r="K5" s="54"/>
-      <c r="L5" s="55">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L5" s="55"/>
       <c r="M5" s="54">
         <f t="shared" ref="M5:M17" si="5">(E6-H6)/A6</f>
         <v>0.6333333333333333</v>
       </c>
       <c r="N5" s="54"/>
-      <c r="O5" s="55">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="O5" s="55"/>
       <c r="P5" s="55">
         <v>0.65</v>
       </c>
@@ -1298,19 +1292,13 @@
         <v>0.75</v>
       </c>
       <c r="K6" s="54"/>
-      <c r="L6" s="55">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L6" s="55"/>
       <c r="M6" s="54">
         <f t="shared" si="5"/>
         <v>0.4375</v>
       </c>
       <c r="N6" s="54"/>
-      <c r="O6" s="55">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="O6" s="55"/>
       <c r="P6" s="55">
         <v>0.75</v>
       </c>
@@ -2330,19 +2318,13 @@
         <v>0.67500000000000004</v>
       </c>
       <c r="K21" s="54"/>
-      <c r="L21" s="55">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L21" s="55"/>
       <c r="M21" s="54">
         <f t="shared" si="6"/>
         <v>1.0083333333333333</v>
       </c>
       <c r="N21" s="54"/>
-      <c r="O21" s="55">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="O21" s="55"/>
       <c r="P21" s="55">
         <v>0.62</v>
       </c>
@@ -2394,19 +2376,13 @@
         <v>0.6166666666666667</v>
       </c>
       <c r="K22" s="54"/>
-      <c r="L22" s="55">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L22" s="55"/>
       <c r="M22" s="54">
         <f t="shared" si="6"/>
         <v>0.51666666666666672</v>
       </c>
       <c r="N22" s="54"/>
-      <c r="O22" s="55">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="O22" s="55"/>
       <c r="P22" s="55">
         <v>0.5</v>
       </c>
@@ -2458,19 +2434,13 @@
         <v>0.73333333333333328</v>
       </c>
       <c r="K23" s="54"/>
-      <c r="L23" s="55">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L23" s="55"/>
       <c r="M23" s="54">
         <f t="shared" si="6"/>
         <v>0.58333333333333337</v>
       </c>
       <c r="N23" s="54"/>
-      <c r="O23" s="55">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="O23" s="55"/>
       <c r="P23" s="55">
         <v>0.68</v>
       </c>

--- a/data/observation_alpha_beta.xlsx
+++ b/data/observation_alpha_beta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phd\php_pulsating_heat_pipe\Krp_Analysis\Advanced_PulseHeatPipe_krp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC9E0F1-BBD3-4453-A86D-081082238606}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBBCA33-E16F-472A-A796-78673E6338E9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="60" windowWidth="18200" windowHeight="8510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,7 +103,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +122,13 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -427,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -507,15 +514,9 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -525,9 +526,6 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -566,9 +564,6 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -607,6 +602,34 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,20 +938,20 @@
   <dimension ref="A1:T31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="9" style="49" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" style="50" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.453125" style="50" customWidth="1"/>
-    <col min="13" max="13" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.26953125" style="50" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.26953125" style="50" customWidth="1"/>
-    <col min="16" max="16" width="8.54296875" style="51" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="8.54296875" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="9" style="45" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" style="45" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.26953125" style="46" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" style="46" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.453125" style="46" customWidth="1"/>
+    <col min="13" max="13" width="10.26953125" style="46" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.26953125" style="46" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.26953125" style="46" customWidth="1"/>
+    <col min="16" max="16" width="8.54296875" style="47" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.54296875" style="45" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.81640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.54296875" style="45" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.81640625" style="45" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -994,2026 +1017,2026 @@
       </c>
     </row>
     <row r="2" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="53">
+      <c r="A2" s="49">
         <v>40</v>
       </c>
-      <c r="B2" s="53">
+      <c r="B2" s="49">
         <v>90</v>
       </c>
-      <c r="C2" s="53">
-        <v>0</v>
-      </c>
-      <c r="D2" s="53">
+      <c r="C2" s="49">
+        <v>0</v>
+      </c>
+      <c r="D2" s="49">
         <v>348</v>
       </c>
-      <c r="E2" s="53">
+      <c r="E2" s="49">
         <v>352</v>
       </c>
-      <c r="F2" s="53">
+      <c r="F2" s="49">
         <f t="shared" ref="F2:F31" si="0">(E2-D2)</f>
         <v>4</v>
       </c>
-      <c r="G2" s="53">
+      <c r="G2" s="49">
         <v>306</v>
       </c>
-      <c r="H2" s="53">
+      <c r="H2" s="49">
         <v>315</v>
       </c>
-      <c r="I2" s="53">
+      <c r="I2" s="49">
         <f t="shared" ref="I2:I31" si="1">(H2-G2)</f>
         <v>9</v>
       </c>
-      <c r="J2" s="54">
+      <c r="J2" s="50">
         <f t="shared" ref="J2:J31" si="2">(D2-G2)/A2</f>
         <v>1.05</v>
       </c>
-      <c r="K2" s="55">
-        <v>0</v>
-      </c>
-      <c r="L2" s="55">
-        <v>0</v>
-      </c>
-      <c r="M2" s="54">
+      <c r="K2" s="51">
+        <v>0</v>
+      </c>
+      <c r="L2" s="51">
+        <v>0</v>
+      </c>
+      <c r="M2" s="50">
         <f>(E2-H2)/A2</f>
         <v>0.92500000000000004</v>
       </c>
-      <c r="N2" s="55">
-        <v>0</v>
-      </c>
-      <c r="O2" s="55">
-        <v>0</v>
-      </c>
-      <c r="P2" s="55">
+      <c r="N2" s="51">
+        <v>0</v>
+      </c>
+      <c r="O2" s="51">
+        <v>0</v>
+      </c>
+      <c r="P2" s="51">
         <v>0.62</v>
       </c>
-      <c r="Q2" s="55">
+      <c r="Q2" s="51">
         <v>0.75</v>
       </c>
-      <c r="R2" s="53">
+      <c r="R2" s="49">
         <v>-155</v>
       </c>
-      <c r="S2" s="53">
+      <c r="S2" s="49">
         <v>-190</v>
       </c>
-      <c r="T2" s="53">
+      <c r="T2" s="49">
         <v>-100</v>
       </c>
     </row>
     <row r="3" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="53">
+      <c r="A3" s="49">
         <v>40</v>
       </c>
-      <c r="B3" s="53">
+      <c r="B3" s="49">
         <v>60</v>
       </c>
-      <c r="C3" s="53">
-        <v>0</v>
-      </c>
-      <c r="D3" s="53">
+      <c r="C3" s="49">
+        <v>0</v>
+      </c>
+      <c r="D3" s="49">
         <v>349</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="49">
         <v>357</v>
       </c>
-      <c r="F3" s="53">
+      <c r="F3" s="49">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G3" s="53">
+      <c r="G3" s="49">
         <v>304</v>
       </c>
-      <c r="H3" s="53">
+      <c r="H3" s="49">
         <v>305</v>
       </c>
-      <c r="I3" s="56">
+      <c r="I3" s="52">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J3" s="54">
+      <c r="J3" s="50">
         <f t="shared" si="2"/>
         <v>1.125</v>
       </c>
-      <c r="K3" s="54">
+      <c r="K3" s="50">
         <f>(J2-J3)/J2</f>
         <v>-7.1428571428571383E-2</v>
       </c>
-      <c r="L3" s="55">
+      <c r="L3" s="51">
         <f t="shared" ref="L3:L31" si="3">K3*100</f>
         <v>-7.1428571428571379</v>
       </c>
-      <c r="M3" s="54">
+      <c r="M3" s="50">
         <f>(E3-H3)/A3</f>
         <v>1.3</v>
       </c>
-      <c r="N3" s="54">
+      <c r="N3" s="50">
         <f>(M2-M3)/M2</f>
         <v>-0.40540540540540537</v>
       </c>
-      <c r="O3" s="55">
+      <c r="O3" s="51">
         <f t="shared" ref="O3:O31" si="4">N3*100</f>
         <v>-40.54054054054054</v>
       </c>
-      <c r="P3" s="55">
+      <c r="P3" s="51">
         <v>0.7</v>
       </c>
-      <c r="Q3" s="55">
+      <c r="Q3" s="51">
         <v>0.8</v>
       </c>
-      <c r="R3" s="53">
+      <c r="R3" s="49">
         <v>-140</v>
       </c>
-      <c r="S3" s="53">
+      <c r="S3" s="49">
         <v>-160</v>
       </c>
-      <c r="T3" s="55">
+      <c r="T3" s="51">
         <v>-0.85</v>
       </c>
     </row>
     <row r="4" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="53">
+      <c r="A4" s="49">
         <v>40</v>
       </c>
-      <c r="B4" s="53">
+      <c r="B4" s="49">
         <v>30</v>
       </c>
-      <c r="C4" s="53">
-        <v>0</v>
-      </c>
-      <c r="D4" s="53">
+      <c r="C4" s="49">
+        <v>0</v>
+      </c>
+      <c r="D4" s="49">
         <v>349</v>
       </c>
-      <c r="E4" s="55">
+      <c r="E4" s="51">
         <v>358.5</v>
       </c>
-      <c r="F4" s="55">
+      <c r="F4" s="51">
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="G4" s="53">
+      <c r="G4" s="49">
         <v>304</v>
       </c>
-      <c r="H4" s="53">
+      <c r="H4" s="49">
         <v>306</v>
       </c>
-      <c r="I4" s="56">
+      <c r="I4" s="52">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J4" s="54">
+      <c r="J4" s="50">
         <f t="shared" si="2"/>
         <v>1.125</v>
       </c>
-      <c r="K4" s="54">
+      <c r="K4" s="50">
         <f>(J2-J4)/J2</f>
         <v>-7.1428571428571383E-2</v>
       </c>
-      <c r="L4" s="55">
+      <c r="L4" s="51">
         <f t="shared" si="3"/>
         <v>-7.1428571428571379</v>
       </c>
-      <c r="M4" s="54">
+      <c r="M4" s="50">
         <f>(E4-H4)/A4</f>
         <v>1.3125</v>
       </c>
-      <c r="N4" s="54">
+      <c r="N4" s="50">
         <f>(M2-M4)/M2</f>
         <v>-0.41891891891891886</v>
       </c>
-      <c r="O4" s="55">
+      <c r="O4" s="51">
         <f t="shared" si="4"/>
         <v>-41.891891891891888</v>
       </c>
-      <c r="P4" s="55">
+      <c r="P4" s="51">
         <v>0.7</v>
       </c>
-      <c r="Q4" s="55">
+      <c r="Q4" s="51">
         <v>0.83</v>
       </c>
-      <c r="R4" s="53">
+      <c r="R4" s="49">
         <v>-130</v>
       </c>
-      <c r="S4" s="53">
+      <c r="S4" s="49">
         <v>-150</v>
       </c>
-      <c r="T4" s="53">
+      <c r="T4" s="49">
         <v>-90</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="53">
+      <c r="A5" s="49">
         <v>60</v>
       </c>
-      <c r="B5" s="53">
+      <c r="B5" s="49">
         <v>60</v>
       </c>
-      <c r="C5" s="53">
-        <v>0</v>
-      </c>
-      <c r="D5" s="53">
+      <c r="C5" s="49">
+        <v>0</v>
+      </c>
+      <c r="D5" s="49">
         <v>350</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="49">
         <v>355</v>
       </c>
-      <c r="F5" s="53">
+      <c r="F5" s="49">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G5" s="53">
+      <c r="G5" s="49">
         <v>303</v>
       </c>
-      <c r="H5" s="53">
+      <c r="H5" s="49">
         <v>319</v>
       </c>
-      <c r="I5" s="56">
+      <c r="I5" s="52">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="J5" s="54">
+      <c r="J5" s="50">
         <f t="shared" si="2"/>
         <v>0.78333333333333333</v>
       </c>
-      <c r="K5" s="54"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="54">
+      <c r="K5" s="50"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="50">
         <f t="shared" ref="M5:M17" si="5">(E6-H6)/A6</f>
         <v>0.6333333333333333</v>
       </c>
-      <c r="N5" s="54"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55">
+      <c r="N5" s="50"/>
+      <c r="O5" s="51"/>
+      <c r="P5" s="51">
         <v>0.65</v>
       </c>
-      <c r="Q5" s="53">
+      <c r="Q5" s="49">
         <v>1</v>
       </c>
-      <c r="R5" s="53">
+      <c r="R5" s="49">
         <v>-160</v>
       </c>
-      <c r="S5" s="53">
+      <c r="S5" s="49">
         <v>-180</v>
       </c>
-      <c r="T5" s="53">
+      <c r="T5" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="53">
+      <c r="A6" s="49">
         <v>60</v>
       </c>
-      <c r="B6" s="53">
+      <c r="B6" s="49">
         <v>30</v>
       </c>
-      <c r="C6" s="53">
-        <v>0</v>
-      </c>
-      <c r="D6" s="53">
+      <c r="C6" s="49">
+        <v>0</v>
+      </c>
+      <c r="D6" s="49">
         <v>350</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="49">
         <v>359</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F6" s="49">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="49">
         <v>305</v>
       </c>
-      <c r="H6" s="53">
+      <c r="H6" s="49">
         <v>321</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="52">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="50">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="K6" s="54"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="54">
+      <c r="K6" s="50"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="50">
         <f t="shared" si="5"/>
         <v>0.4375</v>
       </c>
-      <c r="N6" s="54"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="55">
+      <c r="N6" s="50"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="51">
         <v>0.75</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="49">
         <v>1</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="49">
         <v>-120</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="49">
         <v>-150</v>
       </c>
-      <c r="T6" s="53">
+      <c r="T6" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="53">
+      <c r="A7" s="49">
         <v>80</v>
       </c>
-      <c r="B7" s="53">
+      <c r="B7" s="49">
         <v>90</v>
       </c>
-      <c r="C7" s="53">
-        <v>0</v>
-      </c>
-      <c r="D7" s="53">
+      <c r="C7" s="49">
+        <v>0</v>
+      </c>
+      <c r="D7" s="49">
         <v>350</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="49">
         <v>355</v>
       </c>
-      <c r="F7" s="53">
+      <c r="F7" s="49">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G7" s="53">
+      <c r="G7" s="49">
         <v>302</v>
       </c>
-      <c r="H7" s="53">
+      <c r="H7" s="49">
         <v>320</v>
       </c>
-      <c r="I7" s="56">
+      <c r="I7" s="52">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="J7" s="54">
+      <c r="J7" s="50">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="K7" s="55">
-        <v>0</v>
-      </c>
-      <c r="L7" s="55">
-        <v>0</v>
-      </c>
-      <c r="M7" s="54">
+      <c r="K7" s="51">
+        <v>0</v>
+      </c>
+      <c r="L7" s="51">
+        <v>0</v>
+      </c>
+      <c r="M7" s="50">
         <f t="shared" si="5"/>
         <v>0.5625</v>
       </c>
-      <c r="N7" s="55">
-        <v>0</v>
-      </c>
-      <c r="O7" s="55">
-        <v>0</v>
-      </c>
-      <c r="P7" s="55">
+      <c r="N7" s="51">
+        <v>0</v>
+      </c>
+      <c r="O7" s="51">
+        <v>0</v>
+      </c>
+      <c r="P7" s="51">
         <v>0.75</v>
       </c>
-      <c r="Q7" s="53">
+      <c r="Q7" s="49">
         <v>1</v>
       </c>
-      <c r="R7" s="53">
+      <c r="R7" s="49">
         <v>-125</v>
       </c>
-      <c r="S7" s="53">
+      <c r="S7" s="49">
         <v>-150</v>
       </c>
-      <c r="T7" s="53">
+      <c r="T7" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="53">
+      <c r="A8" s="49">
         <v>80</v>
       </c>
-      <c r="B8" s="53">
+      <c r="B8" s="49">
         <v>60</v>
       </c>
-      <c r="C8" s="53">
-        <v>0</v>
-      </c>
-      <c r="D8" s="53">
+      <c r="C8" s="49">
+        <v>0</v>
+      </c>
+      <c r="D8" s="49">
         <v>355</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="49">
         <v>358</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="49">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="49">
         <v>305</v>
       </c>
-      <c r="H8" s="53">
+      <c r="H8" s="49">
         <v>313</v>
       </c>
-      <c r="I8" s="56">
+      <c r="I8" s="52">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="J8" s="54">
+      <c r="J8" s="50">
         <f t="shared" si="2"/>
         <v>0.625</v>
       </c>
-      <c r="K8" s="54">
+      <c r="K8" s="50">
         <f>(J7-J8)/J7</f>
         <v>-4.1666666666666706E-2</v>
       </c>
-      <c r="L8" s="55">
+      <c r="L8" s="51">
         <f t="shared" si="3"/>
         <v>-4.1666666666666705</v>
       </c>
-      <c r="M8" s="54">
+      <c r="M8" s="50">
         <f t="shared" si="5"/>
         <v>0.45</v>
       </c>
-      <c r="N8" s="54">
+      <c r="N8" s="50">
         <f>(M7-M8)/M7</f>
         <v>0.19999999999999998</v>
       </c>
-      <c r="O8" s="55">
+      <c r="O8" s="51">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="P8" s="55">
+      <c r="P8" s="51">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="53">
+      <c r="Q8" s="49">
         <v>1</v>
       </c>
-      <c r="R8" s="53">
+      <c r="R8" s="49">
         <v>-85</v>
       </c>
-      <c r="S8" s="53">
+      <c r="S8" s="49">
         <v>-100</v>
       </c>
-      <c r="T8" s="53">
+      <c r="T8" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="53">
+      <c r="A9" s="49">
         <v>80</v>
       </c>
-      <c r="B9" s="53">
+      <c r="B9" s="49">
         <v>30</v>
       </c>
-      <c r="C9" s="53">
-        <v>0</v>
-      </c>
-      <c r="D9" s="53">
+      <c r="C9" s="49">
+        <v>0</v>
+      </c>
+      <c r="D9" s="49">
         <v>348</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="49">
         <v>358</v>
       </c>
-      <c r="F9" s="53">
+      <c r="F9" s="49">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="49">
         <v>303</v>
       </c>
-      <c r="H9" s="53">
+      <c r="H9" s="49">
         <v>322</v>
       </c>
-      <c r="I9" s="56">
+      <c r="I9" s="52">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="J9" s="54">
+      <c r="J9" s="50">
         <f t="shared" si="2"/>
         <v>0.5625</v>
       </c>
-      <c r="K9" s="54">
+      <c r="K9" s="50">
         <f>(J7-J9)/J7</f>
         <v>6.2499999999999965E-2</v>
       </c>
-      <c r="L9" s="55">
+      <c r="L9" s="51">
         <f t="shared" si="3"/>
         <v>6.2499999999999964</v>
       </c>
-      <c r="M9" s="54">
+      <c r="M9" s="50">
         <f t="shared" si="5"/>
         <v>0.75624999999999998</v>
       </c>
-      <c r="N9" s="54">
+      <c r="N9" s="50">
         <f>(M7-M9)/M7</f>
         <v>-0.34444444444444439</v>
       </c>
-      <c r="O9" s="55">
+      <c r="O9" s="51">
         <f t="shared" si="4"/>
         <v>-34.444444444444436</v>
       </c>
-      <c r="P9" s="55">
+      <c r="P9" s="51">
         <v>0.65</v>
       </c>
-      <c r="Q9" s="53">
+      <c r="Q9" s="49">
         <v>1</v>
       </c>
-      <c r="R9" s="53">
+      <c r="R9" s="49">
         <v>-160</v>
       </c>
-      <c r="S9" s="53">
+      <c r="S9" s="49">
         <v>-200</v>
       </c>
-      <c r="T9" s="53">
+      <c r="T9" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:20" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="57">
+      <c r="A10" s="53">
         <v>80</v>
       </c>
-      <c r="B10" s="57">
-        <v>0</v>
-      </c>
-      <c r="C10" s="57">
-        <v>0</v>
-      </c>
-      <c r="D10" s="57">
+      <c r="B10" s="53">
+        <v>0</v>
+      </c>
+      <c r="C10" s="53">
+        <v>0</v>
+      </c>
+      <c r="D10" s="53">
         <v>360</v>
       </c>
-      <c r="E10" s="57">
+      <c r="E10" s="53">
         <v>364</v>
       </c>
-      <c r="F10" s="57">
+      <c r="F10" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G10" s="57">
+      <c r="G10" s="53">
         <v>303</v>
       </c>
-      <c r="H10" s="58">
+      <c r="H10" s="54">
         <v>303.5</v>
       </c>
-      <c r="I10" s="59">
+      <c r="I10" s="55">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="J10" s="60">
+      <c r="J10" s="56">
         <f t="shared" si="2"/>
         <v>0.71250000000000002</v>
       </c>
-      <c r="K10" s="60">
+      <c r="K10" s="56">
         <f>(J7-J10)/J7</f>
         <v>-0.18750000000000008</v>
       </c>
-      <c r="L10" s="55">
+      <c r="L10" s="51">
         <f t="shared" si="3"/>
         <v>-18.750000000000007</v>
       </c>
-      <c r="M10" s="60">
+      <c r="M10" s="56">
         <f t="shared" si="5"/>
         <v>0.4</v>
       </c>
-      <c r="N10" s="60">
+      <c r="N10" s="56">
         <f>(M7-M10)/M7</f>
         <v>0.28888888888888886</v>
       </c>
-      <c r="O10" s="55">
+      <c r="O10" s="51">
         <f t="shared" si="4"/>
         <v>28.888888888888886</v>
       </c>
-      <c r="P10" s="58">
+      <c r="P10" s="54">
         <v>0.7</v>
       </c>
-      <c r="Q10" s="58">
+      <c r="Q10" s="54">
         <v>0.75</v>
       </c>
-      <c r="R10" s="57">
+      <c r="R10" s="53">
         <v>-150</v>
       </c>
-      <c r="S10" s="57">
+      <c r="S10" s="53">
         <v>-160</v>
       </c>
-      <c r="T10" s="57">
+      <c r="T10" s="53">
         <v>-140</v>
       </c>
     </row>
     <row r="11" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="53">
+      <c r="A11" s="49">
         <v>100</v>
       </c>
-      <c r="B11" s="53">
+      <c r="B11" s="49">
         <v>90</v>
       </c>
-      <c r="C11" s="53">
-        <v>0</v>
-      </c>
-      <c r="D11" s="53">
+      <c r="C11" s="49">
+        <v>0</v>
+      </c>
+      <c r="D11" s="49">
         <v>352</v>
       </c>
-      <c r="E11" s="53">
+      <c r="E11" s="49">
         <v>355</v>
       </c>
-      <c r="F11" s="53">
+      <c r="F11" s="49">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G11" s="53">
+      <c r="G11" s="49">
         <v>305</v>
       </c>
-      <c r="H11" s="53">
+      <c r="H11" s="49">
         <v>315</v>
       </c>
-      <c r="I11" s="56">
+      <c r="I11" s="52">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J11" s="54">
+      <c r="J11" s="50">
         <f t="shared" si="2"/>
         <v>0.47</v>
       </c>
-      <c r="K11" s="54">
-        <v>0</v>
-      </c>
-      <c r="L11" s="55">
-        <v>0</v>
-      </c>
-      <c r="M11" s="54">
+      <c r="K11" s="50">
+        <v>0</v>
+      </c>
+      <c r="L11" s="51">
+        <v>0</v>
+      </c>
+      <c r="M11" s="50">
         <f t="shared" si="5"/>
         <v>0.37</v>
       </c>
-      <c r="N11" s="54">
-        <v>0</v>
-      </c>
-      <c r="O11" s="55">
-        <v>0</v>
-      </c>
-      <c r="P11" s="55">
+      <c r="N11" s="50">
+        <v>0</v>
+      </c>
+      <c r="O11" s="51">
+        <v>0</v>
+      </c>
+      <c r="P11" s="51">
         <v>0.72</v>
       </c>
-      <c r="Q11" s="53">
+      <c r="Q11" s="49">
         <v>1</v>
       </c>
-      <c r="R11" s="53">
+      <c r="R11" s="49">
         <v>-130</v>
       </c>
-      <c r="S11" s="53">
+      <c r="S11" s="49">
         <v>-160</v>
       </c>
-      <c r="T11" s="53">
+      <c r="T11" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="53">
+      <c r="A12" s="49">
         <v>100</v>
       </c>
-      <c r="B12" s="53">
+      <c r="B12" s="49">
         <v>60</v>
       </c>
-      <c r="C12" s="53">
-        <v>0</v>
-      </c>
-      <c r="D12" s="53">
+      <c r="C12" s="49">
+        <v>0</v>
+      </c>
+      <c r="D12" s="49">
         <v>353</v>
       </c>
-      <c r="E12" s="53">
+      <c r="E12" s="49">
         <v>358</v>
       </c>
-      <c r="F12" s="53">
+      <c r="F12" s="49">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G12" s="53">
+      <c r="G12" s="49">
         <v>306</v>
       </c>
-      <c r="H12" s="53">
+      <c r="H12" s="49">
         <v>321</v>
       </c>
-      <c r="I12" s="56">
+      <c r="I12" s="52">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="J12" s="54">
+      <c r="J12" s="50">
         <f t="shared" si="2"/>
         <v>0.47</v>
       </c>
-      <c r="K12" s="54">
+      <c r="K12" s="50">
         <f>(J11-J12)/J11</f>
         <v>0</v>
       </c>
-      <c r="L12" s="55">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="54">
+      <c r="L12" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="50">
         <f t="shared" si="5"/>
         <v>0.32</v>
       </c>
-      <c r="N12" s="54">
+      <c r="N12" s="50">
         <f>(M11-M12)/M11</f>
         <v>0.13513513513513511</v>
       </c>
-      <c r="O12" s="55">
+      <c r="O12" s="51">
         <f t="shared" si="4"/>
         <v>13.513513513513512</v>
       </c>
-      <c r="P12" s="55">
+      <c r="P12" s="51">
         <v>0.75</v>
       </c>
-      <c r="Q12" s="53">
+      <c r="Q12" s="49">
         <v>1</v>
       </c>
-      <c r="R12" s="53">
+      <c r="R12" s="49">
         <v>-120</v>
       </c>
-      <c r="S12" s="53">
+      <c r="S12" s="49">
         <v>-130</v>
       </c>
-      <c r="T12" s="53">
+      <c r="T12" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="53">
+      <c r="A13" s="49">
         <v>100</v>
       </c>
-      <c r="B13" s="53">
+      <c r="B13" s="49">
         <v>30</v>
       </c>
-      <c r="C13" s="53">
-        <v>0</v>
-      </c>
-      <c r="D13" s="53">
+      <c r="C13" s="49">
+        <v>0</v>
+      </c>
+      <c r="D13" s="49">
         <v>346</v>
       </c>
-      <c r="E13" s="53">
+      <c r="E13" s="49">
         <v>357</v>
       </c>
-      <c r="F13" s="53">
+      <c r="F13" s="49">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="G13" s="53">
+      <c r="G13" s="49">
         <v>306</v>
       </c>
-      <c r="H13" s="53">
+      <c r="H13" s="49">
         <v>325</v>
       </c>
-      <c r="I13" s="56">
+      <c r="I13" s="52">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="J13" s="54">
+      <c r="J13" s="50">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="K13" s="54">
+      <c r="K13" s="50">
         <f>(J11-J13)/J11</f>
         <v>0.14893617021276587</v>
       </c>
-      <c r="L13" s="55">
+      <c r="L13" s="51">
         <f t="shared" si="3"/>
         <v>14.893617021276587</v>
       </c>
-      <c r="M13" s="54">
+      <c r="M13" s="50">
         <f t="shared" si="5"/>
         <v>0.79</v>
       </c>
-      <c r="N13" s="54">
+      <c r="N13" s="50">
         <f>(M11-M13)/M11</f>
         <v>-1.1351351351351353</v>
       </c>
-      <c r="O13" s="55">
+      <c r="O13" s="51">
         <f t="shared" si="4"/>
         <v>-113.51351351351353</v>
       </c>
-      <c r="P13" s="55">
+      <c r="P13" s="51">
         <v>0.45</v>
       </c>
-      <c r="Q13" s="53">
+      <c r="Q13" s="49">
         <v>1</v>
       </c>
-      <c r="R13" s="53">
+      <c r="R13" s="49">
         <v>-250</v>
       </c>
-      <c r="S13" s="53">
+      <c r="S13" s="49">
         <v>-280</v>
       </c>
-      <c r="T13" s="53">
+      <c r="T13" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="53">
+      <c r="A14" s="49">
         <v>100</v>
       </c>
-      <c r="B14" s="53">
-        <v>0</v>
-      </c>
-      <c r="C14" s="53">
-        <v>0</v>
-      </c>
-      <c r="D14" s="53">
+      <c r="B14" s="49">
+        <v>0</v>
+      </c>
+      <c r="C14" s="49">
+        <v>0</v>
+      </c>
+      <c r="D14" s="49">
         <v>350</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="49">
         <v>385</v>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="49">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="G14" s="53">
+      <c r="G14" s="49">
         <v>302</v>
       </c>
-      <c r="H14" s="53">
+      <c r="H14" s="49">
         <v>306</v>
       </c>
-      <c r="I14" s="56">
+      <c r="I14" s="52">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="J14" s="54">
+      <c r="J14" s="50">
         <f t="shared" si="2"/>
         <v>0.48</v>
       </c>
-      <c r="K14" s="54">
+      <c r="K14" s="50">
         <f>(J11-J14)/J11</f>
         <v>-2.1276595744680871E-2</v>
       </c>
-      <c r="L14" s="55">
+      <c r="L14" s="51">
         <f t="shared" si="3"/>
         <v>-2.1276595744680873</v>
       </c>
-      <c r="M14" s="54">
+      <c r="M14" s="50">
         <f t="shared" si="5"/>
         <v>0.34166666666666667</v>
       </c>
-      <c r="N14" s="54">
+      <c r="N14" s="50">
         <f>(M11-M14)/M11</f>
         <v>7.6576576576576544E-2</v>
       </c>
-      <c r="O14" s="55">
+      <c r="O14" s="51">
         <f t="shared" si="4"/>
         <v>7.657657657657654</v>
       </c>
-      <c r="P14" s="55">
+      <c r="P14" s="51">
         <v>0.67</v>
       </c>
-      <c r="Q14" s="55">
+      <c r="Q14" s="51">
         <v>0.69</v>
       </c>
-      <c r="R14" s="53">
+      <c r="R14" s="49">
         <v>-270</v>
       </c>
-      <c r="S14" s="53">
+      <c r="S14" s="49">
         <v>-370</v>
       </c>
-      <c r="T14" s="53">
+      <c r="T14" s="49">
         <v>-240</v>
       </c>
     </row>
     <row r="15" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="53">
+      <c r="A15" s="49">
         <v>120</v>
       </c>
-      <c r="B15" s="53">
+      <c r="B15" s="49">
         <v>90</v>
       </c>
-      <c r="C15" s="53">
-        <v>0</v>
-      </c>
-      <c r="D15" s="53">
+      <c r="C15" s="49">
+        <v>0</v>
+      </c>
+      <c r="D15" s="49">
         <v>353</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="49">
         <v>356</v>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="49">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G15" s="53">
+      <c r="G15" s="49">
         <v>304</v>
       </c>
-      <c r="H15" s="53">
+      <c r="H15" s="49">
         <v>315</v>
       </c>
-      <c r="I15" s="56">
+      <c r="I15" s="52">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="J15" s="54">
+      <c r="J15" s="50">
         <f t="shared" si="2"/>
         <v>0.40833333333333333</v>
       </c>
-      <c r="K15" s="54">
-        <v>0</v>
-      </c>
-      <c r="L15" s="55">
-        <v>0</v>
-      </c>
-      <c r="M15" s="54">
+      <c r="K15" s="50">
+        <v>0</v>
+      </c>
+      <c r="L15" s="51">
+        <v>0</v>
+      </c>
+      <c r="M15" s="50">
         <f t="shared" si="5"/>
         <v>0.35833333333333334</v>
       </c>
-      <c r="N15" s="54">
-        <v>0</v>
-      </c>
-      <c r="O15" s="55">
-        <v>0</v>
-      </c>
-      <c r="P15" s="55">
+      <c r="N15" s="50">
+        <v>0</v>
+      </c>
+      <c r="O15" s="51">
+        <v>0</v>
+      </c>
+      <c r="P15" s="51">
         <v>0.77</v>
       </c>
-      <c r="Q15" s="53">
+      <c r="Q15" s="49">
         <v>1</v>
       </c>
-      <c r="R15" s="53">
+      <c r="R15" s="49">
         <v>-100</v>
       </c>
-      <c r="S15" s="53">
+      <c r="S15" s="49">
         <v>-130</v>
       </c>
-      <c r="T15" s="53">
+      <c r="T15" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="53">
+      <c r="A16" s="49">
         <v>120</v>
       </c>
-      <c r="B16" s="53">
+      <c r="B16" s="49">
         <v>60</v>
       </c>
-      <c r="C16" s="53">
-        <v>0</v>
-      </c>
-      <c r="D16" s="53">
+      <c r="C16" s="49">
+        <v>0</v>
+      </c>
+      <c r="D16" s="49">
         <v>353</v>
       </c>
-      <c r="E16" s="53">
+      <c r="E16" s="49">
         <v>356</v>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="49">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="49">
         <v>307</v>
       </c>
-      <c r="H16" s="53">
+      <c r="H16" s="49">
         <v>313</v>
       </c>
-      <c r="I16" s="56">
+      <c r="I16" s="52">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="J16" s="54">
+      <c r="J16" s="50">
         <f t="shared" si="2"/>
         <v>0.38333333333333336</v>
       </c>
-      <c r="K16" s="54">
+      <c r="K16" s="50">
         <f>(J15-J16)/J15</f>
         <v>6.122448979591829E-2</v>
       </c>
-      <c r="L16" s="55">
+      <c r="L16" s="51">
         <f t="shared" si="3"/>
         <v>6.1224489795918293</v>
       </c>
-      <c r="M16" s="54">
+      <c r="M16" s="50">
         <f t="shared" si="5"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="N16" s="54">
+      <c r="N16" s="50">
         <f>(M15-M16)/M15</f>
         <v>0.18604651162790695</v>
       </c>
-      <c r="O16" s="55">
+      <c r="O16" s="51">
         <f t="shared" si="4"/>
         <v>18.604651162790695</v>
       </c>
-      <c r="P16" s="55">
+      <c r="P16" s="51">
         <v>0.8</v>
       </c>
-      <c r="Q16" s="53">
+      <c r="Q16" s="49">
         <v>1</v>
       </c>
-      <c r="R16" s="53">
+      <c r="R16" s="49">
         <v>-75</v>
       </c>
-      <c r="S16" s="53">
+      <c r="S16" s="49">
         <v>-85</v>
       </c>
-      <c r="T16" s="53">
+      <c r="T16" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="53">
+      <c r="A17" s="49">
         <v>120</v>
       </c>
-      <c r="B17" s="53">
+      <c r="B17" s="49">
         <v>30</v>
       </c>
-      <c r="C17" s="53">
-        <v>0</v>
-      </c>
-      <c r="D17" s="53">
+      <c r="C17" s="49">
+        <v>0</v>
+      </c>
+      <c r="D17" s="49">
         <v>348</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="49">
         <v>358</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="49">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G17" s="53">
+      <c r="G17" s="49">
         <v>303</v>
       </c>
-      <c r="H17" s="53">
+      <c r="H17" s="49">
         <v>323</v>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="52">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="J17" s="54">
+      <c r="J17" s="50">
         <f t="shared" si="2"/>
         <v>0.375</v>
       </c>
-      <c r="K17" s="54">
+      <c r="K17" s="50">
         <f>(J15-J17)/J15</f>
         <v>8.1632653061224469E-2</v>
       </c>
-      <c r="L17" s="55">
+      <c r="L17" s="51">
         <f t="shared" si="3"/>
         <v>8.1632653061224474</v>
       </c>
-      <c r="M17" s="54">
+      <c r="M17" s="50">
         <f t="shared" si="5"/>
         <v>1.2375</v>
       </c>
-      <c r="N17" s="54">
+      <c r="N17" s="50">
         <f>(M15-M17)/M15</f>
         <v>-2.4534883720930232</v>
       </c>
-      <c r="O17" s="55">
+      <c r="O17" s="51">
         <f t="shared" si="4"/>
         <v>-245.3488372093023</v>
       </c>
-      <c r="P17" s="55">
+      <c r="P17" s="51">
         <v>0.6</v>
       </c>
-      <c r="Q17" s="53">
+      <c r="Q17" s="49">
         <v>1</v>
       </c>
-      <c r="R17" s="53">
+      <c r="R17" s="49">
         <v>-185</v>
       </c>
-      <c r="S17" s="53">
+      <c r="S17" s="49">
         <v>-230</v>
       </c>
-      <c r="T17" s="53">
+      <c r="T17" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="53">
+      <c r="A18" s="49">
         <v>40</v>
       </c>
-      <c r="B18" s="53">
+      <c r="B18" s="49">
         <v>90</v>
       </c>
-      <c r="C18" s="53">
+      <c r="C18" s="49">
         <v>90</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="49">
         <v>342</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="49">
         <v>355</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="49">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="51">
         <v>304.5</v>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="51">
         <v>305.5</v>
       </c>
-      <c r="I18" s="56">
+      <c r="I18" s="52">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J18" s="54">
+      <c r="J18" s="50">
         <f t="shared" si="2"/>
         <v>0.9375</v>
       </c>
-      <c r="K18" s="54">
+      <c r="K18" s="50">
         <f>(J2-J18)/J2</f>
         <v>0.10714285714285718</v>
       </c>
-      <c r="L18" s="55">
+      <c r="L18" s="51">
         <f t="shared" si="3"/>
         <v>10.714285714285717</v>
       </c>
-      <c r="M18" s="54">
+      <c r="M18" s="50">
         <f t="shared" ref="M18:M31" si="6">(E18-H18)/A18</f>
         <v>1.2375</v>
       </c>
-      <c r="N18" s="54">
+      <c r="N18" s="50">
         <f>(M2-M18)/M2</f>
         <v>-0.33783783783783783</v>
       </c>
-      <c r="O18" s="55">
+      <c r="O18" s="51">
         <f t="shared" si="4"/>
         <v>-33.783783783783782</v>
       </c>
-      <c r="P18" s="55">
+      <c r="P18" s="51">
         <v>0.5</v>
       </c>
-      <c r="Q18" s="55">
+      <c r="Q18" s="51">
         <v>0.57999999999999996</v>
       </c>
-      <c r="R18" s="53">
+      <c r="R18" s="49">
         <v>-220</v>
       </c>
-      <c r="S18" s="53">
+      <c r="S18" s="49">
         <v>-235</v>
       </c>
-      <c r="T18" s="53">
+      <c r="T18" s="49">
         <v>-225</v>
       </c>
     </row>
     <row r="19" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="53">
+      <c r="A19" s="49">
         <v>40</v>
       </c>
-      <c r="B19" s="53">
+      <c r="B19" s="49">
         <v>90</v>
       </c>
-      <c r="C19" s="53">
+      <c r="C19" s="49">
         <v>60</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="49">
         <v>347</v>
       </c>
-      <c r="E19" s="53">
+      <c r="E19" s="49">
         <v>352</v>
       </c>
-      <c r="F19" s="53">
+      <c r="F19" s="49">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G19" s="53">
+      <c r="G19" s="49">
         <v>305</v>
       </c>
-      <c r="H19" s="53">
+      <c r="H19" s="49">
         <v>307</v>
       </c>
-      <c r="I19" s="56">
+      <c r="I19" s="52">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J19" s="54">
+      <c r="J19" s="50">
         <f t="shared" si="2"/>
         <v>1.05</v>
       </c>
-      <c r="K19" s="54">
+      <c r="K19" s="50">
         <f>(J2-J19)/J2</f>
         <v>0</v>
       </c>
-      <c r="L19" s="55">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="54">
+      <c r="L19" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="50">
         <f t="shared" si="6"/>
         <v>1.125</v>
       </c>
-      <c r="N19" s="54">
+      <c r="N19" s="50">
         <f>(M2-M19)/M2</f>
         <v>-0.21621621621621614</v>
       </c>
-      <c r="O19" s="55">
+      <c r="O19" s="51">
         <f t="shared" si="4"/>
         <v>-21.621621621621614</v>
       </c>
-      <c r="P19" s="55">
+      <c r="P19" s="51">
         <v>0.6</v>
       </c>
-      <c r="Q19" s="55">
+      <c r="Q19" s="51">
         <v>0.72</v>
       </c>
-      <c r="R19" s="53">
+      <c r="R19" s="49">
         <v>-175</v>
       </c>
-      <c r="S19" s="53">
+      <c r="S19" s="49">
         <v>-190</v>
       </c>
-      <c r="T19" s="53">
+      <c r="T19" s="49">
         <v>-120</v>
       </c>
     </row>
     <row r="20" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="53">
+      <c r="A20" s="49">
         <v>40</v>
       </c>
-      <c r="B20" s="53">
+      <c r="B20" s="49">
         <v>90</v>
       </c>
-      <c r="C20" s="53">
+      <c r="C20" s="49">
         <v>30</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="49">
         <v>350</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="49">
         <v>354</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="49">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="49">
         <v>305</v>
       </c>
-      <c r="H20" s="53">
+      <c r="H20" s="49">
         <v>306</v>
       </c>
-      <c r="I20" s="56">
+      <c r="I20" s="52">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J20" s="54">
+      <c r="J20" s="50">
         <f t="shared" si="2"/>
         <v>1.125</v>
       </c>
-      <c r="K20" s="54">
+      <c r="K20" s="50">
         <f>(J2-J20)/J2</f>
         <v>-7.1428571428571383E-2</v>
       </c>
-      <c r="L20" s="55">
+      <c r="L20" s="51">
         <f t="shared" si="3"/>
         <v>-7.1428571428571379</v>
       </c>
-      <c r="M20" s="54">
+      <c r="M20" s="50">
         <f t="shared" si="6"/>
         <v>1.2</v>
       </c>
-      <c r="N20" s="54">
+      <c r="N20" s="50">
         <f>(M2-M20)/M2</f>
         <v>-0.2972972972972972</v>
       </c>
-      <c r="O20" s="55">
+      <c r="O20" s="51">
         <f t="shared" si="4"/>
         <v>-29.729729729729719</v>
       </c>
-      <c r="P20" s="55">
+      <c r="P20" s="51">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q20" s="55">
+      <c r="Q20" s="51">
         <v>0.6</v>
       </c>
-      <c r="R20" s="53">
+      <c r="R20" s="49">
         <v>-230</v>
       </c>
-      <c r="S20" s="53">
+      <c r="S20" s="49">
         <v>-240</v>
       </c>
-      <c r="T20" s="53">
+      <c r="T20" s="49">
         <v>-220</v>
       </c>
     </row>
     <row r="21" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="53">
+      <c r="A21" s="49">
         <v>60</v>
       </c>
-      <c r="B21" s="53">
+      <c r="B21" s="49">
         <v>90</v>
       </c>
-      <c r="C21" s="53">
+      <c r="C21" s="49">
         <v>90</v>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="49">
         <v>345</v>
       </c>
-      <c r="E21" s="53">
+      <c r="E21" s="49">
         <v>368</v>
       </c>
-      <c r="F21" s="53">
+      <c r="F21" s="49">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="51">
         <v>304.5</v>
       </c>
-      <c r="H21" s="55">
+      <c r="H21" s="51">
         <v>307.5</v>
       </c>
-      <c r="I21" s="56">
+      <c r="I21" s="52">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J21" s="54">
+      <c r="J21" s="50">
         <f t="shared" si="2"/>
         <v>0.67500000000000004</v>
       </c>
-      <c r="K21" s="54"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="54">
+      <c r="K21" s="50"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="50">
         <f t="shared" si="6"/>
         <v>1.0083333333333333</v>
       </c>
-      <c r="N21" s="54"/>
-      <c r="O21" s="55"/>
-      <c r="P21" s="55">
+      <c r="N21" s="50"/>
+      <c r="O21" s="51"/>
+      <c r="P21" s="51">
         <v>0.62</v>
       </c>
-      <c r="Q21" s="55">
+      <c r="Q21" s="51">
         <v>0.8</v>
       </c>
-      <c r="R21" s="53">
+      <c r="R21" s="49">
         <v>-155</v>
       </c>
-      <c r="S21" s="53">
+      <c r="S21" s="49">
         <v>-175</v>
       </c>
-      <c r="T21" s="53">
+      <c r="T21" s="49">
         <v>-90</v>
       </c>
     </row>
     <row r="22" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="53">
+      <c r="A22" s="49">
         <v>60</v>
       </c>
-      <c r="B22" s="53">
+      <c r="B22" s="49">
         <v>90</v>
       </c>
-      <c r="C22" s="53">
+      <c r="C22" s="49">
         <v>60</v>
       </c>
-      <c r="D22" s="53">
+      <c r="D22" s="49">
         <v>342</v>
       </c>
-      <c r="E22" s="53">
+      <c r="E22" s="49">
         <v>351</v>
       </c>
-      <c r="F22" s="53">
+      <c r="F22" s="49">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G22" s="53">
+      <c r="G22" s="49">
         <v>305</v>
       </c>
-      <c r="H22" s="53">
+      <c r="H22" s="49">
         <v>320</v>
       </c>
-      <c r="I22" s="56">
+      <c r="I22" s="52">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="J22" s="54">
+      <c r="J22" s="50">
         <f t="shared" si="2"/>
         <v>0.6166666666666667</v>
       </c>
-      <c r="K22" s="54"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="54">
+      <c r="K22" s="50"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="50">
         <f t="shared" si="6"/>
         <v>0.51666666666666672</v>
       </c>
-      <c r="N22" s="54"/>
-      <c r="O22" s="55"/>
-      <c r="P22" s="55">
+      <c r="N22" s="50"/>
+      <c r="O22" s="51"/>
+      <c r="P22" s="51">
         <v>0.5</v>
       </c>
-      <c r="Q22" s="55">
+      <c r="Q22" s="51">
         <v>0.74</v>
       </c>
-      <c r="R22" s="53">
+      <c r="R22" s="49">
         <v>-220</v>
       </c>
-      <c r="S22" s="53">
+      <c r="S22" s="49">
         <v>-225</v>
       </c>
-      <c r="T22" s="53">
+      <c r="T22" s="49">
         <v>-75</v>
       </c>
     </row>
     <row r="23" spans="1:20" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="53">
+      <c r="A23" s="49">
         <v>60</v>
       </c>
-      <c r="B23" s="53">
+      <c r="B23" s="49">
         <v>90</v>
       </c>
-      <c r="C23" s="53">
+      <c r="C23" s="49">
         <v>30</v>
       </c>
-      <c r="D23" s="53">
+      <c r="D23" s="49">
         <v>351</v>
       </c>
-      <c r="E23" s="53">
+      <c r="E23" s="49">
         <v>354</v>
       </c>
-      <c r="F23" s="53">
+      <c r="F23" s="49">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G23" s="53">
+      <c r="G23" s="49">
         <v>307</v>
       </c>
-      <c r="H23" s="53">
+      <c r="H23" s="49">
         <v>319</v>
       </c>
-      <c r="I23" s="56">
+      <c r="I23" s="52">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="J23" s="54">
+      <c r="J23" s="50">
         <f t="shared" si="2"/>
         <v>0.73333333333333328</v>
       </c>
-      <c r="K23" s="54"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="54">
+      <c r="K23" s="50"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="50">
         <f t="shared" si="6"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="N23" s="54"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="55">
+      <c r="N23" s="50"/>
+      <c r="O23" s="51"/>
+      <c r="P23" s="51">
         <v>0.68</v>
       </c>
-      <c r="Q23" s="55">
+      <c r="Q23" s="51">
         <v>0.78</v>
       </c>
-      <c r="R23" s="53">
+      <c r="R23" s="49">
         <v>-130</v>
       </c>
-      <c r="S23" s="53">
+      <c r="S23" s="49">
         <v>-260</v>
       </c>
-      <c r="T23" s="53">
+      <c r="T23" s="49">
         <v>-70</v>
       </c>
     </row>
     <row r="24" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="53">
+      <c r="A24" s="49">
         <v>80</v>
       </c>
-      <c r="B24" s="53">
+      <c r="B24" s="49">
         <v>90</v>
       </c>
-      <c r="C24" s="53">
+      <c r="C24" s="49">
         <v>60</v>
       </c>
-      <c r="D24" s="53">
+      <c r="D24" s="49">
         <v>348</v>
       </c>
-      <c r="E24" s="53">
+      <c r="E24" s="49">
         <v>360</v>
       </c>
-      <c r="F24" s="53">
+      <c r="F24" s="49">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="G24" s="53">
+      <c r="G24" s="49">
         <v>304</v>
       </c>
-      <c r="H24" s="53">
+      <c r="H24" s="49">
         <v>329</v>
       </c>
-      <c r="I24" s="56">
+      <c r="I24" s="52">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="J24" s="54">
+      <c r="J24" s="50">
         <f t="shared" si="2"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="K24" s="54">
+      <c r="K24" s="50">
         <f>(J7-J24)/J7</f>
         <v>8.3333333333333232E-2</v>
       </c>
-      <c r="L24" s="55">
+      <c r="L24" s="51">
         <f t="shared" si="3"/>
         <v>8.3333333333333233</v>
       </c>
-      <c r="M24" s="54">
+      <c r="M24" s="50">
         <f t="shared" si="6"/>
         <v>0.38750000000000001</v>
       </c>
-      <c r="N24" s="54">
+      <c r="N24" s="50">
         <f>(M7-M24)/M7</f>
         <v>0.31111111111111112</v>
       </c>
-      <c r="O24" s="55">
+      <c r="O24" s="51">
         <f t="shared" si="4"/>
         <v>31.111111111111111</v>
       </c>
-      <c r="P24" s="55">
+      <c r="P24" s="51">
         <v>0.62</v>
       </c>
-      <c r="Q24" s="53">
+      <c r="Q24" s="49">
         <v>1</v>
       </c>
-      <c r="R24" s="53">
+      <c r="R24" s="49">
         <v>-160</v>
       </c>
-      <c r="S24" s="53">
+      <c r="S24" s="49">
         <v>-230</v>
       </c>
-      <c r="T24" s="53">
+      <c r="T24" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="53">
+      <c r="A25" s="49">
         <v>80</v>
       </c>
-      <c r="B25" s="53">
+      <c r="B25" s="49">
         <v>90</v>
       </c>
-      <c r="C25" s="53">
+      <c r="C25" s="49">
         <v>30</v>
       </c>
-      <c r="D25" s="53">
+      <c r="D25" s="49">
         <v>346</v>
       </c>
-      <c r="E25" s="53">
+      <c r="E25" s="49">
         <v>354</v>
       </c>
-      <c r="F25" s="53">
+      <c r="F25" s="49">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G25" s="53">
+      <c r="G25" s="49">
         <v>304</v>
       </c>
-      <c r="H25" s="53">
+      <c r="H25" s="49">
         <v>326</v>
       </c>
-      <c r="I25" s="56">
+      <c r="I25" s="52">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="J25" s="54">
+      <c r="J25" s="50">
         <f t="shared" si="2"/>
         <v>0.52500000000000002</v>
       </c>
-      <c r="K25" s="54">
+      <c r="K25" s="50">
         <f>(J7-J25)/J7</f>
         <v>0.12499999999999993</v>
       </c>
-      <c r="L25" s="55">
+      <c r="L25" s="51">
         <f t="shared" si="3"/>
         <v>12.499999999999993</v>
       </c>
-      <c r="M25" s="54">
+      <c r="M25" s="50">
         <f t="shared" si="6"/>
         <v>0.35</v>
       </c>
-      <c r="N25" s="54">
+      <c r="N25" s="50">
         <f>(M7-M25)/M7</f>
         <v>0.37777777777777782</v>
       </c>
-      <c r="O25" s="55">
+      <c r="O25" s="51">
         <f t="shared" si="4"/>
         <v>37.777777777777786</v>
       </c>
-      <c r="P25" s="55">
+      <c r="P25" s="51">
         <v>0.46</v>
       </c>
-      <c r="Q25" s="55">
+      <c r="Q25" s="51">
         <v>0.92</v>
       </c>
-      <c r="R25" s="53">
+      <c r="R25" s="49">
         <v>-255</v>
       </c>
-      <c r="S25" s="53">
+      <c r="S25" s="49">
         <v>-300</v>
       </c>
-      <c r="T25" s="53">
+      <c r="T25" s="49">
         <v>-20</v>
       </c>
     </row>
     <row r="26" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="53">
+      <c r="A26" s="49">
         <v>100</v>
       </c>
-      <c r="B26" s="53">
+      <c r="B26" s="49">
         <v>90</v>
       </c>
-      <c r="C26" s="53">
+      <c r="C26" s="49">
         <v>90</v>
       </c>
-      <c r="D26" s="53">
+      <c r="D26" s="49">
         <v>352</v>
       </c>
-      <c r="E26" s="53">
+      <c r="E26" s="49">
         <v>374</v>
       </c>
-      <c r="F26" s="53">
+      <c r="F26" s="49">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G26" s="53">
+      <c r="G26" s="49">
         <v>306</v>
       </c>
-      <c r="H26" s="53">
+      <c r="H26" s="49">
         <v>308</v>
       </c>
-      <c r="I26" s="56">
+      <c r="I26" s="52">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J26" s="54">
+      <c r="J26" s="50">
         <f t="shared" si="2"/>
         <v>0.46</v>
       </c>
-      <c r="K26" s="54">
+      <c r="K26" s="50">
         <f>(J11-J26)/J11</f>
         <v>2.1276595744680753E-2</v>
       </c>
-      <c r="L26" s="55">
+      <c r="L26" s="51">
         <f t="shared" si="3"/>
         <v>2.1276595744680753</v>
       </c>
-      <c r="M26" s="54">
+      <c r="M26" s="50">
         <f t="shared" si="6"/>
         <v>0.66</v>
       </c>
-      <c r="N26" s="54">
+      <c r="N26" s="50">
         <f>(M11-M26)/M11</f>
         <v>-0.78378378378378388</v>
       </c>
-      <c r="O26" s="55">
+      <c r="O26" s="51">
         <f t="shared" si="4"/>
         <v>-78.378378378378386</v>
       </c>
-      <c r="P26" s="55">
+      <c r="P26" s="51">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Q26" s="53">
+      <c r="Q26" s="49">
         <v>1</v>
       </c>
-      <c r="R26" s="53">
+      <c r="R26" s="49">
         <v>-150</v>
       </c>
-      <c r="S26" s="53">
+      <c r="S26" s="49">
         <v>-170</v>
       </c>
-      <c r="T26" s="53">
+      <c r="T26" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="53">
+      <c r="A27" s="49">
         <v>100</v>
       </c>
-      <c r="B27" s="53">
+      <c r="B27" s="49">
         <v>90</v>
       </c>
-      <c r="C27" s="53">
+      <c r="C27" s="49">
         <v>60</v>
       </c>
-      <c r="D27" s="53">
+      <c r="D27" s="49">
         <v>341</v>
       </c>
-      <c r="E27" s="53">
+      <c r="E27" s="49">
         <v>357</v>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="49">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G27" s="53">
+      <c r="G27" s="49">
         <v>302</v>
       </c>
-      <c r="H27" s="53">
+      <c r="H27" s="49">
         <v>330</v>
       </c>
-      <c r="I27" s="56">
+      <c r="I27" s="52">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="J27" s="54">
+      <c r="J27" s="50">
         <f t="shared" si="2"/>
         <v>0.39</v>
       </c>
-      <c r="K27" s="54">
+      <c r="K27" s="50">
         <f>(J11-J27)/J11</f>
         <v>0.17021276595744672</v>
       </c>
-      <c r="L27" s="55">
+      <c r="L27" s="51">
         <f t="shared" si="3"/>
         <v>17.021276595744673</v>
       </c>
-      <c r="M27" s="54">
+      <c r="M27" s="50">
         <f t="shared" si="6"/>
         <v>0.27</v>
       </c>
-      <c r="N27" s="54">
+      <c r="N27" s="50">
         <f>(M11-M27)/M11</f>
         <v>0.27027027027027023</v>
       </c>
-      <c r="O27" s="55">
+      <c r="O27" s="51">
         <f t="shared" si="4"/>
         <v>27.027027027027025</v>
       </c>
-      <c r="P27" s="55">
+      <c r="P27" s="51">
         <v>0.48</v>
       </c>
-      <c r="Q27" s="53">
+      <c r="Q27" s="49">
         <v>1</v>
       </c>
-      <c r="R27" s="53">
+      <c r="R27" s="49">
         <v>-220</v>
       </c>
-      <c r="S27" s="53">
+      <c r="S27" s="49">
         <v>-250</v>
       </c>
-      <c r="T27" s="53">
+      <c r="T27" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="53">
+      <c r="A28" s="49">
         <v>100</v>
       </c>
-      <c r="B28" s="53">
+      <c r="B28" s="49">
         <v>90</v>
       </c>
-      <c r="C28" s="53">
+      <c r="C28" s="49">
         <v>30</v>
       </c>
-      <c r="D28" s="53">
+      <c r="D28" s="49">
         <v>346</v>
       </c>
-      <c r="E28" s="53">
+      <c r="E28" s="49">
         <v>355</v>
       </c>
-      <c r="F28" s="53">
+      <c r="F28" s="49">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G28" s="53">
+      <c r="G28" s="49">
         <v>306</v>
       </c>
-      <c r="H28" s="53">
+      <c r="H28" s="49">
         <v>329</v>
       </c>
-      <c r="I28" s="56">
+      <c r="I28" s="52">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="J28" s="54">
+      <c r="J28" s="50">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="K28" s="54">
+      <c r="K28" s="50">
         <f>(J11-J28)/J11</f>
         <v>0.14893617021276587</v>
       </c>
-      <c r="L28" s="55">
+      <c r="L28" s="51">
         <f t="shared" si="3"/>
         <v>14.893617021276587</v>
       </c>
-      <c r="M28" s="54">
+      <c r="M28" s="50">
         <f t="shared" si="6"/>
         <v>0.26</v>
       </c>
-      <c r="N28" s="54">
+      <c r="N28" s="50">
         <f>(M11-M28)/M11</f>
         <v>0.29729729729729726</v>
       </c>
-      <c r="O28" s="55">
+      <c r="O28" s="51">
         <f t="shared" si="4"/>
         <v>29.729729729729726</v>
       </c>
-      <c r="P28" s="55">
+      <c r="P28" s="51">
         <v>0.6</v>
       </c>
-      <c r="Q28" s="53">
+      <c r="Q28" s="49">
         <v>1</v>
       </c>
-      <c r="R28" s="53">
+      <c r="R28" s="49">
         <v>-150</v>
       </c>
-      <c r="S28" s="53">
+      <c r="S28" s="49">
         <v>-210</v>
       </c>
-      <c r="T28" s="53">
+      <c r="T28" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="53">
+      <c r="A29" s="49">
         <v>120</v>
       </c>
-      <c r="B29" s="53">
+      <c r="B29" s="49">
         <v>90</v>
       </c>
-      <c r="C29" s="53">
+      <c r="C29" s="49">
         <v>90</v>
       </c>
-      <c r="D29" s="53">
+      <c r="D29" s="49">
         <v>354</v>
       </c>
-      <c r="E29" s="53">
+      <c r="E29" s="49">
         <v>370</v>
       </c>
-      <c r="F29" s="53">
+      <c r="F29" s="49">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G29" s="53">
+      <c r="G29" s="49">
         <v>304</v>
       </c>
-      <c r="H29" s="53">
+      <c r="H29" s="49">
         <v>314</v>
       </c>
-      <c r="I29" s="56">
+      <c r="I29" s="52">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J29" s="54">
+      <c r="J29" s="50">
         <f t="shared" si="2"/>
         <v>0.41666666666666669</v>
       </c>
-      <c r="K29" s="54">
+      <c r="K29" s="50">
         <f>(J15-J29)/J15</f>
         <v>-2.0408163265306187E-2</v>
       </c>
-      <c r="L29" s="55">
+      <c r="L29" s="51">
         <f t="shared" si="3"/>
         <v>-2.0408163265306185</v>
       </c>
-      <c r="M29" s="54">
+      <c r="M29" s="50">
         <f t="shared" si="6"/>
         <v>0.46666666666666667</v>
       </c>
-      <c r="N29" s="54">
+      <c r="N29" s="50">
         <f>(M15-M29)/M15</f>
         <v>-0.30232558139534882</v>
       </c>
-      <c r="O29" s="55">
+      <c r="O29" s="51">
         <f t="shared" si="4"/>
         <v>-30.232558139534881</v>
       </c>
-      <c r="P29" s="55">
+      <c r="P29" s="51">
         <v>0.6</v>
       </c>
-      <c r="Q29" s="53">
+      <c r="Q29" s="49">
         <v>1</v>
       </c>
-      <c r="R29" s="53">
+      <c r="R29" s="49">
         <v>215</v>
       </c>
-      <c r="S29" s="53">
+      <c r="S29" s="49">
         <v>-230</v>
       </c>
-      <c r="T29" s="53">
+      <c r="T29" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="53">
+      <c r="A30" s="49">
         <v>120</v>
       </c>
-      <c r="B30" s="53">
+      <c r="B30" s="49">
         <v>90</v>
       </c>
-      <c r="C30" s="53">
+      <c r="C30" s="49">
         <v>60</v>
       </c>
-      <c r="D30" s="53">
+      <c r="D30" s="49">
         <v>342</v>
       </c>
-      <c r="E30" s="53">
+      <c r="E30" s="49">
         <v>355</v>
       </c>
-      <c r="F30" s="53">
+      <c r="F30" s="49">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="G30" s="53">
+      <c r="G30" s="49">
         <v>302</v>
       </c>
-      <c r="H30" s="53">
+      <c r="H30" s="49">
         <v>330</v>
       </c>
-      <c r="I30" s="56">
+      <c r="I30" s="52">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="J30" s="54">
+      <c r="J30" s="50">
         <f t="shared" si="2"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="K30" s="54">
+      <c r="K30" s="50">
         <f>(J15-J30)/J15</f>
         <v>0.18367346938775514</v>
       </c>
-      <c r="L30" s="55">
+      <c r="L30" s="51">
         <f t="shared" si="3"/>
         <v>18.367346938775515</v>
       </c>
-      <c r="M30" s="54">
+      <c r="M30" s="50">
         <f t="shared" si="6"/>
         <v>0.20833333333333334</v>
       </c>
-      <c r="N30" s="54">
+      <c r="N30" s="50">
         <f>(M15-M30)/M15</f>
         <v>0.41860465116279066</v>
       </c>
-      <c r="O30" s="55">
+      <c r="O30" s="51">
         <f t="shared" si="4"/>
         <v>41.860465116279066</v>
       </c>
-      <c r="P30" s="55">
+      <c r="P30" s="51">
         <v>0.54</v>
       </c>
-      <c r="Q30" s="53">
+      <c r="Q30" s="49">
         <v>1</v>
       </c>
-      <c r="R30" s="53">
+      <c r="R30" s="49">
         <v>-215</v>
       </c>
-      <c r="S30" s="53">
+      <c r="S30" s="49">
         <v>-230</v>
       </c>
-      <c r="T30" s="53">
+      <c r="T30" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="53">
+      <c r="A31" s="49">
         <v>120</v>
       </c>
-      <c r="B31" s="53">
+      <c r="B31" s="49">
         <v>90</v>
       </c>
-      <c r="C31" s="53">
+      <c r="C31" s="49">
         <v>30</v>
       </c>
-      <c r="D31" s="53">
+      <c r="D31" s="49">
         <v>343</v>
       </c>
-      <c r="E31" s="53">
+      <c r="E31" s="49">
         <v>355</v>
       </c>
-      <c r="F31" s="53">
+      <c r="F31" s="49">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="G31" s="53">
+      <c r="G31" s="49">
         <v>304</v>
       </c>
-      <c r="H31" s="53">
+      <c r="H31" s="49">
         <v>327</v>
       </c>
-      <c r="I31" s="56">
+      <c r="I31" s="52">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="J31" s="54">
+      <c r="J31" s="50">
         <f t="shared" si="2"/>
         <v>0.32500000000000001</v>
       </c>
-      <c r="K31" s="54">
+      <c r="K31" s="50">
         <f>(J15-J31)/J15</f>
         <v>0.20408163265306117</v>
       </c>
-      <c r="L31" s="55">
+      <c r="L31" s="51">
         <f t="shared" si="3"/>
         <v>20.408163265306118</v>
       </c>
-      <c r="M31" s="54">
+      <c r="M31" s="50">
         <f t="shared" si="6"/>
         <v>0.23333333333333334</v>
       </c>
-      <c r="N31" s="54">
+      <c r="N31" s="50">
         <f>(M15-M31)/M15</f>
         <v>0.34883720930232559</v>
       </c>
-      <c r="O31" s="55">
+      <c r="O31" s="51">
         <f t="shared" si="4"/>
         <v>34.883720930232556</v>
       </c>
-      <c r="P31" s="55">
+      <c r="P31" s="51">
         <v>0.52</v>
       </c>
-      <c r="Q31" s="53">
+      <c r="Q31" s="49">
         <v>1</v>
       </c>
-      <c r="R31" s="53">
+      <c r="R31" s="49">
         <v>-200</v>
       </c>
-      <c r="S31" s="53">
+      <c r="S31" s="49">
         <v>-250</v>
       </c>
-      <c r="T31" s="53">
+      <c r="T31" s="49">
         <v>0</v>
       </c>
     </row>
@@ -3030,16 +3053,16 @@
   <dimension ref="A1:Q36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="9" style="49" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.26953125" style="50" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.54296875" style="51" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.54296875" style="49" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.81640625" style="49" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.453125" style="52" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="8.54296875" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="9" style="45" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" style="45" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.26953125" style="46" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.54296875" style="47" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.54296875" style="45" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.81640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.54296875" style="45" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.81640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.453125" style="48" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3299,7 +3322,7 @@
       </c>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" s="62" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="25">
         <v>60</v>
       </c>
@@ -3309,36 +3332,36 @@
       <c r="C6" s="26">
         <v>0</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="7">
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="60"/>
+      <c r="M6" s="26">
         <v>1</v>
       </c>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="s">
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="61">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="62" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3519,7 +3542,7 @@
       <c r="H10" s="7">
         <v>320</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="27">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
@@ -3658,60 +3681,60 @@
       </c>
       <c r="Q12" s="5"/>
     </row>
-    <row r="13" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="30">
+    <row r="13" spans="1:17" s="62" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="28">
         <v>80</v>
       </c>
-      <c r="B13" s="31">
-        <v>0</v>
-      </c>
-      <c r="C13" s="31">
-        <v>0</v>
-      </c>
-      <c r="D13" s="31">
+      <c r="B13" s="29">
+        <v>0</v>
+      </c>
+      <c r="C13" s="29">
+        <v>0</v>
+      </c>
+      <c r="D13" s="29">
         <v>360</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="29">
         <v>364</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="29">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="29">
         <v>303</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="30">
         <v>303.5</v>
       </c>
-      <c r="I13" s="33">
+      <c r="I13" s="63">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="64">
         <f t="shared" si="2"/>
         <v>0.71250000000000002</v>
       </c>
-      <c r="K13" s="22">
+      <c r="K13" s="64">
         <f t="shared" si="3"/>
         <v>0.75624999999999998</v>
       </c>
-      <c r="L13" s="32">
+      <c r="L13" s="30">
         <v>0.7</v>
       </c>
-      <c r="M13" s="32">
+      <c r="M13" s="30">
         <v>0.75</v>
       </c>
-      <c r="N13" s="31">
+      <c r="N13" s="29">
         <v>-150</v>
       </c>
-      <c r="O13" s="31">
+      <c r="O13" s="29">
         <v>-160</v>
       </c>
-      <c r="P13" s="34">
+      <c r="P13" s="31">
         <v>-140</v>
       </c>
-      <c r="Q13" s="5" t="s">
+      <c r="Q13" s="62" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3741,7 +3764,7 @@
       <c r="H14" s="7">
         <v>315</v>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="27">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3918,10 +3941,10 @@
         <f t="shared" si="3"/>
         <v>0.79</v>
       </c>
-      <c r="L17" s="35">
+      <c r="L17" s="32">
         <v>0.67</v>
       </c>
-      <c r="M17" s="35">
+      <c r="M17" s="32">
         <v>0.69</v>
       </c>
       <c r="N17" s="19">
@@ -3936,56 +3959,56 @@
       <c r="Q17" s="5"/>
     </row>
     <row r="18" spans="1:17" s="1" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="36">
+      <c r="A18" s="33">
         <v>120</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="34">
         <v>90</v>
       </c>
-      <c r="C18" s="37">
-        <v>0</v>
-      </c>
-      <c r="D18" s="37">
+      <c r="C18" s="34">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <v>353</v>
       </c>
-      <c r="E18" s="37">
+      <c r="E18" s="34">
         <v>356</v>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="34">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="34">
         <v>304</v>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="34">
         <v>315</v>
       </c>
-      <c r="I18" s="38">
+      <c r="I18" s="35">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="J18" s="39">
+      <c r="J18" s="36">
         <f t="shared" si="2"/>
         <v>0.40833333333333333</v>
       </c>
-      <c r="K18" s="39">
+      <c r="K18" s="36">
         <f t="shared" si="3"/>
         <v>0.34166666666666667</v>
       </c>
-      <c r="L18" s="40">
+      <c r="L18" s="37">
         <v>0.77</v>
       </c>
-      <c r="M18" s="37">
+      <c r="M18" s="34">
         <v>1</v>
       </c>
-      <c r="N18" s="37">
+      <c r="N18" s="34">
         <v>-100</v>
       </c>
-      <c r="O18" s="37">
+      <c r="O18" s="34">
         <v>-130</v>
       </c>
-      <c r="P18" s="41">
+      <c r="P18" s="38">
         <v>0</v>
       </c>
       <c r="Q18" s="5"/>
@@ -4101,42 +4124,42 @@
       <c r="Q20" s="5"/>
     </row>
     <row r="21" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="42">
+      <c r="A21" s="39">
         <v>120</v>
       </c>
-      <c r="B21" s="43">
-        <v>0</v>
-      </c>
-      <c r="C21" s="43">
+      <c r="B21" s="40">
+        <v>0</v>
+      </c>
+      <c r="C21" s="40">
         <v>0</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="43">
+      <c r="F21" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="44">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="45">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="45">
+      <c r="I21" s="41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="42">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21" s="4"/>
-      <c r="M21" s="43">
+      <c r="M21" s="40">
         <v>1</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="46">
+      <c r="P21" s="43">
         <v>0</v>
       </c>
       <c r="Q21" s="5"/>
@@ -4167,7 +4190,7 @@
       <c r="H22" s="9">
         <v>305.5</v>
       </c>
-      <c r="I22" s="28">
+      <c r="I22" s="27">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -4289,10 +4312,10 @@
         <f t="shared" si="3"/>
         <v>1.2</v>
       </c>
-      <c r="L24" s="35">
+      <c r="L24" s="32">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M24" s="35">
+      <c r="M24" s="32">
         <v>0.6</v>
       </c>
       <c r="N24" s="19">
@@ -4332,7 +4355,7 @@
       <c r="H25" s="9">
         <v>307.5</v>
       </c>
-      <c r="I25" s="28">
+      <c r="I25" s="27">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -4454,10 +4477,10 @@
         <f t="shared" si="3"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="L27" s="35">
+      <c r="L27" s="32">
         <v>0.68</v>
       </c>
-      <c r="M27" s="35">
+      <c r="M27" s="32">
         <v>0.78</v>
       </c>
       <c r="N27" s="19">
@@ -4471,46 +4494,46 @@
       </c>
       <c r="Q27" s="5"/>
     </row>
-    <row r="28" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="6">
+    <row r="28" spans="1:17" s="66" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="25">
         <v>80</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="26">
         <v>90</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="26">
         <v>90</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="29"/>
-      <c r="M28" s="7">
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="60"/>
+      <c r="M28" s="26">
         <v>1</v>
       </c>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="47" t="s">
+      <c r="N28" s="57"/>
+      <c r="O28" s="57"/>
+      <c r="P28" s="61">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="65" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4607,10 +4630,10 @@
         <f t="shared" si="3"/>
         <v>0.35</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="32">
         <v>0.46</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="32">
         <v>0.92</v>
       </c>
       <c r="N30" s="19">
@@ -4625,56 +4648,56 @@
       <c r="Q30" s="5"/>
     </row>
     <row r="31" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="37">
+      <c r="A31" s="34">
         <v>100</v>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="34">
         <v>90</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="34">
         <v>90</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="34">
         <v>352</v>
       </c>
-      <c r="E31" s="37">
+      <c r="E31" s="34">
         <v>374</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="34">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G31" s="37">
+      <c r="G31" s="34">
         <v>306</v>
       </c>
-      <c r="H31" s="37">
+      <c r="H31" s="34">
         <v>308</v>
       </c>
-      <c r="I31" s="38">
+      <c r="I31" s="35">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J31" s="39">
+      <c r="J31" s="36">
         <f t="shared" si="2"/>
         <v>0.46</v>
       </c>
-      <c r="K31" s="39">
+      <c r="K31" s="36">
         <f t="shared" si="3"/>
         <v>0.66</v>
       </c>
-      <c r="L31" s="40">
+      <c r="L31" s="37">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M31" s="37">
+      <c r="M31" s="34">
         <v>1</v>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="34">
         <v>-150</v>
       </c>
-      <c r="O31" s="37">
+      <c r="O31" s="34">
         <v>-170</v>
       </c>
-      <c r="P31" s="37">
+      <c r="P31" s="34">
         <v>0</v>
       </c>
       <c r="Q31" s="5"/>
@@ -4735,56 +4758,56 @@
       <c r="Q32" s="5"/>
     </row>
     <row r="33" spans="1:17" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="43">
+      <c r="A33" s="40">
         <v>100</v>
       </c>
-      <c r="B33" s="43">
+      <c r="B33" s="40">
         <v>90</v>
       </c>
-      <c r="C33" s="43">
+      <c r="C33" s="40">
         <v>30</v>
       </c>
-      <c r="D33" s="43">
+      <c r="D33" s="40">
         <v>346</v>
       </c>
-      <c r="E33" s="43">
+      <c r="E33" s="40">
         <v>355</v>
       </c>
-      <c r="F33" s="43">
+      <c r="F33" s="40">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G33" s="43">
+      <c r="G33" s="40">
         <v>306</v>
       </c>
-      <c r="H33" s="43">
+      <c r="H33" s="40">
         <v>329</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="41">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="J33" s="45">
+      <c r="J33" s="42">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="K33" s="45">
+      <c r="K33" s="42">
         <f t="shared" si="3"/>
         <v>0.26</v>
       </c>
-      <c r="L33" s="48">
+      <c r="L33" s="44">
         <v>0.6</v>
       </c>
-      <c r="M33" s="43">
+      <c r="M33" s="40">
         <v>1</v>
       </c>
-      <c r="N33" s="43">
+      <c r="N33" s="40">
         <v>-150</v>
       </c>
-      <c r="O33" s="43">
+      <c r="O33" s="40">
         <v>-210</v>
       </c>
-      <c r="P33" s="43">
+      <c r="P33" s="40">
         <v>0</v>
       </c>
       <c r="Q33" s="5"/>
@@ -4815,7 +4838,7 @@
       <c r="H34" s="7">
         <v>314</v>
       </c>
-      <c r="I34" s="28">
+      <c r="I34" s="27">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -4937,7 +4960,7 @@
         <f t="shared" si="3"/>
         <v>0.23333333333333334</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="32">
         <v>0.52</v>
       </c>
       <c r="M36" s="19">
@@ -4956,5 +4979,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>